--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -728,7 +728,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18687720981755</v>
+        <v>1.186902800450581</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178397171327068</v>
+        <v>1.178437406491532</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.176970672200089</v>
+        <v>1.17700486602399</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.17234234848569</v>
+        <v>1.172390918760026</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171086135683588</v>
+        <v>1.171137091222328</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169046162627955</v>
+        <v>1.169098864198401</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166572654673833</v>
+        <v>1.166625847547302</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164835296153384</v>
+        <v>1.164888204586424</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166057832340697</v>
+        <v>1.166092052145416</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161161988609994</v>
+        <v>1.161156083714228</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161619289124575</v>
+        <v>1.161615376376194</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160959900153929</v>
+        <v>1.160956774621778</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162371963967262</v>
+        <v>1.162351421841955</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159864178000481</v>
+        <v>1.159854253231951</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413007020844</v>
+        <v>1.155412840059236</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148412306635348</v>
+        <v>1.148415315380937</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143188942448233</v>
+        <v>1.143182491126262</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138118542031075</v>
+        <v>1.138095384336445</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130685110764329</v>
+        <v>1.130638093520714</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125654818564998</v>
+        <v>1.125598211726172</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.131233226734228</v>
+        <v>1.131114731826843</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138863068324055</v>
+        <v>1.138697830793306</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.146050683909448</v>
+        <v>1.145789928949136</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14990378938931</v>
+        <v>1.149603173336506</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.150476891553951</v>
+        <v>1.150120356521364</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.14488303986616</v>
+        <v>1.144517757860967</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.1434792149582</v>
+        <v>1.143102648436</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.1435630141753</v>
+        <v>1.143174119419744</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.153448030855769</v>
+        <v>1.153197821757523</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167895264089923</v>
+        <v>1.167726295125641</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.168180353170768</v>
+        <v>1.168027118243565</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18091127125484</v>
+        <v>1.180888870161153</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.189910804138842</v>
+        <v>1.190036773898356</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.197768622685644</v>
+        <v>1.197922726750471</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.208491065702363</v>
+        <v>1.208731488722015</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204466480868151</v>
+        <v>1.204581124456899</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.204548693175099</v>
+        <v>1.204723357054369</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.206223383272311</v>
+        <v>1.20655490745601</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.210367664509929</v>
+        <v>1.210818477996768</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.215740016579106</v>
+        <v>1.216253920971358</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.215753753050268</v>
+        <v>1.216165621812784</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20386403299272</v>
+        <v>1.204224044132874</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.195862743888921</v>
+        <v>1.19619530761212</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.186330858825448</v>
+        <v>1.18656913171081</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180091782305176</v>
+        <v>1.178689916116308</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176962653542671</v>
+        <v>1.174062406033669</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.175068354566955</v>
+        <v>1.172270130286155</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.178885743750777</v>
+        <v>1.175299502410065</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.175753173893575</v>
+        <v>1.172567525961105</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.176348144219204</v>
+        <v>1.172909019111415</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.180352305528654</v>
+        <v>1.175910471468638</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.177994402225844</v>
+        <v>1.173729907134625</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.169839031505593</v>
+        <v>1.167068013037915</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.172357940360906</v>
+        <v>1.167879153909016</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.172435590931006</v>
+        <v>1.167022211770132</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.171069942482187</v>
+        <v>1.164761839173605</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.17079196160487</v>
+        <v>1.162987917990073</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.170235187436597</v>
+        <v>1.161517249015118</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,15 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.1625</v>
+        <v>1.158101843199004</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B105">
+        <v>1.158827788251623</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -728,7 +728,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186902800450581</v>
+        <v>1.18691463673935</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178437406491532</v>
+        <v>1.178456026549486</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17700486602399</v>
+        <v>1.177020716454956</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172390918760026</v>
+        <v>1.172413421500651</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171137091222328</v>
+        <v>1.171160696246368</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169098864198401</v>
+        <v>1.169123275440607</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166625847547302</v>
+        <v>1.166650485076484</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164888204586424</v>
+        <v>1.164912710234433</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166092052145416</v>
+        <v>1.166107960343894</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161156083714228</v>
+        <v>1.161153369496857</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161615376376194</v>
+        <v>1.161613582893817</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160956774621778</v>
+        <v>1.160955344891255</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162351421841955</v>
+        <v>1.162341949533707</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159854253231951</v>
+        <v>1.159849672055166</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412840059236</v>
+        <v>1.155412788065898</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148415315380937</v>
+        <v>1.14841680214344</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143182491126262</v>
+        <v>1.14317965990382</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138095384336445</v>
+        <v>1.138084897333048</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130638093520714</v>
+        <v>1.130616522731457</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125598211726172</v>
+        <v>1.125572173132896</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.131114731826843</v>
+        <v>1.131060062204671</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138697830793306</v>
+        <v>1.138621504104175</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145789928949136</v>
+        <v>1.14566907241313</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.149603173336506</v>
+        <v>1.149463713811292</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.150120356521364</v>
+        <v>1.149954846664845</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.144517757860967</v>
+        <v>1.144347939356531</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.143102648436</v>
+        <v>1.142927347016935</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.143174119419744</v>
+        <v>1.142992779056463</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.153197821757523</v>
+        <v>1.153081016465429</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167726295125641</v>
+        <v>1.167647495554663</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.168027118243565</v>
+        <v>1.167955494597172</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180888870161153</v>
+        <v>1.180878337282076</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190036773898356</v>
+        <v>1.190095599445404</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.197922726750471</v>
+        <v>1.197994622869463</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.208731488722015</v>
+        <v>1.208843178009956</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204581124456899</v>
+        <v>1.204633373587777</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.204723357054369</v>
+        <v>1.204803327856649</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20655490745601</v>
+        <v>1.206707965741311</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.210818477996768</v>
+        <v>1.211027430722741</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.216253920971358</v>
+        <v>1.216492326704591</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.216165621812784</v>
+        <v>1.216356252496503</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.204224044132874</v>
+        <v>1.204390971380443</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.19619530761212</v>
+        <v>1.196349744844155</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18656913171081</v>
+        <v>1.186680158115997</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.178689916116308</v>
+        <v>1.178781870089386</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174062406033669</v>
+        <v>1.174130875653724</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172270130286155</v>
+        <v>1.17172285427948</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.175299502410065</v>
+        <v>1.174435945021729</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.172567525961105</v>
+        <v>1.171963374236966</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.172909019111415</v>
+        <v>1.172273061751404</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.175910471468638</v>
+        <v>1.174957953906169</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.173729907134625</v>
+        <v>1.172909306217818</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.167068013037915</v>
+        <v>1.16707301757613</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.167879153909016</v>
+        <v>1.167755853419217</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.167022211770132</v>
+        <v>1.166762373343062</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.164761839173605</v>
+        <v>1.164374398296756</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.162987917990073</v>
+        <v>1.16267641077641</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.161517249015118</v>
+        <v>1.160973419370873</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.158101843199004</v>
+        <v>1.157500299408557</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1200,7 +1200,15 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.158827788251623</v>
+        <v>1.156906706998747</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B106">
+        <v>1.152890025811895</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1104,7 +1104,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.174435945021729</v>
+        <v>1.174439087810002</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.171963374236966</v>
+        <v>1.17197249878455</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.172273061751404</v>
+        <v>1.172303213520417</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.174957953906169</v>
+        <v>1.174961151050093</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.172909306217818</v>
+        <v>1.172900913039211</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.16707301757613</v>
+        <v>1.167155894027612</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.167755853419217</v>
+        <v>1.167912802180815</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.166762373343062</v>
+        <v>1.166982320107445</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.164374398296756</v>
+        <v>1.164672086800313</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.16267641077641</v>
+        <v>1.163058744478849</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.160973419370873</v>
+        <v>1.161877855713146</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.157500299408557</v>
+        <v>1.159434325629321</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1200,7 +1200,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.156906706998747</v>
+        <v>1.159219247336718</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1208,7 +1208,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.152890025811895</v>
+        <v>1.156231022717773</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1200,7 +1200,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.159219247336718</v>
+        <v>1.159086454457785</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1208,7 +1208,15 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.156231022717773</v>
+        <v>1.15567109438797</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B107">
+        <v>1.150553704208414</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -728,7 +728,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18691463673935</v>
+        <v>1.18692589600032</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178456026549486</v>
+        <v>1.178473744903413</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177020716454956</v>
+        <v>1.177035814652653</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172413421500651</v>
+        <v>1.172434849356558</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171160696246368</v>
+        <v>1.171183172079141</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169123275440607</v>
+        <v>1.169146517382569</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166650485076484</v>
+        <v>1.16667394171328</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164912710234433</v>
+        <v>1.164936041231862</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166107960343894</v>
+        <v>1.166123140317201</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161153369496857</v>
+        <v>1.161150797543626</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161613582893817</v>
+        <v>1.161611886384956</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160955344891255</v>
+        <v>1.160953994190639</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162341949533707</v>
+        <v>1.162332956047032</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159849672055166</v>
+        <v>1.159845319729331</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412788065898</v>
+        <v>1.1554127533648</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.14841680214344</v>
+        <v>1.148418272233019</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14317965990382</v>
+        <v>1.143177056464381</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138084897333048</v>
+        <v>1.138075053517972</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130616522731457</v>
+        <v>1.130596107267561</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125572173132896</v>
+        <v>1.125547488699259</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.131060062204671</v>
+        <v>1.131008139831724</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138621504104175</v>
+        <v>1.138548959415886</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14566907241313</v>
+        <v>1.145553963047941</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.149463713811292</v>
+        <v>1.149330811939828</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.149954846664845</v>
+        <v>1.149797056209636</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.144347939356531</v>
+        <v>1.144185896366191</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142927347016935</v>
+        <v>1.142759933881933</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142992779056463</v>
+        <v>1.142819423493255</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.153081016465429</v>
+        <v>1.152969273601348</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167647495554663</v>
+        <v>1.167572157047563</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167955494597172</v>
+        <v>1.167886922276643</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180878337282076</v>
+        <v>1.180868214553718</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190095599445404</v>
+        <v>1.190151887170378</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.197994622869463</v>
+        <v>1.198063377760501</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.208843178009956</v>
+        <v>1.208949707761791</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204633373587777</v>
+        <v>1.204682615795975</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.204803327856649</v>
+        <v>1.204878914810253</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.206707965741311</v>
+        <v>1.206853390107145</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.211027430722741</v>
+        <v>1.21122644938298</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.216492326704591</v>
+        <v>1.216719519680838</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.216356252496503</v>
+        <v>1.216537658643296</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.204390971380443</v>
+        <v>1.204549995586971</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.196349744844155</v>
+        <v>1.196497008361789</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.186680158115997</v>
+        <v>1.186786248656436</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.178781870089386</v>
+        <v>1.178869786338816</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174130875653724</v>
+        <v>1.174196345554609</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17172285427948</v>
+        <v>1.171251390675486</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.174439087810002</v>
+        <v>1.17361293318207</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.17197249878455</v>
+        <v>1.171423963898234</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.172303213520417</v>
+        <v>1.172085106431751</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.174961151050093</v>
+        <v>1.174983330364731</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.172900913039211</v>
+        <v>1.173644652532417</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.167155894027612</v>
+        <v>1.169102043884245</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.167912802180815</v>
+        <v>1.170004213023621</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.166982320107445</v>
+        <v>1.16918843164945</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.164672086800313</v>
+        <v>1.167582261976458</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.163058744478849</v>
+        <v>1.1666382213196</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.161877855713146</v>
+        <v>1.166605974956324</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.159434325629321</v>
+        <v>1.165852893415045</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1200,7 +1200,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.159086454457785</v>
+        <v>1.167096588560188</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1208,7 +1208,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.15567109438797</v>
+        <v>1.16704676274408</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1216,7 +1216,15 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150553704208414</v>
+        <v>1.160971521834358</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B108">
+        <v>1.163987284281374</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -728,7 +728,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18692589600032</v>
+        <v>1.186936619417427</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178473744903413</v>
+        <v>1.178490625477302</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177035814652653</v>
+        <v>1.177050212856847</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172434849356558</v>
+        <v>1.172455277467459</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171183172079141</v>
+        <v>1.171204597772057</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169146517382569</v>
+        <v>1.169168671991581</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.16667394171328</v>
+        <v>1.16669630029059</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164936041231862</v>
+        <v>1.164958279979615</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166123140317201</v>
+        <v>1.166137640701499</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161150797543626</v>
+        <v>1.16114835700766</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161611886384956</v>
+        <v>1.161610279260852</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160953994190639</v>
+        <v>1.160952716225138</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162332956047032</v>
+        <v>1.162324406058071</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159845319729331</v>
+        <v>1.15984117958283</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.1554127533648</v>
+        <v>1.155412733659595</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148418272233019</v>
+        <v>1.148419722921864</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143177056464381</v>
+        <v>1.143174658379954</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138075053517972</v>
+        <v>1.138065798070279</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130596107267561</v>
+        <v>1.130576757766256</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125547488699259</v>
+        <v>1.12552405621724</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.131008139831724</v>
+        <v>1.130958763890279</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138548959415886</v>
+        <v>1.13847992412373</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145553963047941</v>
+        <v>1.145444202448872</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.149330811939828</v>
+        <v>1.149204018940292</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.149797056209636</v>
+        <v>1.149646461782713</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.144185896366191</v>
+        <v>1.144031112528705</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142759933881933</v>
+        <v>1.142599895530573</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142819423493255</v>
+        <v>1.142653546065752</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152969273601348</v>
+        <v>1.152862276314061</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167572157047563</v>
+        <v>1.167500058819225</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167886922276643</v>
+        <v>1.167821213696508</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180868214553718</v>
+        <v>1.180858478336881</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190151887170378</v>
+        <v>1.190205795416848</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198063377760501</v>
+        <v>1.198129190397463</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.208949707761791</v>
+        <v>1.209051425709503</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204682615795975</v>
+        <v>1.204729095221715</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.204878914810253</v>
+        <v>1.204950460545133</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.206853390107145</v>
+        <v>1.206991732348563</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21122644938298</v>
+        <v>1.211416221547001</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.216719519680838</v>
+        <v>1.216936266204755</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.216537658643296</v>
+        <v>1.21671048860339</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.204549995586971</v>
+        <v>1.204701659460325</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.196497008361789</v>
+        <v>1.196637580431972</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.186786248656436</v>
+        <v>1.186887719646871</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.178869786338816</v>
+        <v>1.178953920641584</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174196345554609</v>
+        <v>1.174259006476559</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171251390675486</v>
+        <v>1.171293723509259</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17361293318207</v>
+        <v>1.171851511487136</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.171423963898234</v>
+        <v>1.169567229703083</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.172085106431751</v>
+        <v>1.170164091553901</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.174983330364731</v>
+        <v>1.172659806736462</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.173644652532417</v>
+        <v>1.171128014434903</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.169102043884245</v>
+        <v>1.166565926200696</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.170004213023621</v>
+        <v>1.166813255429945</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.16918843164945</v>
+        <v>1.165437502905446</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.167582261976458</v>
+        <v>1.163314542151022</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.1666382213196</v>
+        <v>1.161312735626603</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.166605974956324</v>
+        <v>1.159611178140314</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.165852893415045</v>
+        <v>1.156703997772817</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1200,7 +1200,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.167096588560188</v>
+        <v>1.151338485118599</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1208,7 +1208,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.16704676274408</v>
+        <v>1.14239785704049</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1216,7 +1216,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.160971521834358</v>
+        <v>1.134297217102859</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1224,7 +1224,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.163987284281374</v>
+        <v>1.118624407433438</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -728,7 +728,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186936619417427</v>
+        <v>1.186946844347174</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178490625477302</v>
+        <v>1.178506726294745</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177050212856847</v>
+        <v>1.177063958585797</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172455277467459</v>
+        <v>1.172474774136119</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171204597772057</v>
+        <v>1.17122504517316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169168671991581</v>
+        <v>1.169189813756011</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.16669630029059</v>
+        <v>1.166717636078549</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164958279979615</v>
+        <v>1.164979501354716</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166137640701499</v>
+        <v>1.166151505919465</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.16114835700766</v>
+        <v>1.161146038113042</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161610279260852</v>
+        <v>1.161608754698815</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160952716225138</v>
+        <v>1.160951505344692</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162324406058071</v>
+        <v>1.162316267626579</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15984117958283</v>
+        <v>1.159837236519917</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412733659595</v>
+        <v>1.155412726966607</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148419722921864</v>
+        <v>1.148421152093146</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143174658379954</v>
+        <v>1.143172445857811</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138065798070279</v>
+        <v>1.138057082045148</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130576757766256</v>
+        <v>1.130558393765859</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12552405621724</v>
+        <v>1.125501783450399</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130958763890279</v>
+        <v>1.130911752568378</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.13847992412373</v>
+        <v>1.13841415106063</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145444202448872</v>
+        <v>1.145339428021976</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.149204018940292</v>
+        <v>1.149082925784894</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.149646461782713</v>
+        <v>1.14950258588095</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.144031112528705</v>
+        <v>1.143883115688872</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142599895530573</v>
+        <v>1.142446761416116</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142653546065752</v>
+        <v>1.142494681209527</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152862276314061</v>
+        <v>1.152759733156796</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167500058819225</v>
+        <v>1.16743099826446</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167821213696508</v>
+        <v>1.16775819602856</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180858478336881</v>
+        <v>1.180849106808764</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190205795416848</v>
+        <v>1.19025746984629</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198129190397463</v>
+        <v>1.19819224352069</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209051425709503</v>
+        <v>1.209148649168404</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204729095221715</v>
+        <v>1.20477303087694</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.204950460545133</v>
+        <v>1.205018273530373</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.206991732348563</v>
+        <v>1.207123492797474</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.211416221547001</v>
+        <v>1.211597373158158</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.216936266204755</v>
+        <v>1.217143264899667</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.21671048860339</v>
+        <v>1.216875331835807</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.204701659460325</v>
+        <v>1.204846457628694</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.196637580431972</v>
+        <v>1.196771901606039</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.186887719646871</v>
+        <v>1.186984861471903</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.178953920641584</v>
+        <v>1.179034508026354</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174259006476559</v>
+        <v>1.174319033516225</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171293723509259</v>
+        <v>1.171334267098691</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.171851511487136</v>
+        <v>1.171921050900616</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169567229703083</v>
+        <v>1.168544923018863</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.170164091553901</v>
+        <v>1.168969918923039</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.172659806736462</v>
+        <v>1.171223373576564</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.171128014434903</v>
+        <v>1.169780852844074</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.166565926200696</v>
+        <v>1.165256580634001</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.166813255429945</v>
+        <v>1.164649800240042</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.165437502905446</v>
+        <v>1.162478953257982</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.163314542151022</v>
+        <v>1.159764831252382</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.161312735626603</v>
+        <v>1.157575053597083</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.159611178140314</v>
+        <v>1.155174194938777</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.156703997772817</v>
+        <v>1.151513977620325</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1200,7 +1200,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151338485118599</v>
+        <v>1.143186132956882</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1208,7 +1208,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.14239785704049</v>
+        <v>1.1320548999308</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1216,7 +1216,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.134297217102859</v>
+        <v>1.123257598352522</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1224,7 +1224,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.118624407433438</v>
+        <v>1.117198178271131</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45114</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45121</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45128</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45135</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45142</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45170</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45205</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45233</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45261</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45296</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45324</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45352</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45387</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45415</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45443</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45478</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45506</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45541</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45569</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45597</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45632</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45660</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45688</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45716</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45751</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45779</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45814</v>
       </c>
       <c r="B41">
@@ -692,7 +718,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45821</v>
       </c>
       <c r="B42">
@@ -700,7 +726,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45828</v>
       </c>
       <c r="B43">
@@ -708,7 +734,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45835</v>
       </c>
       <c r="B44">
@@ -716,7 +742,7 @@
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45842</v>
       </c>
       <c r="B45">
@@ -724,507 +750,515 @@
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186946844347174</v>
+        <v>1.186956604753084</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178506726294745</v>
+        <v>1.178522100144093</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177063958585797</v>
+        <v>1.177077095157208</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172474774136119</v>
+        <v>1.172493401587908</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17122504517316</v>
+        <v>1.171244579728551</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169189813756011</v>
+        <v>1.16921001051849</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166717636078549</v>
+        <v>1.16673801762759</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164979501354716</v>
+        <v>1.164999773549104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166151505919465</v>
+        <v>1.166164776624228</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161146038113042</v>
+        <v>1.161143832026278</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161608754698815</v>
+        <v>1.161607306548503</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160951505344692</v>
+        <v>1.160950356464129</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162316267626579</v>
+        <v>1.162308511801071</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159837236519917</v>
+        <v>1.159833476839363</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412726966607</v>
+        <v>1.155412731568041</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148421152093146</v>
+        <v>1.148422558131896</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143172445857811</v>
+        <v>1.14317040138143</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138057082045148</v>
+        <v>1.138048861623561</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130558393765859</v>
+        <v>1.130540942632779</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125501783450399</v>
+        <v>1.125480586953054</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130911752568378</v>
+        <v>1.13086694087397</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.13841415106063</v>
+        <v>1.138351415613295</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145339428021976</v>
+        <v>1.145239309068964</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.149082925784894</v>
+        <v>1.148967158924978</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14950258588095</v>
+        <v>1.149364991998083</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143883115688872</v>
+        <v>1.143741473325497</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142446761416116</v>
+        <v>1.142300099622889</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142494681209527</v>
+        <v>1.142342400477832</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152759733156796</v>
+        <v>1.152661375649083</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16743099826446</v>
+        <v>1.167364789147193</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16775819602856</v>
+        <v>1.167697709814369</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180849106808764</v>
+        <v>1.180840079785721</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19025746984629</v>
+        <v>1.190307044657563</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19819224352069</v>
+        <v>1.198252705234719</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209148649168404</v>
+        <v>1.209241668276932</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20477303087694</v>
+        <v>1.204814619740256</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205018273530373</v>
+        <v>1.205082632165875</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207123492797474</v>
+        <v>1.207249126136387</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.211597373158158</v>
+        <v>1.211770475243342</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.217143264899667</v>
+        <v>1.217341153952818</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.216875331835807</v>
+        <v>1.217032725394421</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.204846457628694</v>
+        <v>1.204984841794274</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.196771901606039</v>
+        <v>1.196900375071196</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.186984861471903</v>
+        <v>1.187077941127664</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179034508026354</v>
+        <v>1.179111764789146</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174319033516225</v>
+        <v>1.174376587677309</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171334267098691</v>
+        <v>1.17137313136477</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.171921050900616</v>
+        <v>1.171987660158468</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168544923018863</v>
+        <v>1.168590385341926</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168969918923039</v>
+        <v>1.167179509380815</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.171223373576564</v>
+        <v>1.169066539362972</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.169780852844074</v>
+        <v>1.167535837040877</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.165256580634001</v>
+        <v>1.162585543553496</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.164649800240042</v>
+        <v>1.161054351182938</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.162478953257982</v>
+        <v>1.157786794044967</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.159764831252382</v>
+        <v>1.153901847164447</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.157575053597083</v>
+        <v>1.150582312791355</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.155174194938777</v>
+        <v>1.14715772728643</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.151513977620325</v>
+        <v>1.141360115052619</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="2">
+      <c r="A105" s="3">
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.143186132956882</v>
+        <v>1.135294211420063</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="2">
+      <c r="A106" s="3">
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.1320548999308</v>
+        <v>1.123202292910311</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="2">
+      <c r="A107" s="3">
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.123257598352522</v>
+        <v>1.114153311510164</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="2">
+      <c r="A108" s="3">
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.117198178271131</v>
+        <v>1.105069842940622</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B109">
+        <v>1.085569842940622</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186956604753084</v>
+        <v>1.186965931582305</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178522100144093</v>
+        <v>1.178536795155666</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177077095157208</v>
+        <v>1.177089662141782</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172493401587908</v>
+        <v>1.172511216631388</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171244579728551</v>
+        <v>1.171263261179246</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16921001051849</v>
+        <v>1.169229324200227</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.16673801762759</v>
+        <v>1.166757507501298</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.164999773549104</v>
+        <v>1.165019158798762</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166164776624228</v>
+        <v>1.166177490088711</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161143832026278</v>
+        <v>1.16114173074578</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161607306548503</v>
+        <v>1.161605929251561</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160950356464129</v>
+        <v>1.160949264994826</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162308511801071</v>
+        <v>1.162301112277884</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159833476839363</v>
+        <v>1.159829888077507</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412731568041</v>
+        <v>1.155412745972922</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148422558131896</v>
+        <v>1.148423939835588</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14317040138143</v>
+        <v>1.143168509406882</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138048861623561</v>
+        <v>1.138041097472282</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130540942632779</v>
+        <v>1.130524338639092</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125480586953054</v>
+        <v>1.125460391052621</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.13086694087397</v>
+        <v>1.130824178742633</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138351415613295</v>
+        <v>1.138291513220033</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145239309068964</v>
+        <v>1.145143543372138</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148967158924978</v>
+        <v>1.148856376551972</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.149364991998083</v>
+        <v>1.149233280354109</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143741473325497</v>
+        <v>1.143605788527309</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142300099622889</v>
+        <v>1.142159513044942</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142342400477832</v>
+        <v>1.142196308999287</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152661375649083</v>
+        <v>1.152566956106062</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167364789147193</v>
+        <v>1.16730125999895</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167697709814369</v>
+        <v>1.167639607726535</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180840079785721</v>
+        <v>1.180831378567426</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190307044657563</v>
+        <v>1.190354643671752</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198252705234719</v>
+        <v>1.198310730424185</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209241668276932</v>
+        <v>1.209330748832742</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204814619740256</v>
+        <v>1.204854039411905</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205082632165875</v>
+        <v>1.20514378830697</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207249126136387</v>
+        <v>1.207369046447575</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.211770475243342</v>
+        <v>1.211936049770325</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.217341153952818</v>
+        <v>1.217530517457987</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.217032725394421</v>
+        <v>1.217183159581963</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.204984841794274</v>
+        <v>1.205117225245201</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.196900375071196</v>
+        <v>1.197023370476915</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187077941127664</v>
+        <v>1.187167204478892</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179111764789146</v>
+        <v>1.179185890284779</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174376587677309</v>
+        <v>1.17443181724302</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17137313136477</v>
+        <v>1.171410417507282</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.171987660158468</v>
+        <v>1.172051518901117</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168590385341926</v>
+        <v>1.168633862440298</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167179509380815</v>
+        <v>1.167230492035406</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.169066539362972</v>
+        <v>1.166605336801641</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.167535837040877</v>
+        <v>1.164748680928667</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.162585543553496</v>
+        <v>1.159850193818048</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.161054351182938</v>
+        <v>1.157320404503362</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.157786794044967</v>
+        <v>1.15329772682442</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.153901847164447</v>
+        <v>1.148698714825542</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.150582312791355</v>
+        <v>1.144714421875135</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.14715772728643</v>
+        <v>1.140616469401034</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.141360115052619</v>
+        <v>1.134346172092954</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.135294211420063</v>
+        <v>1.125342099703679</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.123202292910311</v>
+        <v>1.113067900098153</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.114153311510164</v>
+        <v>1.10399384187574</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.105069842940622</v>
+        <v>1.092635737213677</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.085569842940622</v>
+        <v>1.073135737213677</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B110">
+        <v>1.053635737213677</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186965931582305</v>
+        <v>1.186974853093148</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178536795155666</v>
+        <v>1.178550855304256</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177089662141782</v>
+        <v>1.177101695759316</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172511216631388</v>
+        <v>1.172528271234647</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171263261179246</v>
+        <v>1.17128114416902</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169229324200227</v>
+        <v>1.169247811432707</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166757507501298</v>
+        <v>1.166776162915466</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165019158798762</v>
+        <v>1.165037714019524</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166177490088711</v>
+        <v>1.166189680547976</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.16114173074578</v>
+        <v>1.161139727006503</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161605929251561</v>
+        <v>1.161604617772464</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160949264994826</v>
+        <v>1.160948226785997</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162301112277884</v>
+        <v>1.162294045105802</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159829888077507</v>
+        <v>1.159826458871992</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412745972922</v>
+        <v>1.155412768884381</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148423939835588</v>
+        <v>1.148425296340682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143168509406882</v>
+        <v>1.14316675610513</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138041097472282</v>
+        <v>1.138033754195904</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130524338639092</v>
+        <v>1.130508522166737</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125460391052621</v>
+        <v>1.125441126969507</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130824178742633</v>
+        <v>1.130783329394057</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138291513220033</v>
+        <v>1.138234257192864</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145143543372138</v>
+        <v>1.145051854206801</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148856376551972</v>
+        <v>1.148750265318074</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.149233280354109</v>
+        <v>1.149107084142865</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143605788527309</v>
+        <v>1.143475696442947</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142159513044942</v>
+        <v>1.142024636001077</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142196308999287</v>
+        <v>1.142056042322165</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152566956106062</v>
+        <v>1.152476245702937</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16730125999895</v>
+        <v>1.167240252699383</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167639607726535</v>
+        <v>1.167583753461206</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180831378567426</v>
+        <v>1.180822985799296</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190354643671752</v>
+        <v>1.190400381298853</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198310730424185</v>
+        <v>1.198366462011102</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209330748832742</v>
+        <v>1.209416134782367</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204854039411905</v>
+        <v>1.204891450399171</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20514378830697</v>
+        <v>1.205201970310567</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207369046447575</v>
+        <v>1.207483631611599</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.211936049770325</v>
+        <v>1.212094574775625</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.217530517457987</v>
+        <v>1.217711890982681</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.217183159581963</v>
+        <v>1.217327082892916</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205117225245201</v>
+        <v>1.205243986815999</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197023370476915</v>
+        <v>1.19714122730738</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187167204478892</v>
+        <v>1.187252878266533</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179185890284779</v>
+        <v>1.179257068521652</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17443181724302</v>
+        <v>1.174484858993407</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171410417507282</v>
+        <v>1.171446218841946</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172051518901117</v>
+        <v>1.172112792525191</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168633862440298</v>
+        <v>1.168675480296499</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167230492035406</v>
+        <v>1.167279286250546</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.166605336801641</v>
+        <v>1.166680894293273</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.164748680928667</v>
+        <v>1.164814625475382</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.159850193818048</v>
+        <v>1.158313397045556</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.157320404503362</v>
+        <v>1.155620117155315</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.15329772682442</v>
+        <v>1.151643958429476</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.148698714825542</v>
+        <v>1.146493268662257</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144714421875135</v>
+        <v>1.142190153490532</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.140616469401034</v>
+        <v>1.137779831187534</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.134346172092954</v>
+        <v>1.131336645669953</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.125342099703679</v>
+        <v>1.1221690816007</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.113067900098153</v>
+        <v>1.110251510499844</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.10399384187574</v>
+        <v>1.099424536752973</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.092635737213677</v>
+        <v>1.092464417248675</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.073135737213677</v>
+        <v>1.062517083518139</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.053635737213677</v>
+        <v>1.055500356309899</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B111">
+        <v>1.075000356309899</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.155620117155315</v>
+        <v>1.155636108735207</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.151643958429476</v>
+        <v>1.151696520704965</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.146493268662257</v>
+        <v>1.146665958232892</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.142190153490532</v>
+        <v>1.142471920044953</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.137779831187534</v>
+        <v>1.138246133786372</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.131336645669953</v>
+        <v>1.132075943951957</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.1221690816007</v>
+        <v>1.123396763235553</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.110251510499844</v>
+        <v>1.111996700551196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.099424536752973</v>
+        <v>1.101815913531352</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.092464417248675</v>
+        <v>1.090096295291388</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.062517083518139</v>
+        <v>1.056976943360777</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.055500356309899</v>
+        <v>1.046800259128525</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.075000356309899</v>
+        <v>1.061522632122829</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186974853093148</v>
+        <v>1.186983395140856</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178550855304256</v>
+        <v>1.178564320847982</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177101695759316</v>
+        <v>1.177113229225654</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172528271234647</v>
+        <v>1.172544613029659</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17128114416902</v>
+        <v>1.171298278776241</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169247811432707</v>
+        <v>1.169265524110275</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166776162915466</v>
+        <v>1.166794036297088</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165037714019524</v>
+        <v>1.165055491363221</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166189680547976</v>
+        <v>1.166201379501024</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161139727006503</v>
+        <v>1.161137814197366</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161604617772464</v>
+        <v>1.161603367538793</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160948226785997</v>
+        <v>1.160947238074062</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162294045105802</v>
+        <v>1.162287288429283</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159826458871992</v>
+        <v>1.159823178843066</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412768884381</v>
+        <v>1.155412799172126</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148425296340682</v>
+        <v>1.148426627062117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14316675610513</v>
+        <v>1.1431651291425</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138033754195904</v>
+        <v>1.138026799866064</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130508522166737</v>
+        <v>1.130493439018616</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125441126969507</v>
+        <v>1.125422732053424</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130783329394057</v>
+        <v>1.13074426790013</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138234257192864</v>
+        <v>1.138179476816153</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.145051854206801</v>
+        <v>1.144963987720286</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148750265318074</v>
+        <v>1.148648537452538</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.149107084142865</v>
+        <v>1.148986066226601</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143475696442947</v>
+        <v>1.143350861142091</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.142024636001077</v>
+        <v>1.141895131230496</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.142056042322165</v>
+        <v>1.141921263598751</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152476245702937</v>
+        <v>1.15238903274641</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167240252699383</v>
+        <v>1.167181621215482</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167583753461206</v>
+        <v>1.167530020746521</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180822985799296</v>
+        <v>1.180814885350588</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190400381298853</v>
+        <v>1.190444363400629</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198366462011102</v>
+        <v>1.198420032073488</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209416134782367</v>
+        <v>1.209498050412622</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204891450399171</v>
+        <v>1.204926998090213</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205201970310567</v>
+        <v>1.205257385676167</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207483631611599</v>
+        <v>1.207593227150229</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.212094574775625</v>
+        <v>1.21224648886607</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.217711890982681</v>
+        <v>1.217885766467302</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.217327082892916</v>
+        <v>1.2174649063467</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205243986815999</v>
+        <v>1.205365474372717</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.19714122730738</v>
+        <v>1.197254257860579</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187252878266533</v>
+        <v>1.187335171896344</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179257068521652</v>
+        <v>1.179325469583844</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174484858993407</v>
+        <v>1.174535839287316</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171446218841946</v>
+        <v>1.171480621544338</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172112792525191</v>
+        <v>1.172171633552644</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168675480296499</v>
+        <v>1.168715354557122</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167279286250546</v>
+        <v>1.167326028680922</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.166680894293273</v>
+        <v>1.166753370575216</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.164814625475382</v>
+        <v>1.164877847257927</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158313397045556</v>
+        <v>1.156978850621458</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.155636108735207</v>
+        <v>1.154183377613855</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.151696520704965</v>
+        <v>1.150326449530365</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.146665958232892</v>
+        <v>1.144944829300629</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.142471920044953</v>
+        <v>1.140595883026159</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.138246133786372</v>
+        <v>1.136291297108381</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.132075943951957</v>
+        <v>1.130235565244644</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.123396763235553</v>
+        <v>1.121894213131096</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.111996700551196</v>
+        <v>1.111196756914988</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.101815913531352</v>
+        <v>1.100192611582596</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.090096295291388</v>
+        <v>1.088292761764193</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.056976943360777</v>
+        <v>1.060432711969195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.046800259128525</v>
+        <v>1.05334636617006</v>
       </c>
     </row>
     <row r="111" spans="1:2">

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186983395140856</v>
+        <v>1.186991581427701</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178564320847982</v>
+        <v>1.178577228712697</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177113229225654</v>
+        <v>1.177124293057457</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172544613029659</v>
+        <v>1.172560285754908</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171298278776241</v>
+        <v>1.171314710980518</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169265524110275</v>
+        <v>1.169282509874926</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166794036297088</v>
+        <v>1.166811175774718</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165055491363221</v>
+        <v>1.165072538705526</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166201379501024</v>
+        <v>1.166212615977509</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161137814197366</v>
+        <v>1.161135986289512</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161603367538793</v>
+        <v>1.161602174389465</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160947238074062</v>
+        <v>1.160946295438852</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162287288429283</v>
+        <v>1.162280822264546</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159823178843066</v>
+        <v>1.15982003848987</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412799172126</v>
+        <v>1.155412835849235</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148426627062117</v>
+        <v>1.14842793164335</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.1431651291425</v>
+        <v>1.143163617493046</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138026799866064</v>
+        <v>1.138020205615586</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130493439018616</v>
+        <v>1.130479039820297</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125422732053424</v>
+        <v>1.125405149118626</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.13074426790013</v>
+        <v>1.130706879933593</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138179476816153</v>
+        <v>1.138127015681829</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144963987720286</v>
+        <v>1.144879710626426</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148648537452538</v>
+        <v>1.148550928219384</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148986066226601</v>
+        <v>1.148869916217209</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143350861142091</v>
+        <v>1.143230972834018</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141895131230496</v>
+        <v>1.141770687221095</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141921263598751</v>
+        <v>1.141791661069203</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15238903274641</v>
+        <v>1.152305121128532</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167181621215482</v>
+        <v>1.167125230479437</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167530020746521</v>
+        <v>1.167478292453564</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180814885350588</v>
+        <v>1.180807062206028</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190444363400629</v>
+        <v>1.190486688062088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198420032073488</v>
+        <v>1.198471562842539</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209498050412622</v>
+        <v>1.20957670228447</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204926998090213</v>
+        <v>1.2049608144642</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205257385676167</v>
+        <v>1.205310223342579</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207593227150229</v>
+        <v>1.207698149593389</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21224648886607</v>
+        <v>1.21239219518099</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.217885766467302</v>
+        <v>1.218052596547141</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.2174649063467</v>
+        <v>1.217597007296509</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205365474372717</v>
+        <v>1.205482007887321</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197254257860579</v>
+        <v>1.197362749885717</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187335171896344</v>
+        <v>1.187414279035007</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179325469583844</v>
+        <v>1.179391250901314</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174535839287316</v>
+        <v>1.174584875025972</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171480621544338</v>
+        <v>1.171513705312283</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172171633552644</v>
+        <v>1.172228182846796</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168715354557122</v>
+        <v>1.168753591561213</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167326028680922</v>
+        <v>1.167370844936719</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.166753370575216</v>
+        <v>1.166822949090876</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.164877847257927</v>
+        <v>1.164938510685051</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.156978850621458</v>
+        <v>1.157027607245663</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.154183377613855</v>
+        <v>1.152955962094027</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.150326449530365</v>
+        <v>1.149177577626898</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144944829300629</v>
+        <v>1.144026426123888</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140595883026159</v>
+        <v>1.139559058927149</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.136291297108381</v>
+        <v>1.135308951256966</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.130235565244644</v>
+        <v>1.129418726266183</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.121894213131096</v>
+        <v>1.121233057474158</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.111196756914988</v>
+        <v>1.111053326102876</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.100192611582596</v>
+        <v>1.100762096281367</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.088292761764193</v>
+        <v>1.088639001536621</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.060432711969195</v>
+        <v>1.064909869612106</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.05334636617006</v>
+        <v>1.058254185487455</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.061522632122829</v>
+        <v>1.073731752323389</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B112">
+        <v>1.093231752323389</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186991581427701</v>
+        <v>1.186999433722475</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178577228712697</v>
+        <v>1.178589612829667</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177124293057457</v>
+        <v>1.177134915340641</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172560285754908</v>
+        <v>1.172575329644929</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171314710980518</v>
+        <v>1.171330483073311</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169282509874926</v>
+        <v>1.169298812542791</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166811175774718</v>
+        <v>1.166827625609829</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165072538705526</v>
+        <v>1.165088900075113</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166212615977509</v>
+        <v>1.166223416774006</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161135986289512</v>
+        <v>1.161134237773783</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161602174389465</v>
+        <v>1.16160103452974</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160946295438852</v>
+        <v>1.160945395765579</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162280822264546</v>
+        <v>1.162274628303727</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15982003848987</v>
+        <v>1.159817029099576</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412835849235</v>
+        <v>1.155412878052491</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.14842793164335</v>
+        <v>1.148429209915037</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143163617493046</v>
+        <v>1.143162211277615</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138020205615586</v>
+        <v>1.138013945287468</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130479039820297</v>
+        <v>1.130465279498792</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125405149118626</v>
+        <v>1.125388325863468</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130706879933593</v>
+        <v>1.130671060671378</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138127015681829</v>
+        <v>1.138076730227695</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144879710626426</v>
+        <v>1.144798808172236</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148550928219384</v>
+        <v>1.148457193670599</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148869916217209</v>
+        <v>1.14875834789278</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143230972834018</v>
+        <v>1.143115745397595</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141770687221095</v>
+        <v>1.141651015829021</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141791661069203</v>
+        <v>1.141666945809531</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152305121128532</v>
+        <v>1.152224328941543</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167125230479437</v>
+        <v>1.167070955387901</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167478292453564</v>
+        <v>1.167428459798063</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180807062206028</v>
+        <v>1.180799502369144</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190486688062088</v>
+        <v>1.1905274462824</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198471562842539</v>
+        <v>1.198521167593208</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.20957670228447</v>
+        <v>1.209652280943858</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.2049608144642</v>
+        <v>1.204993019577512</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205310223342579</v>
+        <v>1.205360655691084</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207698149593389</v>
+        <v>1.207798689437054</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21239219518099</v>
+        <v>1.212532064888542</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.218052596547141</v>
+        <v>1.218212798374359</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.217597007296509</v>
+        <v>1.217723732785842</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205482007887321</v>
+        <v>1.205593882156187</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197362749885717</v>
+        <v>1.197466968923163</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187414279035007</v>
+        <v>1.18749037903681</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179391250901314</v>
+        <v>1.179454558386331</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174584875025972</v>
+        <v>1.174632074512802</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171513705312283</v>
+        <v>1.171545543956795</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172228182846796</v>
+        <v>1.172282570694633</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168753591561213</v>
+        <v>1.168790289249487</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167370844936719</v>
+        <v>1.167413850667535</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.166822949090876</v>
+        <v>1.166889799103703</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.164938510685051</v>
+        <v>1.164996767253118</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157027607245663</v>
+        <v>1.157074339724521</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152955962094027</v>
+        <v>1.152211785420454</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.149177577626898</v>
+        <v>1.14858057028528</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144026426123888</v>
+        <v>1.143654986818301</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.139559058927149</v>
+        <v>1.139205783046171</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.135308951256966</v>
+        <v>1.135089188525328</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.129418726266183</v>
+        <v>1.129446877440189</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.121233057474158</v>
+        <v>1.121583988216169</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.111053326102876</v>
+        <v>1.111952893333789</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.100762096281367</v>
+        <v>1.102383498417108</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.088639001536621</v>
+        <v>1.090414146996728</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.064909869612106</v>
+        <v>1.071003190025722</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.058254185487455</v>
+        <v>1.065787166224829</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.073731752323389</v>
+        <v>1.077384991847833</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.093231752323389</v>
+        <v>1.091161958967128</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.186999433722475</v>
+        <v>1.187006972053676</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178589612829667</v>
+        <v>1.178601504433012</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177134915340641</v>
+        <v>1.177145121967435</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172575329644929</v>
+        <v>1.172589781774039</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171330483073311</v>
+        <v>1.171345634020183</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169298812542791</v>
+        <v>1.169314472480352</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166827625609829</v>
+        <v>1.166843426577289</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165088900075113</v>
+        <v>1.165104616032179</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166223416774006</v>
+        <v>1.166233806663791</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161134237773783</v>
+        <v>1.161132563606063</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.16160103452974</v>
+        <v>1.161599944491972</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160945395765579</v>
+        <v>1.160944536211731</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162274628303727</v>
+        <v>1.162268689743078</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159817029099576</v>
+        <v>1.15981414266752</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412878052491</v>
+        <v>1.155412925025685</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148429209915037</v>
+        <v>1.148430461860775</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143162211277615</v>
+        <v>1.143160901625402</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138013945287468</v>
+        <v>1.138007995130366</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130465279498792</v>
+        <v>1.13045211682712</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125388325863468</v>
+        <v>1.125372214362131</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130671060671378</v>
+        <v>1.130636713830823</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138076730227695</v>
+        <v>1.138028488450614</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144798808172236</v>
+        <v>1.144721082340193</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148457193670599</v>
+        <v>1.148367108655771</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14875834789278</v>
+        <v>1.148651096905762</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143115745397595</v>
+        <v>1.143004914183277</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141651015829021</v>
+        <v>1.141535850153778</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141666945809531</v>
+        <v>1.14154684971282</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152224328941543</v>
+        <v>1.152146487234984</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167070955387901</v>
+        <v>1.167018679907788</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167428459798063</v>
+        <v>1.16738042162252</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180799502369144</v>
+        <v>1.180792192775812</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.1905274462824</v>
+        <v>1.190566722594685</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198521167593208</v>
+        <v>1.198568951441064</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209652280943858</v>
+        <v>1.209724962438845</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.204993019577512</v>
+        <v>1.205023722859107</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205360655691084</v>
+        <v>1.205408840297487</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207798689437054</v>
+        <v>1.207895113748572</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.212532064888542</v>
+        <v>1.212666440278503</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.218212798374359</v>
+        <v>1.218366757005639</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.217723732785842</v>
+        <v>1.21784540251378</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205593882156187</v>
+        <v>1.20570136920938</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197466968923163</v>
+        <v>1.197567160384828</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18749037903681</v>
+        <v>1.187563638220967</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179454558386331</v>
+        <v>1.179515527451865</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174632074512802</v>
+        <v>1.174677538222161</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171545543956795</v>
+        <v>1.171576205930258</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172282570694633</v>
+        <v>1.172334917772005</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168790289249487</v>
+        <v>1.168825537970018</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167413850667535</v>
+        <v>1.167455152522215</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.166889799103703</v>
+        <v>1.166954077031881</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.164996767253118</v>
+        <v>1.165052756783309</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157074339724521</v>
+        <v>1.157119170345821</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152211785420454</v>
+        <v>1.1518729550685</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14858057028528</v>
+        <v>1.14842932749537</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143654986818301</v>
+        <v>1.143710016366743</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.139205783046171</v>
+        <v>1.139349167476384</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.135089188525328</v>
+        <v>1.135392542661438</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.129446877440189</v>
+        <v>1.130032080459716</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.121583988216169</v>
+        <v>1.122544435857311</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.111952893333789</v>
+        <v>1.113420410375183</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.102383498417108</v>
+        <v>1.1045136604465</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.090414146996728</v>
+        <v>1.092756326763996</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.071003190025722</v>
+        <v>1.076608710997963</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.065787166224829</v>
+        <v>1.072274066576845</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.077384991847833</v>
+        <v>1.081344079706402</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.091161958967128</v>
+        <v>1.100714190851584</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187006972053676</v>
+        <v>1.187021179241123</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178601504433012</v>
+        <v>1.178623923095632</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177145121967435</v>
+        <v>1.177164382087991</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172589781774039</v>
+        <v>1.172617045035693</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171345634020183</v>
+        <v>1.17137421359508</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169314472480352</v>
+        <v>1.169344010340703</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166843426577289</v>
+        <v>1.166873229556207</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165104616032179</v>
+        <v>1.165134258577484</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166233806663791</v>
+        <v>1.16625344379964</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161132563606063</v>
+        <v>1.161129420181668</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161599944491972</v>
+        <v>1.161597901445443</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160944536211731</v>
+        <v>1.16094292728373</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162268689743078</v>
+        <v>1.162257518238977</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15981414266752</v>
+        <v>1.159808709786412</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155412925025685</v>
+        <v>1.155413030708859</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148430461860775</v>
+        <v>1.148432887307767</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143160901625402</v>
+        <v>1.143158540868398</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.138007995130366</v>
+        <v>1.137996940796007</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13045211682712</v>
+        <v>1.130427436409289</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125372214362131</v>
+        <v>1.125341954172073</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130636713830823</v>
+        <v>1.130572089989632</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.138028488450614</v>
+        <v>1.137937659026556</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144721082340193</v>
+        <v>1.144574442768295</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148367108655771</v>
+        <v>1.148197070205641</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148651096905762</v>
+        <v>1.148448586921846</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.143004914183277</v>
+        <v>1.142795477630027</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141535850153778</v>
+        <v>1.14131806336475</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.14154684971282</v>
+        <v>1.141319535973599</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.152146487234984</v>
+        <v>1.151999037657766</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.167018679907788</v>
+        <v>1.166919704280192</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16738042162252</v>
+        <v>1.16728935839972</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180792192775812</v>
+        <v>1.180778276267524</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190566722594685</v>
+        <v>1.190641138583004</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198568951441064</v>
+        <v>1.198659440306372</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209724962438845</v>
+        <v>1.209862273581947</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205023722859107</v>
+        <v>1.20508101515928</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205408840297487</v>
+        <v>1.205499031593634</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.207895113748572</v>
+        <v>1.208076580440169</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.212666440278503</v>
+        <v>1.212919949021365</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.218366757005639</v>
+        <v>1.218657342155971</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.21784540251378</v>
+        <v>1.218074732219808</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20570136920938</v>
+        <v>1.205904168562356</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197567160384828</v>
+        <v>1.19775635250739</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187563638220967</v>
+        <v>1.187702240993864</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179515527451865</v>
+        <v>1.179630944872286</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174677538222161</v>
+        <v>1.17476362512103</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171576205930258</v>
+        <v>1.171634249669508</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172334917772005</v>
+        <v>1.172433929347394</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168825537970018</v>
+        <v>1.168892016151291</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167455152522215</v>
+        <v>1.167533031211838</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.166954077031881</v>
+        <v>1.167075485078937</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165052756783309</v>
+        <v>1.165158442107577</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157119170345821</v>
+        <v>1.157203568236036</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.1518729550685</v>
+        <v>1.150969790481418</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14842932749537</v>
+        <v>1.14783554483065</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143710016366743</v>
+        <v>1.14356439398263</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.139349167476384</v>
+        <v>1.139605946908638</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.135392542661438</v>
+        <v>1.136226061059512</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.130032080459716</v>
+        <v>1.131556496504313</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.122544435857311</v>
+        <v>1.1248170302082</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.113420410375183</v>
+        <v>1.116555388026699</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.1045136604465</v>
+        <v>1.108741038431919</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.092756326763996</v>
+        <v>1.098405398681586</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.076608710997963</v>
+        <v>1.086816571354566</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.072274066576845</v>
+        <v>1.083488574596602</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.081344079706402</v>
+        <v>1.089584221110466</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.100714190851584</v>
+        <v>1.102543491820535</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187021179241123</v>
+        <v>1.187027880891542</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178623923095632</v>
+        <v>1.178634501355064</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177164382087991</v>
+        <v>1.17717347817161</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172617045035693</v>
+        <v>1.172629917084772</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17137421359508</v>
+        <v>1.171387706231573</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169344010340703</v>
+        <v>1.169357954558682</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166873229556207</v>
+        <v>1.166887298526414</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165134258577484</v>
+        <v>1.165148251771158</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16625344379964</v>
+        <v>1.166262732057265</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161129420181668</v>
+        <v>1.161127942758851</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161597901445443</v>
+        <v>1.161596942848406</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16094292728373</v>
+        <v>1.16094217334311</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162257518238977</v>
+        <v>1.162252257935289</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159808709786412</v>
+        <v>1.159806150275628</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413030708859</v>
+        <v>1.155413088323508</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148432887307767</v>
+        <v>1.148434061308271</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143158540868398</v>
+        <v>1.143157476066445</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137996940796007</v>
+        <v>1.137991798923478</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130427436409289</v>
+        <v>1.130415852082828</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125341954172073</v>
+        <v>1.125327727753218</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130572089989632</v>
+        <v>1.130541655964433</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137937659026556</v>
+        <v>1.137894855583609</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144574442768295</v>
+        <v>1.144505203198669</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148197070205641</v>
+        <v>1.148116745501323</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148448586921846</v>
+        <v>1.148352891346012</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142795477630027</v>
+        <v>1.142696433729673</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.14131806336475</v>
+        <v>1.141214998530147</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141319535973599</v>
+        <v>1.141211870782751</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151999037657766</v>
+        <v>1.151929147165711</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166919704280192</v>
+        <v>1.166872810616186</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16728935839972</v>
+        <v>1.167246163663218</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180778276267524</v>
+        <v>1.18077164722622</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190641138583004</v>
+        <v>1.190676419734694</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198659440306372</v>
+        <v>1.198702320830344</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209862273581947</v>
+        <v>1.20992719425496</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20508101515928</v>
+        <v>1.205107779408607</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205499031593634</v>
+        <v>1.205541292334547</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208076580440169</v>
+        <v>1.20816205922964</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.212919949021365</v>
+        <v>1.213039645755078</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.218657342155971</v>
+        <v>1.218794603785849</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218074732219808</v>
+        <v>1.218182917068748</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205904168562356</v>
+        <v>1.205999929204522</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.19775635250739</v>
+        <v>1.197845759059449</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187702240993864</v>
+        <v>1.187767861784928</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179630944872286</v>
+        <v>1.179685619332654</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17476362512103</v>
+        <v>1.174804415965454</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171634249669508</v>
+        <v>1.171661745565802</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172433929347394</v>
+        <v>1.172480794462412</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168892016151291</v>
+        <v>1.16892339440083</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167533031211838</v>
+        <v>1.167569783548506</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167075485078937</v>
+        <v>1.167132873871225</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165158442107577</v>
+        <v>1.165208368462442</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157203568236036</v>
+        <v>1.157243335778174</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150969790481418</v>
+        <v>1.150497517272983</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14783554483065</v>
+        <v>1.147508578886156</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14356439398263</v>
+        <v>1.143461437585731</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.139605946908638</v>
+        <v>1.139812109428663</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.136226061059512</v>
+        <v>1.136773572908979</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.131556496504313</v>
+        <v>1.132475979071574</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.1248170302082</v>
+        <v>1.126079388935885</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.116555388026699</v>
+        <v>1.118148997466255</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.108741038431919</v>
+        <v>1.110862320660918</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.098405398681586</v>
+        <v>1.101211902962468</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.086816571354566</v>
+        <v>1.091237106558546</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.083488574596602</v>
+        <v>1.088375089639657</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.089584221110466</v>
+        <v>1.093433180078957</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.102543491820535</v>
+        <v>1.103988944962822</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187027880891542</v>
+        <v>1.187034334419423</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178634501355064</v>
+        <v>1.17864468989125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17717347817161</v>
+        <v>1.177182244091931</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172629917084772</v>
+        <v>1.172642319659235</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171387706231573</v>
+        <v>1.171400706216476</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169357954558682</v>
+        <v>1.169371389132277</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166887298526414</v>
+        <v>1.166900853047507</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165148251771158</v>
+        <v>1.16516173326164</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166262732057265</v>
+        <v>1.166271691713253</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161127942758851</v>
+        <v>1.161126523281808</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161596942848406</v>
+        <v>1.161596022846931</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16094217334311</v>
+        <v>1.160941450347148</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162252257935289</v>
+        <v>1.162247198088974</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159806150275628</v>
+        <v>1.159803687495734</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413088323508</v>
+        <v>1.155413148498084</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148434061308271</v>
+        <v>1.148435209945305</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143157476066445</v>
+        <v>1.143156480265559</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137991798923478</v>
+        <v>1.13798689145159</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130415852082828</v>
+        <v>1.130404731663804</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125327727753218</v>
+        <v>1.125314056973969</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130541655964433</v>
+        <v>1.13051237905765</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137894855583609</v>
+        <v>1.137853662542158</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144505203198669</v>
+        <v>1.14443848620746</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148116745501323</v>
+        <v>1.148039325137449</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148352891346012</v>
+        <v>1.148260636878714</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142696433729673</v>
+        <v>1.1426009059554</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141214998530147</v>
+        <v>1.141115549069274</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141211870782751</v>
+        <v>1.141107926866495</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151929147165711</v>
+        <v>1.151861640186915</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166872810616186</v>
+        <v>1.16682752830484</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167246163663218</v>
+        <v>1.167204423025349</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18077164722622</v>
+        <v>1.180765224056125</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190676419734694</v>
+        <v>1.190710502789186</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198702320830344</v>
+        <v>1.198743732561188</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.20992719425496</v>
+        <v>1.209989801844881</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205107779408607</v>
+        <v>1.205133393927742</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205541292334547</v>
+        <v>1.205581815679032</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20816205922964</v>
+        <v>1.208244298718668</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213039645755078</v>
+        <v>1.213154979040646</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.218794603785849</v>
+        <v>1.218926896968376</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218182917068748</v>
+        <v>1.218287099819547</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.205999929204522</v>
+        <v>1.206092202533569</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197845759059449</v>
+        <v>1.197931952623474</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187767861784928</v>
+        <v>1.187831197922483</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179685619332654</v>
+        <v>1.179738408991862</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174804415965454</v>
+        <v>1.174843807397685</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171661745565802</v>
+        <v>1.171688293776518</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172480794462412</v>
+        <v>1.172526021355632</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16892339440083</v>
+        <v>1.168953622335615</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167569783548506</v>
+        <v>1.167605184291006</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167132873871225</v>
+        <v>1.167188209719801</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165208368462442</v>
+        <v>1.165256490550771</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157243335778174</v>
+        <v>1.157281603538565</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150497517272983</v>
+        <v>1.150547219681889</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.147508578886156</v>
+        <v>1.147160292676583</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143461437585731</v>
+        <v>1.14347712585182</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.139812109428663</v>
+        <v>1.140138556300927</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.136773572908979</v>
+        <v>1.137550316251988</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.132475979071574</v>
+        <v>1.133862378085206</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.126079388935885</v>
+        <v>1.128248035774291</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.118148997466255</v>
+        <v>1.120827203629249</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.110862320660918</v>
+        <v>1.113780610919537</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.101211902962468</v>
+        <v>1.10505430857376</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.091237106558546</v>
+        <v>1.096918631248203</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.088375089639657</v>
+        <v>1.094745209282222</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.093433180078957</v>
+        <v>1.099440475760905</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.103988944962822</v>
+        <v>1.109366333149803</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B113">
+        <v>1.123878833149803</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187034334419423</v>
+        <v>1.187040553352588</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17864468989125</v>
+        <v>1.178654509846666</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177182244091931</v>
+        <v>1.17719069749154</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172642319659235</v>
+        <v>1.172654277968059</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171400706216476</v>
+        <v>1.17141324003236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169371389132277</v>
+        <v>1.169384341484608</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166900853047507</v>
+        <v>1.166913920814366</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.16516173326164</v>
+        <v>1.165174730597379</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166271691713253</v>
+        <v>1.166280339855759</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161126523281808</v>
+        <v>1.161125158417406</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161596022846931</v>
+        <v>1.161595139169944</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160941450347148</v>
+        <v>1.160940756445585</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162247198088974</v>
+        <v>1.162242327472794</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159803687495734</v>
+        <v>1.159801316076269</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413148498084</v>
+        <v>1.155413210834913</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148435209945305</v>
+        <v>1.148436333625218</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143156480265559</v>
+        <v>1.143155548132193</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.13798689145159</v>
+        <v>1.137982203289415</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130404731663804</v>
+        <v>1.130394048043055</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125314056973969</v>
+        <v>1.125300910056779</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.13051237905765</v>
+        <v>1.130484194744243</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137853662542158</v>
+        <v>1.137813991031311</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14443848620746</v>
+        <v>1.144374156793694</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.148039325137449</v>
+        <v>1.147964654989869</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148260636878714</v>
+        <v>1.148171642031301</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.1426009059554</v>
+        <v>1.142508711434982</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141115549069274</v>
+        <v>1.141019529419517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141107926866495</v>
+        <v>1.141007516374356</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151861640186915</v>
+        <v>1.151796397856641</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16682752830484</v>
+        <v>1.166783776169826</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167204423025349</v>
+        <v>1.16716406493431</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180765224056125</v>
+        <v>1.180758997334593</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190710502789186</v>
+        <v>1.190743447277913</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198743732561188</v>
+        <v>1.19878374919357</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.209989801844881</v>
+        <v>1.210050217452513</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205133393927742</v>
+        <v>1.205157929469088</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205581815679032</v>
+        <v>1.205620704872285</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208244298718668</v>
+        <v>1.208323478542852</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213154979040646</v>
+        <v>1.213266182354424</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.218926896968376</v>
+        <v>1.219054485404618</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218287099819547</v>
+        <v>1.218387497468864</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206092202533569</v>
+        <v>1.206181174562264</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.197931952623474</v>
+        <v>1.198015102134079</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187831197922483</v>
+        <v>1.187892365589995</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179738408991862</v>
+        <v>1.179789408781713</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174843807397685</v>
+        <v>1.174881869778071</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171688293776518</v>
+        <v>1.171713942162409</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172526021355632</v>
+        <v>1.17256969392963</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168953622335615</v>
+        <v>1.168982761638328</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167605184291006</v>
+        <v>1.167639306146732</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167188209719801</v>
+        <v>1.167241600287701</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165256490550771</v>
+        <v>1.165302904085835</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157281603538565</v>
+        <v>1.157318454114432</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150547219681889</v>
+        <v>1.150595261815729</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.147160292676583</v>
+        <v>1.146748506928292</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14347712585182</v>
+        <v>1.14336539052563</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140138556300927</v>
+        <v>1.140299132201149</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.137550316251988</v>
+        <v>1.138067064879723</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.133862378085206</v>
+        <v>1.134888995377369</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.128248035774291</v>
+        <v>1.129902829305816</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.120827203629249</v>
+        <v>1.122884865890347</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.113780610919537</v>
+        <v>1.116042986952534</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.10505430857376</v>
+        <v>1.108077710016532</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.096918631248203</v>
+        <v>1.101259344732201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.094745209282222</v>
+        <v>1.099549681921429</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.099440475760905</v>
+        <v>1.103837791700732</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.109366333149803</v>
+        <v>1.112932353610974</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.123878833149803</v>
+        <v>1.127444853610974</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14336539052563</v>
+        <v>1.143363734724256</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140299132201149</v>
+        <v>1.140341489213901</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.138067064879723</v>
+        <v>1.138105536335746</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.134888995377369</v>
+        <v>1.134832070883955</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.129902829305816</v>
+        <v>1.129697479218845</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.122884865890347</v>
+        <v>1.122690684744178</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.116042986952534</v>
+        <v>1.115897867655237</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.108077710016532</v>
+        <v>1.107788742134036</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.101259344732201</v>
+        <v>1.100967467828847</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.099549681921429</v>
+        <v>1.099306566297492</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.103837791700732</v>
+        <v>1.103667681648288</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.112932353610974</v>
+        <v>1.112777572674689</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.127444853610974</v>
+        <v>1.127290072674689</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143363734724256</v>
+        <v>1.143365507476171</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140341489213901</v>
+        <v>1.140404438803981</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.138105536335746</v>
+        <v>1.138256413586969</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.134832070883955</v>
+        <v>1.13498766252894</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.129697479218845</v>
+        <v>1.129885195123493</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.122690684744178</v>
+        <v>1.122867737682813</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.115897867655237</v>
+        <v>1.116247287960856</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.107788742134036</v>
+        <v>1.108050854544418</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.100967467828847</v>
+        <v>1.101191977033431</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.099306566297492</v>
+        <v>1.099443506464435</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.103667681648288</v>
+        <v>1.103805813261249</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.112777572674689</v>
+        <v>1.112892510403974</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.127290072674689</v>
+        <v>1.127405010403975</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187040553352588</v>
+        <v>1.187046550253117</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178654509846666</v>
+        <v>1.178663980862005</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17719069749154</v>
+        <v>1.177198854778938</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172654277968059</v>
+        <v>1.172665815448185</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17141324003236</v>
+        <v>1.171425332298191</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169384341484608</v>
+        <v>1.169396837107094</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166913920814366</v>
+        <v>1.166926527570092</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165174730597379</v>
+        <v>1.165187269385263</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166280339855759</v>
+        <v>1.16628869241163</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161125158417406</v>
+        <v>1.16112384508266</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161595139169944</v>
+        <v>1.161594289720238</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160940756445585</v>
+        <v>1.160940089931748</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162242327472794</v>
+        <v>1.162237635681425</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159801316076269</v>
+        <v>1.159799031036332</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413210834913</v>
+        <v>1.155413274983264</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148436333625218</v>
+        <v>1.148437432794242</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143155548132193</v>
+        <v>1.143154674822729</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137982203289415</v>
+        <v>1.137977720581876</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130394048043055</v>
+        <v>1.130383776169902</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125300910056779</v>
+        <v>1.125288257592153</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130484194744243</v>
+        <v>1.130457043193503</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137813991031311</v>
+        <v>1.137775758578795</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144374156793694</v>
+        <v>1.144312089393687</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147964654989869</v>
+        <v>1.14789259160818</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148171642031301</v>
+        <v>1.14808573779838</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142508711434982</v>
+        <v>1.142419679684038</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.141019529419517</v>
+        <v>1.140926766404843</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.141007516374356</v>
+        <v>1.140910463761302</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151796397856641</v>
+        <v>1.151733309011351</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166783776169826</v>
+        <v>1.166741478364657</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16716406493431</v>
+        <v>1.167125022410154</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180758997334593</v>
+        <v>1.180752958206353</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190743447277913</v>
+        <v>1.190775308886343</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19878374919357</v>
+        <v>1.198822439608059</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210050217452513</v>
+        <v>1.210108553893775</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205157929469088</v>
+        <v>1.205181451200747</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205620704872285</v>
+        <v>1.205658055244442</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208323478542852</v>
+        <v>1.208399765368535</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213266182354424</v>
+        <v>1.213373472866822</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219054485404618</v>
+        <v>1.219177614547063</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218387497468864</v>
+        <v>1.218484311676053</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206181174562264</v>
+        <v>1.206267018379936</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198015102134079</v>
+        <v>1.198095364970938</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187892365589995</v>
+        <v>1.187951473302266</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179789408781713</v>
+        <v>1.179838707425992</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174881869778071</v>
+        <v>1.17491866885823</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171713942162409</v>
+        <v>1.171738735436191</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17256969392963</v>
+        <v>1.172611890489937</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.168982761638328</v>
+        <v>1.169010869688676</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167639306146732</v>
+        <v>1.167672216734155</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167241600287701</v>
+        <v>1.167293145877481</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165302904085835</v>
+        <v>1.165347698153117</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157318454114432</v>
+        <v>1.157353964192606</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150595261815729</v>
+        <v>1.150641723944168</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146748506928292</v>
+        <v>1.146453228710112</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143365507476171</v>
+        <v>1.143366548505757</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140404438803981</v>
+        <v>1.140707240260905</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.138256413586969</v>
+        <v>1.138990580246328</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.13498766252894</v>
+        <v>1.136201637390315</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.129885195123493</v>
+        <v>1.131711252852733</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.122867737682813</v>
+        <v>1.125048093209254</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.116247287960856</v>
+        <v>1.118764589957834</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.108050854544418</v>
+        <v>1.111170666812969</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.101191977033431</v>
+        <v>1.105390512777175</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.099443506464435</v>
+        <v>1.103928023053754</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.103805813261249</v>
+        <v>1.107928024132953</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.112892510403974</v>
+        <v>1.116275360732261</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.127405010403975</v>
+        <v>1.135042062425862</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187046550253117</v>
+        <v>1.187052336802011</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178663980862005</v>
+        <v>1.178673121207163</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177198854778938</v>
+        <v>1.177206731234506</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172665815448185</v>
+        <v>1.172676953917443</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171425332298191</v>
+        <v>1.171437005930336</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169396837107094</v>
+        <v>1.169408899726507</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166926527570092</v>
+        <v>1.166938697274881</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165187269385263</v>
+        <v>1.165199373458618</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16628869241163</v>
+        <v>1.166296764243114</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.16112384508266</v>
+        <v>1.161122580421752</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161594289720238</v>
+        <v>1.161593472558218</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160940089931748</v>
+        <v>1.160939449228969</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162237635681425</v>
+        <v>1.162233113057693</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159799031036332</v>
+        <v>1.15979682774995</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413274983264</v>
+        <v>1.155413340633598</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148437432794242</v>
+        <v>1.148438507929031</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143154674822729</v>
+        <v>1.143153855931229</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137977720581876</v>
+        <v>1.137973430588084</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130383776169902</v>
+        <v>1.130373892861464</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125288257592153</v>
+        <v>1.125276072322891</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130457043193503</v>
+        <v>1.130430868851055</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137775758578795</v>
+        <v>1.137738888547136</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144312089393687</v>
+        <v>1.144252167072878</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14789259160818</v>
+        <v>1.147823001311058</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14808573779838</v>
+        <v>1.148002766607744</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142419679684038</v>
+        <v>1.142333651581299</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140926766404843</v>
+        <v>1.140837098227894</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140910463761302</v>
+        <v>1.140816604807807</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151733309011351</v>
+        <v>1.151672269581447</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166741478364657</v>
+        <v>1.166700563945101</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167125022410154</v>
+        <v>1.167087232689503</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180752958206353</v>
+        <v>1.180747098341137</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190775308886343</v>
+        <v>1.190806139756672</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198822439608059</v>
+        <v>1.198859868254923</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210108553893775</v>
+        <v>1.210164916394344</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205181451200747</v>
+        <v>1.205204019239058</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205658055244442</v>
+        <v>1.205693954946621</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208399765368535</v>
+        <v>1.20847331403654</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213373472866822</v>
+        <v>1.213477052836339</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219177614547063</v>
+        <v>1.219296513143737</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218484311676053</v>
+        <v>1.218577730088604</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206267018379936</v>
+        <v>1.206349895249257</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198095364970938</v>
+        <v>1.198172887922838</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.187951473302266</v>
+        <v>1.188008622520979</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179838707425992</v>
+        <v>1.179886387934367</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17491866885823</v>
+        <v>1.174954266149741</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171738735436191</v>
+        <v>1.171762715415328</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172611890489937</v>
+        <v>1.172652684200985</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169010869688676</v>
+        <v>1.169037999929663</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167672216734155</v>
+        <v>1.167703979017538</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167293145877481</v>
+        <v>1.167342940046401</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165347698153117</v>
+        <v>1.165390955772163</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157353964192606</v>
+        <v>1.157388205065119</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150641723944168</v>
+        <v>1.150686681355391</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146453228710112</v>
+        <v>1.145973866391314</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143366548505757</v>
+        <v>1.143100543287058</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140707240260905</v>
+        <v>1.140622746618628</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.138990580246328</v>
+        <v>1.139213322830102</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.136201637390315</v>
+        <v>1.136865277189892</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.131711252852733</v>
+        <v>1.132940519958409</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.125048093209254</v>
+        <v>1.126540664363583</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.118764589957834</v>
+        <v>1.120316821391641</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.111170666812969</v>
+        <v>1.113346430422266</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.105390512777175</v>
+        <v>1.108221648259074</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.103928023053754</v>
+        <v>1.106887402437923</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.107928024132953</v>
+        <v>1.11034324482788</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.116275360732261</v>
+        <v>1.117732500818839</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.135042062425862</v>
+        <v>1.132670028634974</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143100543287058</v>
+        <v>1.143100643286097</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140622746618628</v>
+        <v>1.140714193365832</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139213322830102</v>
+        <v>1.139377109207916</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.136865277189892</v>
+        <v>1.136950191905275</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.132940519958409</v>
+        <v>1.132925255992838</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.126540664363583</v>
+        <v>1.126525930437988</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.120316821391641</v>
+        <v>1.120489899453067</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.113346430422266</v>
+        <v>1.113323498898987</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.108221648259074</v>
+        <v>1.108166096825136</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.106887402437923</v>
+        <v>1.10680113170782</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.11034324482788</v>
+        <v>1.110317536796988</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.117732500818839</v>
+        <v>1.117701759801627</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.132670028634974</v>
+        <v>1.132597101691759</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187052336802011</v>
+        <v>1.187057923875099</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178673121207163</v>
+        <v>1.178681947898753</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177206731234506</v>
+        <v>1.177214341105754</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172676953917443</v>
+        <v>1.172687713711914</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171437005930336</v>
+        <v>1.17144828228716</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169408899726507</v>
+        <v>1.16942055145499</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166938697274881</v>
+        <v>1.166950452257664</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165199373458618</v>
+        <v>1.165211065028058</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166296764243114</v>
+        <v>1.166304569235095</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161122580421752</v>
+        <v>1.161121361785536</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161593472558218</v>
+        <v>1.161592685887424</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160939449228969</v>
+        <v>1.160938832878502</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162233113057693</v>
+        <v>1.162228750626595</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15979682774995</v>
+        <v>1.159794701915079</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413340633598</v>
+        <v>1.155413407512583</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148438507929031</v>
+        <v>1.148439559528792</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143153855931229</v>
+        <v>1.143153087443518</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137973430588084</v>
+        <v>1.137969321573577</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130373892861464</v>
+        <v>1.130364376632677</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125276072322891</v>
+        <v>1.125264328951409</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130430868851055</v>
+        <v>1.130405620064629</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137738888547136</v>
+        <v>1.137703309628239</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144252167072878</v>
+        <v>1.14419428079907</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147823001311058</v>
+        <v>1.147755759371697</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.148002766607744</v>
+        <v>1.147922581374038</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142333651581299</v>
+        <v>1.142250478443247</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140837098227894</v>
+        <v>1.140750373558012</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140816604807807</v>
+        <v>1.140725785730864</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151672269581447</v>
+        <v>1.15161318203989</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166700563945101</v>
+        <v>1.166660966481839</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167087232689503</v>
+        <v>1.167050636902448</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180747098341137</v>
+        <v>1.180741409895097</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190806139756672</v>
+        <v>1.19083598876268</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198859868254923</v>
+        <v>1.198896095502089</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210164916394344</v>
+        <v>1.210219403215748</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205204019239058</v>
+        <v>1.205225689122022</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205693954946621</v>
+        <v>1.205728485607083</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20847331403654</v>
+        <v>1.208544268587549</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213477052836339</v>
+        <v>1.213577110863489</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219296513143737</v>
+        <v>1.219411394628906</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218577730088604</v>
+        <v>1.218667927533074</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206349895249257</v>
+        <v>1.206429955593846</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198172887922838</v>
+        <v>1.198247808057531</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188008622520979</v>
+        <v>1.188063908212615</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179886387934367</v>
+        <v>1.179932528050436</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174954266149741</v>
+        <v>1.174988719258262</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171762715415328</v>
+        <v>1.171785921251028</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172652684200985</v>
+        <v>1.172692143498513</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169037999929663</v>
+        <v>1.169064202197337</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167703979017538</v>
+        <v>1.167734651698126</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167342940046401</v>
+        <v>1.167391070161255</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165390955772163</v>
+        <v>1.165432754402448</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157388205065119</v>
+        <v>1.157421243092116</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150686681355391</v>
+        <v>1.150730204726747</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145973866391314</v>
+        <v>1.145537296364407</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143100643286097</v>
+        <v>1.142818176255676</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140714193365832</v>
+        <v>1.140634740995849</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139377109207916</v>
+        <v>1.139498687188615</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.136950191905275</v>
+        <v>1.137233073217191</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.132925255992838</v>
+        <v>1.133221951762631</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.126525930437988</v>
+        <v>1.126936329762851</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.120489899453067</v>
+        <v>1.120934596407884</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.113323498898987</v>
+        <v>1.113961923970403</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.108166096825136</v>
+        <v>1.108822872060768</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.10680113170782</v>
+        <v>1.107286965438652</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.110317536796988</v>
+        <v>1.110112298136568</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.117701759801627</v>
+        <v>1.116211178907018</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.132597101691759</v>
+        <v>1.125746825122423</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187057923875099</v>
+        <v>1.187068539473654</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178681947898753</v>
+        <v>1.178698722744542</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177214341105754</v>
+        <v>1.17722881342714</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172687713711914</v>
+        <v>1.172708171941665</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17144828228716</v>
+        <v>1.171469721586245</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16942055145499</v>
+        <v>1.169442703411157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166950452257664</v>
+        <v>1.166972800021738</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165211065028058</v>
+        <v>1.165233292185067</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166304569235095</v>
+        <v>1.166319429818715</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161121361785536</v>
+        <v>1.161119052915937</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161592685887424</v>
+        <v>1.16159119747328</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160938832878502</v>
+        <v>1.160937667925743</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162228750626595</v>
+        <v>1.162220473504513</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159794701915079</v>
+        <v>1.15979066684722</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413407512583</v>
+        <v>1.155413544018773</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148439559528792</v>
+        <v>1.148441594194643</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143153087443518</v>
+        <v>1.143151687343724</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137969321573577</v>
+        <v>1.137961604013227</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130364376632677</v>
+        <v>1.130346367067865</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125264328951409</v>
+        <v>1.12524207549299</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130405620064629</v>
+        <v>1.130357710080939</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137703309628239</v>
+        <v>1.137635763865127</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14419428079907</v>
+        <v>1.144084215911058</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147755759371697</v>
+        <v>1.147627862094311</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147922581374038</v>
+        <v>1.147770027826126</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142250478443247</v>
+        <v>1.142092149572806</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140750373558012</v>
+        <v>1.14058519686833</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140725785730864</v>
+        <v>1.140552699484859</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15161318203989</v>
+        <v>1.151500502263473</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166660966481839</v>
+        <v>1.16658547720497</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167050636902448</v>
+        <v>1.166980809377619</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180741409895097</v>
+        <v>1.180730518109177</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19083598876268</v>
+        <v>1.190892921811937</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198896095502089</v>
+        <v>1.198965168724222</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210219403215748</v>
+        <v>1.210323111384085</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205225689122022</v>
+        <v>1.205266536167525</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205728485607083</v>
+        <v>1.205793737156843</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208544268587549</v>
+        <v>1.208678922934398</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213577110863489</v>
+        <v>1.213767353872405</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219411394628906</v>
+        <v>1.219629890840408</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218667927533074</v>
+        <v>1.218839301046039</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206429955593846</v>
+        <v>1.20658217946696</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198247808057531</v>
+        <v>1.198390344183501</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188063908212615</v>
+        <v>1.188169239396864</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179932528050436</v>
+        <v>1.180020474155015</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174988719258262</v>
+        <v>1.175054405611114</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171785921251028</v>
+        <v>1.171830154993293</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172692143498513</v>
+        <v>1.172767311159471</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169064202197337</v>
+        <v>1.169114005877572</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167734651698126</v>
+        <v>1.167792943822353</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167391070161255</v>
+        <v>1.167482659703276</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165432754402448</v>
+        <v>1.165512259427683</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157421243092116</v>
+        <v>1.157483953847761</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150730204726747</v>
+        <v>1.150813211011094</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145537296364407</v>
+        <v>1.145268452031714</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.142818176255676</v>
+        <v>1.142389452935191</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140634740995849</v>
+        <v>1.140436889521832</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139498687188615</v>
+        <v>1.139521526646933</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.137233073217191</v>
+        <v>1.137503806949922</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.133221951762631</v>
+        <v>1.133618015608727</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.126936329762851</v>
+        <v>1.127622391712546</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.120934596407884</v>
+        <v>1.12182817967836</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.113961923970403</v>
+        <v>1.11543595495907</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.108822872060768</v>
+        <v>1.110649248789047</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.107286965438652</v>
+        <v>1.108925892756085</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.110112298136568</v>
+        <v>1.110892076014933</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.116211178907018</v>
+        <v>1.115338912723903</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.125746825122423</v>
+        <v>1.120489154458885</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B114">
+        <v>1.108604902867937</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187068539473654</v>
+        <v>1.187057923875099</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178698722744542</v>
+        <v>1.178681947898753</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17722881342714</v>
+        <v>1.177214341105754</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172708171941665</v>
+        <v>1.172687713711914</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171469721586245</v>
+        <v>1.17144828228716</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169442703411157</v>
+        <v>1.16942055145499</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166972800021738</v>
+        <v>1.166950452257664</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165233292185067</v>
+        <v>1.165211065028058</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166319429818715</v>
+        <v>1.166304569235095</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161119052915937</v>
+        <v>1.161121361785536</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.16159119747328</v>
+        <v>1.161592685887424</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160937667925743</v>
+        <v>1.160938832878502</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162220473504513</v>
+        <v>1.162228750626595</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15979066684722</v>
+        <v>1.159794701915079</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413544018773</v>
+        <v>1.155413407512583</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148441594194643</v>
+        <v>1.148439559528792</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143151687343724</v>
+        <v>1.143153087443518</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137961604013227</v>
+        <v>1.137969321573577</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130346367067865</v>
+        <v>1.130364376632677</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12524207549299</v>
+        <v>1.125264328951409</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130357710080939</v>
+        <v>1.130405620064629</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137635763865127</v>
+        <v>1.137703309628239</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144084215911058</v>
+        <v>1.14419428079907</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147627862094311</v>
+        <v>1.147755759371697</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147770027826126</v>
+        <v>1.147922581374038</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142092149572806</v>
+        <v>1.142250478443247</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.14058519686833</v>
+        <v>1.140750373558012</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140552699484859</v>
+        <v>1.140725785730864</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151500502263473</v>
+        <v>1.15161318203989</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16658547720497</v>
+        <v>1.166660966481839</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166980809377619</v>
+        <v>1.167050636902448</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180730518109177</v>
+        <v>1.180741409895097</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190892921811937</v>
+        <v>1.19083598876268</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198965168724222</v>
+        <v>1.198896095502089</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210323111384085</v>
+        <v>1.210219403215748</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205266536167525</v>
+        <v>1.205225689122022</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205793737156843</v>
+        <v>1.205728485607083</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208678922934398</v>
+        <v>1.208544268587549</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213767353872405</v>
+        <v>1.213577110863489</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219629890840408</v>
+        <v>1.219411394628906</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218839301046039</v>
+        <v>1.218667927533074</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20658217946696</v>
+        <v>1.206429955593846</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198390344183501</v>
+        <v>1.198247808057531</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188169239396864</v>
+        <v>1.188063908212615</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180020474155015</v>
+        <v>1.179932528050436</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175054405611114</v>
+        <v>1.174988719258262</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171830154993293</v>
+        <v>1.171785921251028</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172767311159471</v>
+        <v>1.172692143498513</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169114005877572</v>
+        <v>1.169064202197337</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167792943822353</v>
+        <v>1.167734651698126</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167482659703276</v>
+        <v>1.167391070161255</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165512259427683</v>
+        <v>1.165432754402448</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157483953847761</v>
+        <v>1.157421243092116</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150813211011094</v>
+        <v>1.150730204726747</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145268452031714</v>
+        <v>1.146014769547723</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.142389452935191</v>
+        <v>1.14277495992793</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140436889521832</v>
+        <v>1.140388050717654</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139521526646933</v>
+        <v>1.139164537492519</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.137503806949922</v>
+        <v>1.137054430331377</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.133618015608727</v>
+        <v>1.133361735732241</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.127622391712546</v>
+        <v>1.127280944024749</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.12182817967836</v>
+        <v>1.121153126258548</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.11543595495907</v>
+        <v>1.114400268816235</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.110649248789047</v>
+        <v>1.109506638124726</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.108925892756085</v>
+        <v>1.107808261704239</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.110892076014933</v>
+        <v>1.110622341028561</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.115338912723903</v>
+        <v>1.116766546704789</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.120489154458885</v>
+        <v>1.126841438648622</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.108604902867937</v>
+        <v>1.112328938648622</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140388050717654</v>
+        <v>1.140385605254104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139164537492519</v>
+        <v>1.139163525021443</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.137054430331377</v>
+        <v>1.137055745890066</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.133361735732241</v>
+        <v>1.133214797774227</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.127280944024749</v>
+        <v>1.127002092673068</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.121153126258548</v>
+        <v>1.120951474985584</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.114400268816235</v>
+        <v>1.114250994342502</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.109506638124726</v>
+        <v>1.109380136776757</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.107808261704239</v>
+        <v>1.107754462730321</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.110622341028561</v>
+        <v>1.110541536829695</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.116766546704789</v>
+        <v>1.116698094488943</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.126841438648622</v>
+        <v>1.126738917043312</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.112328938648622</v>
+        <v>1.112226417043311</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187057923875099</v>
+        <v>1.187063321611229</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178681947898753</v>
+        <v>1.178690476805734</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177214341105754</v>
+        <v>1.177221697693082</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172687713711914</v>
+        <v>1.172698113809558</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17144828228716</v>
+        <v>1.171459181299157</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16942055145499</v>
+        <v>1.169431812925036</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166950452257664</v>
+        <v>1.166961813352537</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165211065028058</v>
+        <v>1.165222364817214</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166304569235095</v>
+        <v>1.166312120373916</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161121361785536</v>
+        <v>1.161120186713217</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161592685887424</v>
+        <v>1.161591928041627</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160938832878502</v>
+        <v>1.160938239528767</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162228750626595</v>
+        <v>1.16222454003619</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159794701915079</v>
+        <v>1.15979264952578</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413407512583</v>
+        <v>1.15541347537876</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148439559528792</v>
+        <v>1.148440588108735</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143153087443518</v>
+        <v>1.143152365696752</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137969321573577</v>
+        <v>1.137965382714645</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130364376632677</v>
+        <v>1.130355207544471</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125264328951409</v>
+        <v>1.125253003967347</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130405620064629</v>
+        <v>1.130381248748336</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137703309628239</v>
+        <v>1.137668955389454</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14419428079907</v>
+        <v>1.144138328787716</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147755759371697</v>
+        <v>1.147690749283108</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147922581374038</v>
+        <v>1.147845044644435</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142250478443247</v>
+        <v>1.142170021187143</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140750373558012</v>
+        <v>1.140666450704838</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140725785730864</v>
+        <v>1.140637862376435</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15161318203989</v>
+        <v>1.151555954900887</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166660966481839</v>
+        <v>1.166622623709023</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167050636902448</v>
+        <v>1.167015179778355</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180741409895097</v>
+        <v>1.180735885475618</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19083598876268</v>
+        <v>1.190864901759654</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198896095502089</v>
+        <v>1.198931177951069</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210219403215748</v>
+        <v>1.210272106220649</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205225689122022</v>
+        <v>1.205246512231062</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205728485607083</v>
+        <v>1.205761722917357</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208544268587549</v>
+        <v>1.20861276318311</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213577110863489</v>
+        <v>1.213673823020729</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219411394628906</v>
+        <v>1.219522458377782</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218667927533074</v>
+        <v>1.218755067087093</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206429955593846</v>
+        <v>1.206507339889084</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198247808057531</v>
+        <v>1.198320253507888</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188063908212615</v>
+        <v>1.188117419354858</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179932528050436</v>
+        <v>1.179977200658741</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.174988719258262</v>
+        <v>1.17502208218676</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171785921251028</v>
+        <v>1.171808389636013</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172692143498513</v>
+        <v>1.172730332463167</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169064202197337</v>
+        <v>1.169089523018154</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167734651698126</v>
+        <v>1.167764289566777</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167391070161255</v>
+        <v>1.167437617899595</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165432754402448</v>
+        <v>1.165473166399618</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157421243092116</v>
+        <v>1.157453140118234</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150730204726747</v>
+        <v>1.150772360463852</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146014769547723</v>
+        <v>1.146054456300762</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14277495992793</v>
+        <v>1.142553876780243</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140385605254104</v>
+        <v>1.140255253931804</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139163525021443</v>
+        <v>1.139208276438863</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.137055745890066</v>
+        <v>1.137350822498674</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.133214797774227</v>
+        <v>1.133614228375613</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.127002092673068</v>
+        <v>1.127603326482113</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.120951474985584</v>
+        <v>1.121735605288147</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.114250994342502</v>
+        <v>1.115313473483041</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.109380136776757</v>
+        <v>1.110723784493537</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.107754462730321</v>
+        <v>1.108931384793967</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.110541536829695</v>
+        <v>1.111209054436478</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.116698094488943</v>
+        <v>1.11644819863772</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.126738917043312</v>
+        <v>1.123956118782587</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.112226417043311</v>
+        <v>1.109443618782587</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187063321611229</v>
+        <v>1.187073586305369</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178690476805734</v>
+        <v>1.17870669956491</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177221697693082</v>
+        <v>1.177235699938737</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172698113809558</v>
+        <v>1.172717904693518</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171459181299157</v>
+        <v>1.171479920563696</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169431812925036</v>
+        <v>1.169453240939748</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166961813352537</v>
+        <v>1.16698343046668</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165222364817214</v>
+        <v>1.165243865236402</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166312120373916</v>
+        <v>1.166326508966089</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161120186713217</v>
+        <v>1.161117958262051</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161591928041627</v>
+        <v>1.161590492743179</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160938239528767</v>
+        <v>1.160937116904364</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16222454003619</v>
+        <v>1.162216543771821</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15979264952578</v>
+        <v>1.159788750393154</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541347537876</v>
+        <v>1.155413613244074</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148440588108735</v>
+        <v>1.148442578318367</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143152365696752</v>
+        <v>1.143151049321292</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137965382714645</v>
+        <v>1.137957976221035</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130355207544471</v>
+        <v>1.130337837962101</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125253003967347</v>
+        <v>1.125231523144428</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130381248748336</v>
+        <v>1.130334962234154</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137668955389454</v>
+        <v>1.137603677188422</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144138328787716</v>
+        <v>1.144031853164002</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147690749283108</v>
+        <v>1.147566995809612</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147845044644435</v>
+        <v>1.147697410486643</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142170021187143</v>
+        <v>1.142016741514712</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140666450704838</v>
+        <v>1.140506487457172</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140637862376435</v>
+        <v>1.140470170021764</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151555954900887</v>
+        <v>1.151446743395438</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166622623709023</v>
+        <v>1.166549472101612</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.167015179778355</v>
+        <v>1.166947476846809</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180735885475618</v>
+        <v>1.180725301211944</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190864901759654</v>
+        <v>1.1909200894004</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198931177951069</v>
+        <v>1.198998117726306</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210272106220649</v>
+        <v>1.210372499256581</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205246512231062</v>
+        <v>1.205285805089425</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205761722917357</v>
+        <v>1.205824593663231</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20861276318311</v>
+        <v>1.208742864649294</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213673823020729</v>
+        <v>1.213857857396969</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219522458377782</v>
+        <v>1.219733866568029</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218755067087093</v>
+        <v>1.21892077179618</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206507339889084</v>
+        <v>1.206654597244434</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198320253507888</v>
+        <v>1.198458192415819</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188117419354858</v>
+        <v>1.188219446678179</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.179977200658741</v>
+        <v>1.180062412783426</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17502208218676</v>
+        <v>1.175085737130971</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171808389636013</v>
+        <v>1.171851249647931</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172730332463167</v>
+        <v>1.172803135943808</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169089523018154</v>
+        <v>1.169137691463077</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167764289566777</v>
+        <v>1.167820662359696</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167437617899595</v>
+        <v>1.167526267189485</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165473166399618</v>
+        <v>1.165550096832028</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157453140118234</v>
+        <v>1.157513738183245</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150772360463852</v>
+        <v>1.150852815136208</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146054456300762</v>
+        <v>1.14530652341787</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.142553876780243</v>
+        <v>1.142201200343397</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140255253931804</v>
+        <v>1.140298376329449</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139208276438863</v>
+        <v>1.139513418553302</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.137350822498674</v>
+        <v>1.137562274924913</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.133614228375613</v>
+        <v>1.133753190708147</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.127603326482113</v>
+        <v>1.127883514918467</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.121735605288147</v>
+        <v>1.122220928685634</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.115313473483041</v>
+        <v>1.116113726967734</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.110723784493537</v>
+        <v>1.1116389342351</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.108931384793967</v>
+        <v>1.10983181963441</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.111209054436478</v>
+        <v>1.111508423822237</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.11644819863772</v>
+        <v>1.11536223161751</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.123956118782587</v>
+        <v>1.11943289702222</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.109443618782587</v>
+        <v>1.109806755887536</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187073586305369</v>
+        <v>1.187068539473654</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17870669956491</v>
+        <v>1.178698722744542</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177235699938737</v>
+        <v>1.17722881342714</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172717904693518</v>
+        <v>1.172708171941665</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171479920563696</v>
+        <v>1.171469721586245</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169453240939748</v>
+        <v>1.169442703411157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.16698343046668</v>
+        <v>1.166972800021738</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165243865236402</v>
+        <v>1.165233292185067</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166326508966089</v>
+        <v>1.166319429818715</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161117958262051</v>
+        <v>1.161119052915937</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161590492743179</v>
+        <v>1.16159119747328</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160937116904364</v>
+        <v>1.160937667925743</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162216543771821</v>
+        <v>1.162220473504513</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159788750393154</v>
+        <v>1.15979066684722</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413613244074</v>
+        <v>1.155413544018773</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148442578318367</v>
+        <v>1.148441594194643</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143151049321292</v>
+        <v>1.143151687343724</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137957976221035</v>
+        <v>1.137961604013227</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130337837962101</v>
+        <v>1.130346367067865</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125231523144428</v>
+        <v>1.12524207549299</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130334962234154</v>
+        <v>1.130357710080939</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137603677188422</v>
+        <v>1.137635763865127</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144031853164002</v>
+        <v>1.144084215911058</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147566995809612</v>
+        <v>1.147627862094311</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147697410486643</v>
+        <v>1.147770027826126</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142016741514712</v>
+        <v>1.142092149572806</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140506487457172</v>
+        <v>1.14058519686833</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140470170021764</v>
+        <v>1.140552699484859</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151446743395438</v>
+        <v>1.151500502263473</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166549472101612</v>
+        <v>1.16658547720497</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166947476846809</v>
+        <v>1.166980809377619</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180725301211944</v>
+        <v>1.180730518109177</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.1909200894004</v>
+        <v>1.190892921811937</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198998117726306</v>
+        <v>1.198965168724222</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210372499256581</v>
+        <v>1.210323111384085</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205285805089425</v>
+        <v>1.205266536167525</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205824593663231</v>
+        <v>1.205793737156843</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208742864649294</v>
+        <v>1.208678922934398</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213857857396969</v>
+        <v>1.213767353872405</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219733866568029</v>
+        <v>1.219629890840408</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.21892077179618</v>
+        <v>1.218839301046039</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206654597244434</v>
+        <v>1.20658217946696</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198458192415819</v>
+        <v>1.198390344183501</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188219446678179</v>
+        <v>1.188169239396864</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180062412783426</v>
+        <v>1.180020474155015</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175085737130971</v>
+        <v>1.175054405611114</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171851249647931</v>
+        <v>1.171830154993293</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172803135943808</v>
+        <v>1.172767311159471</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169137691463077</v>
+        <v>1.169114005877572</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167820662359696</v>
+        <v>1.167792943822353</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167526267189485</v>
+        <v>1.167482659703276</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165550096832028</v>
+        <v>1.165512259427683</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157513738183245</v>
+        <v>1.157483953847761</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150852815136208</v>
+        <v>1.150813211011094</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14530652341787</v>
+        <v>1.146092978717539</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.142201200343397</v>
+        <v>1.142755201450033</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140298376329449</v>
+        <v>1.140589042283701</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139513418553302</v>
+        <v>1.139701510938917</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.137562274924913</v>
+        <v>1.138163564598268</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.133753190708147</v>
+        <v>1.134609796506723</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.127883514918467</v>
+        <v>1.128887838709604</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.122220928685634</v>
+        <v>1.123255972703457</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.116113726967734</v>
+        <v>1.117214253076308</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.1116389342351</v>
+        <v>1.113110627437498</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.10983181963441</v>
+        <v>1.111402300823265</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.111508423822237</v>
+        <v>1.113428215456131</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.11536223161751</v>
+        <v>1.11823045330879</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.11943289702222</v>
+        <v>1.125570985450776</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.109806755887536</v>
+        <v>1.11575026721823</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187068539473654</v>
+        <v>1.187078470379111</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178698722744542</v>
+        <v>1.178714420227427</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17722881342714</v>
+        <v>1.177242368122112</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172708171941665</v>
+        <v>1.172727327595463</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171469721586245</v>
+        <v>1.171489794537962</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169442703411157</v>
+        <v>1.169463442388451</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166972800021738</v>
+        <v>1.166993721728377</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165233292185067</v>
+        <v>1.165254100921712</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166319429818715</v>
+        <v>1.166333368508806</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161119052915937</v>
+        <v>1.161116900763883</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.16159119747328</v>
+        <v>1.161589812511177</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160937667925743</v>
+        <v>1.160936585380811</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162220473504513</v>
+        <v>1.16221274405756</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15979066684722</v>
+        <v>1.159786896905618</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413544018773</v>
+        <v>1.15541368288805</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148441594194643</v>
+        <v>1.148443541014107</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143151687343724</v>
+        <v>1.143150448822406</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137961604013227</v>
+        <v>1.13795449077179</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130346367067865</v>
+        <v>1.130329604165142</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12524207549299</v>
+        <v>1.125221327906596</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130357710080939</v>
+        <v>1.130312966127591</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137635763865127</v>
+        <v>1.137572641258868</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.144084215911058</v>
+        <v>1.143981157180481</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147627862094311</v>
+        <v>1.147508054844096</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147770027826126</v>
+        <v>1.147627079719197</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.142092149572806</v>
+        <v>1.141943682456949</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.14058519686833</v>
+        <v>1.140430205468462</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140552699484859</v>
+        <v>1.140390154567845</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151500502263473</v>
+        <v>1.151394602353544</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16658547720497</v>
+        <v>1.166514556819759</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166980809377619</v>
+        <v>1.166915136194854</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180730518109177</v>
+        <v>1.180720228562838</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190892921811937</v>
+        <v>1.190946442611835</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.198965168724222</v>
+        <v>1.199030071882949</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210323111384085</v>
+        <v>1.210420345384331</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205266536167525</v>
+        <v>1.205304360013211</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205793737156843</v>
+        <v>1.205854353255107</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208678922934398</v>
+        <v>1.208804697506972</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213767353872405</v>
+        <v>1.213945477822186</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219629890840408</v>
+        <v>1.219834549143595</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218839301046039</v>
+        <v>1.218999612604655</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20658217946696</v>
+        <v>1.206724708383613</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198390344183501</v>
+        <v>1.198523903543874</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188169239396864</v>
+        <v>1.188268114810515</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180020474155015</v>
+        <v>1.180103076944174</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175054405611114</v>
+        <v>1.175116121498369</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171830154993293</v>
+        <v>1.171871703983535</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172767311159471</v>
+        <v>1.172837859744669</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169114005877572</v>
+        <v>1.169160617884395</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167792943822353</v>
+        <v>1.16784749003047</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167482659703276</v>
+        <v>1.167568507523837</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165512259427683</v>
+        <v>1.165586737977506</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157483953847761</v>
+        <v>1.157542543531603</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150813211011094</v>
+        <v>1.150891228191322</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146092978717539</v>
+        <v>1.14534352219659</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.142755201450033</v>
+        <v>1.142751339966348</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.140589042283701</v>
+        <v>1.141043493301807</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.139701510938917</v>
+        <v>1.140460871798095</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.138163564598268</v>
+        <v>1.138778387968163</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.134609796506723</v>
+        <v>1.135211860144025</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.128887838709604</v>
+        <v>1.129615227906295</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.123255972703457</v>
+        <v>1.124196540401733</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.117214253076308</v>
+        <v>1.11847768642582</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.113110627437498</v>
+        <v>1.114567240140289</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.111402300823265</v>
+        <v>1.112983747306385</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.113428215456131</v>
+        <v>1.114623337838911</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.11823045330879</v>
+        <v>1.118313568480515</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.125570985450776</v>
+        <v>1.123128766176396</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.11575026721823</v>
+        <v>1.122545740996689</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187078470379111</v>
+        <v>1.187083199442592</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178714420227427</v>
+        <v>1.178721896873753</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177242368122112</v>
+        <v>1.177248828192303</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172727327595463</v>
+        <v>1.172736455205434</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171489794537962</v>
+        <v>1.171499358793498</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169463442388451</v>
+        <v>1.169473323576197</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.166993721728377</v>
+        <v>1.167003689778429</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165254100921712</v>
+        <v>1.165264015127708</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166333368508806</v>
+        <v>1.166340018489185</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161116900763883</v>
+        <v>1.161115878565798</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161589812511177</v>
+        <v>1.161589155527845</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160936585380811</v>
+        <v>1.160936072345593</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16221274405756</v>
+        <v>1.162209068021508</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159786896905618</v>
+        <v>1.159785103336566</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541368288805</v>
+        <v>1.155413752803497</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148443541014107</v>
+        <v>1.148444482815351</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143150448822406</v>
+        <v>1.143149883271261</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.13795449077179</v>
+        <v>1.137951139720574</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130329604165142</v>
+        <v>1.130321650695104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125221327906596</v>
+        <v>1.125211472020621</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130312966127591</v>
+        <v>1.130291685207315</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137572641258868</v>
+        <v>1.137542605441664</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143981157180481</v>
+        <v>1.143932049794842</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147508054844096</v>
+        <v>1.147450949529313</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147627079719197</v>
+        <v>1.147558929566089</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141943682456949</v>
+        <v>1.141872864804481</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140430205468462</v>
+        <v>1.140356240922403</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140390154567845</v>
+        <v>1.140312540761625</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151394602353544</v>
+        <v>1.151344007636428</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166514556819759</v>
+        <v>1.166480682827543</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166915136194854</v>
+        <v>1.166883744088232</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180720228562838</v>
+        <v>1.180715294278813</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190946442611835</v>
+        <v>1.190972017312063</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199030071882949</v>
+        <v>1.199061075358365</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210420345384331</v>
+        <v>1.210466720691005</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205304360013211</v>
+        <v>1.205322239084681</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205854353255107</v>
+        <v>1.205883072612282</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208804697506972</v>
+        <v>1.208864523668046</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.213945477822186</v>
+        <v>1.214030350382722</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219834549143595</v>
+        <v>1.219932092026647</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.218999612604655</v>
+        <v>1.219075948335345</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206724708383613</v>
+        <v>1.206792620891024</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198523903543874</v>
+        <v>1.198587576446853</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188268114810515</v>
+        <v>1.188315313026126</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180103076944174</v>
+        <v>1.180142523474383</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175116121498369</v>
+        <v>1.1751456008264</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171871703983535</v>
+        <v>1.171891546585053</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172837859744669</v>
+        <v>1.172871532318002</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169160617884395</v>
+        <v>1.169182820873346</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.16784749003047</v>
+        <v>1.167873468879825</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167568507523837</v>
+        <v>1.167609443759518</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165586737977506</v>
+        <v>1.165622238555354</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157542543531603</v>
+        <v>1.157570417081299</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150891228191322</v>
+        <v>1.150928502352634</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14534352219659</v>
+        <v>1.145379491883047</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.142751339966348</v>
+        <v>1.143385079714514</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.141043493301807</v>
+        <v>1.141886411696174</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.140460871798095</v>
+        <v>1.141509281571463</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.138778387968163</v>
+        <v>1.140098862662746</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.135211860144025</v>
+        <v>1.136774688887768</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.129615227906295</v>
+        <v>1.131457073061697</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.124196540401733</v>
+        <v>1.126261791462078</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.11847768642582</v>
+        <v>1.120915260060096</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.114567240140289</v>
+        <v>1.117535369865612</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.112983747306385</v>
+        <v>1.116194478744441</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.114623337838911</v>
+        <v>1.117829535661085</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.118313568480515</v>
+        <v>1.121411560215905</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.123128766176396</v>
+        <v>1.126904968627247</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.122545740996689</v>
+        <v>1.130928529649994</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145379491883047</v>
+        <v>1.146202039175446</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143385079714514</v>
+        <v>1.143925581746828</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.141886411696174</v>
+        <v>1.142639491769493</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.141509281571463</v>
+        <v>1.142290482865461</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.140098862662746</v>
+        <v>1.141330300241675</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.136774688887768</v>
+        <v>1.138471041529051</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.131457073061697</v>
+        <v>1.133381825630892</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.126261791462078</v>
+        <v>1.128271231589937</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.120915260060096</v>
+        <v>1.123132969525815</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.117535369865612</v>
+        <v>1.120058894885521</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.116194478744441</v>
+        <v>1.118660550903355</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.117829535661085</v>
+        <v>1.120831793060858</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.121411560215905</v>
+        <v>1.124857776466197</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.126904968627247</v>
+        <v>1.132586953742996</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.130928529649994</v>
+        <v>1.132121175826706</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B115">
+        <v>1.120762191550452</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187083199442592</v>
+        <v>1.187087780759495</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178721896873753</v>
+        <v>1.17872914089028</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177248828192303</v>
+        <v>1.177255089737231</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172736455205434</v>
+        <v>1.172745301183848</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171499358793498</v>
+        <v>1.171508627671559</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169473323576197</v>
+        <v>1.169482899344894</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167003689778429</v>
+        <v>1.167013349601576</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165264015127708</v>
+        <v>1.165273622759446</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166340018489185</v>
+        <v>1.166346468347701</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161115878565798</v>
+        <v>1.161114889933441</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161589155527845</v>
+        <v>1.161588520626945</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160936072345593</v>
+        <v>1.160935576857308</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162209068021508</v>
+        <v>1.162205509728644</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159785103336566</v>
+        <v>1.159783366831264</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413752803497</v>
+        <v>1.155413822860417</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148444482815351</v>
+        <v>1.148445404252366</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143149883271261</v>
+        <v>1.143149350301193</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137951139720574</v>
+        <v>1.137947915689455</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130321650695104</v>
+        <v>1.13031396356138</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125211472020621</v>
+        <v>1.125201938882082</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130291685207315</v>
+        <v>1.130271085245432</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137542605441664</v>
+        <v>1.137513522295266</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143932049794842</v>
+        <v>1.143884457643454</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147450949529313</v>
+        <v>1.147395595663867</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147558929566089</v>
+        <v>1.147492860494134</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141872864804481</v>
+        <v>1.141804187404919</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140356240922403</v>
+        <v>1.140284490346439</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140312540761625</v>
+        <v>1.140237222789973</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151344007636428</v>
+        <v>1.151294891867</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166480682827543</v>
+        <v>1.166447804419745</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166883744088232</v>
+        <v>1.16685325966334</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180715294278813</v>
+        <v>1.18071049279215</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190972017312063</v>
+        <v>1.190996847304373</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199061075358365</v>
+        <v>1.199091169754364</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210466720691005</v>
+        <v>1.210511691825206</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205322239084681</v>
+        <v>1.205339477822621</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205883072612282</v>
+        <v>1.205910804618662</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208864523668046</v>
+        <v>1.208922438827315</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214030350382722</v>
+        <v>1.214112602008389</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.219932092026647</v>
+        <v>1.220026639321593</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219075948335345</v>
+        <v>1.219149896098595</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206792620891024</v>
+        <v>1.206858436162434</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198587576446853</v>
+        <v>1.198649304029024</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188315313026126</v>
+        <v>1.188361106496117</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180142523474383</v>
+        <v>1.180180805904946</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.1751456008264</v>
+        <v>1.175174214779892</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171891546585053</v>
+        <v>1.171910804369206</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172871532318002</v>
+        <v>1.172904200480202</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169182820873346</v>
+        <v>1.169204333965493</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167873468879825</v>
+        <v>1.167898638361413</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167609443759518</v>
+        <v>1.167649135146017</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165622238555354</v>
+        <v>1.165656650862218</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157570417081299</v>
+        <v>1.157597403053709</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150928502352634</v>
+        <v>1.150964686840657</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146202039175446</v>
+        <v>1.145414473746002</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143925581746828</v>
+        <v>1.143401898812875</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.142639491769493</v>
+        <v>1.14235808218575</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.142290482865461</v>
+        <v>1.142097807886886</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.141330300241675</v>
+        <v>1.140746902264802</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.138471041529051</v>
+        <v>1.137673521464821</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.133381825630892</v>
+        <v>1.132445901038323</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.128271231589937</v>
+        <v>1.127283750112529</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.123132969525815</v>
+        <v>1.122057508798878</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.120058894885521</v>
+        <v>1.118796656133337</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.118660550903355</v>
+        <v>1.1174162424887</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.120831793060858</v>
+        <v>1.118405569653739</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.124857776466197</v>
+        <v>1.122528673980212</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.132586953742996</v>
+        <v>1.127660303832458</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.132121175826706</v>
+        <v>1.131089735900416</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.120762191550452</v>
+        <v>1.129612607210291</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145414473746002</v>
+        <v>1.14623637087332</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143401898812875</v>
+        <v>1.143941034013711</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.14235808218575</v>
+        <v>1.143069541168872</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.142097807886886</v>
+        <v>1.142817657423097</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.140746902264802</v>
+        <v>1.141899984717013</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.137673521464821</v>
+        <v>1.13919297304641</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.132445901038323</v>
+        <v>1.134099486828667</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.127283750112529</v>
+        <v>1.128932506898764</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.122057508798878</v>
+        <v>1.12381226776076</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.118796656133337</v>
+        <v>1.120657653895581</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.1174162424887</v>
+        <v>1.119059464946881</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.118405569653739</v>
+        <v>1.121427509632551</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.122528673980212</v>
+        <v>1.124954881257072</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.127660303832458</v>
+        <v>1.131633749669549</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.131089735900416</v>
+        <v>1.130536643484063</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.129612607210291</v>
+        <v>1.120761070475956</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187087780759495</v>
+        <v>1.18709222114669</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17872914089028</v>
+        <v>1.178736162965955</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177255089737231</v>
+        <v>1.177261161765074</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172745301183848</v>
+        <v>1.172753878361698</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171508627671559</v>
+        <v>1.171517614641818</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169482899344894</v>
+        <v>1.169492183633683</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167013349601576</v>
+        <v>1.167022715270735</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165273622759446</v>
+        <v>1.165282937814964</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166346468347701</v>
+        <v>1.166352726967311</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161114889933441</v>
+        <v>1.161113933244002</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161588520626945</v>
+        <v>1.161587906718644</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160935576857308</v>
+        <v>1.160935098037032</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162205509728644</v>
+        <v>1.162202063617316</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159783366831264</v>
+        <v>1.15978168471322</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413822860417</v>
+        <v>1.155413892944074</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148445404252366</v>
+        <v>1.148446305850151</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143149350301193</v>
+        <v>1.143148847734979</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137947915689455</v>
+        <v>1.137944811818654</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13031396356138</v>
+        <v>1.130306529684362</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125201938882082</v>
+        <v>1.125192712948977</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130271085245432</v>
+        <v>1.130251134158412</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137513522295266</v>
+        <v>1.137485347324203</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143884457643454</v>
+        <v>1.143838311802306</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147395595663867</v>
+        <v>1.147341914104227</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147492860494134</v>
+        <v>1.147428778916721</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141804187404919</v>
+        <v>1.141737555075673</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140284490346439</v>
+        <v>1.140214856303893</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140237222789973</v>
+        <v>1.140164100921729</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151294891867</v>
+        <v>1.15124719150147</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166447804419745</v>
+        <v>1.166415878515912</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16685325966334</v>
+        <v>1.166823644354372</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18071049279215</v>
+        <v>1.180705818829567</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.190996847304373</v>
+        <v>1.191020964474671</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199091169754364</v>
+        <v>1.199120394292515</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210511691825206</v>
+        <v>1.210555321477113</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205339477822621</v>
+        <v>1.205356109338316</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205910804618662</v>
+        <v>1.205937598671851</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208922438827315</v>
+        <v>1.208978532715284</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214112602008389</v>
+        <v>1.214192351950308</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220026639321593</v>
+        <v>1.220118326477328</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219149896098595</v>
+        <v>1.219221565841779</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206858436162434</v>
+        <v>1.206922249478841</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198649304029024</v>
+        <v>1.198709173661867</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188361106496117</v>
+        <v>1.188405556621621</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180180805904946</v>
+        <v>1.18021797469566</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175174214779892</v>
+        <v>1.175202000749882</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171910804369206</v>
+        <v>1.171929502703811</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172904200480202</v>
+        <v>1.172935908320976</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169204333965493</v>
+        <v>1.169225188665473</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167898638361413</v>
+        <v>1.167923035533043</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167649135146017</v>
+        <v>1.16768763741058</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165656650862218</v>
+        <v>1.165690024054214</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157597403053709</v>
+        <v>1.157623542931417</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150964686840657</v>
+        <v>1.150999828122816</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14623637087332</v>
+        <v>1.145448506944776</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143941034013711</v>
+        <v>1.143418368488722</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.143069541168872</v>
+        <v>1.142791782802652</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.142817657423097</v>
+        <v>1.142638047180766</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.141899984717013</v>
+        <v>1.141332750704272</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.13919297304641</v>
+        <v>1.13850439355552</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.134099486828667</v>
+        <v>1.133350556652714</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.128932506898764</v>
+        <v>1.128225342684993</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.12381226776076</v>
+        <v>1.123106538674154</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.120657653895581</v>
+        <v>1.119943793545867</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.119059464946881</v>
+        <v>1.118524175683893</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.121427509632551</v>
+        <v>1.118938199991578</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.124954881257072</v>
+        <v>1.123513757921302</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131633749669549</v>
+        <v>1.128286563131388</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.130536643484063</v>
+        <v>1.131198269659916</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.120761070475956</v>
+        <v>1.129614549983456</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145448506944776</v>
+        <v>1.146269759500051</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143418368488722</v>
+        <v>1.143956176248145</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.142791782802652</v>
+        <v>1.143682989963762</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.142638047180766</v>
+        <v>1.143547161824553</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.141332750704272</v>
+        <v>1.14266295946808</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.13850439355552</v>
+        <v>1.140162688270033</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.133350556652714</v>
+        <v>1.135083141912784</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.128225342684993</v>
+        <v>1.129904600289366</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.123106538674154</v>
+        <v>1.124828946281983</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.119943793545867</v>
+        <v>1.121680849821628</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.118524175683893</v>
+        <v>1.12047161179923</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.118938199991578</v>
+        <v>1.122526370185522</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.123513757921302</v>
+        <v>1.125683757092646</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.128286563131388</v>
+        <v>1.131797145085808</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.131198269659916</v>
+        <v>1.130766181833131</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.129614549983456</v>
+        <v>1.12450415488339</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18709222114669</v>
+        <v>1.187096527008064</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178736162965955</v>
+        <v>1.178742973144855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177261161765074</v>
+        <v>1.177267052747411</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172753878361698</v>
+        <v>1.172762198802531</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171517614641818</v>
+        <v>1.171526332367561</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169492183633683</v>
+        <v>1.169501189546521</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167022715270735</v>
+        <v>1.167031800015281</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165282937814964</v>
+        <v>1.165291973453214</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166352726967311</v>
+        <v>1.166358802713924</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161113933244002</v>
+        <v>1.161113006977412</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161587906718644</v>
+        <v>1.161587312783384</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160935098037032</v>
+        <v>1.160934635063242</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162202063617316</v>
+        <v>1.162198724470364</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15978168471322</v>
+        <v>1.159780054470508</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413892944074</v>
+        <v>1.155413962953284</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148446305850151</v>
+        <v>1.148447188126794</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143148847734979</v>
+        <v>1.143148373567251</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137944811818654</v>
+        <v>1.137941821722599</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130306529684362</v>
+        <v>1.1302993368228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125192712948977</v>
+        <v>1.125183779658327</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130251134158412</v>
+        <v>1.130231801842144</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137485347324203</v>
+        <v>1.137458038754453</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143838311802306</v>
+        <v>1.143793547456871</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147341914104227</v>
+        <v>1.147289830391643</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147428778916721</v>
+        <v>1.147366596757755</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141737555075673</v>
+        <v>1.141672878171945</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140214856303893</v>
+        <v>1.140147246962729</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140164100921729</v>
+        <v>1.140093081080262</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15124719150147</v>
+        <v>1.151200846562473</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166415878515912</v>
+        <v>1.166384864475455</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166823644354372</v>
+        <v>1.166794861735283</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180705818829567</v>
+        <v>1.18070126739298</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191020964474671</v>
+        <v>1.191044398924654</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199120394292515</v>
+        <v>1.199148785981068</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210555321477113</v>
+        <v>1.210597668667454</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205356109338316</v>
+        <v>1.205372164533618</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205937598671851</v>
+        <v>1.205963500963195</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.208978532715284</v>
+        <v>1.20903288955389</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214192351950308</v>
+        <v>1.214269712351409</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220118326477328</v>
+        <v>1.220207280925225</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219221565841779</v>
+        <v>1.219291060886877</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206922249478841</v>
+        <v>1.206984150458677</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198709173661867</v>
+        <v>1.198767267587755</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188405556621621</v>
+        <v>1.188448721300502</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18021797469566</v>
+        <v>1.180254077450735</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175202000749882</v>
+        <v>1.175228994013461</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171929502703811</v>
+        <v>1.171947665517054</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172935908320976</v>
+        <v>1.172966697398063</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169225188665473</v>
+        <v>1.16924541459769</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167923035533043</v>
+        <v>1.167946695234952</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16768763741058</v>
+        <v>1.167725003015125</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165690024054214</v>
+        <v>1.165722404378555</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157623542931417</v>
+        <v>1.15764887566587</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.150999828122816</v>
+        <v>1.151033970099951</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146269759500051</v>
+        <v>1.145481628656922</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143956176248145</v>
+        <v>1.143434497319468</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.143682989963762</v>
+        <v>1.143404072232219</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.143547161824553</v>
+        <v>1.143393241935424</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14266295946808</v>
+        <v>1.14215932597186</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.140162688270033</v>
+        <v>1.139590956373431</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.135083141912784</v>
+        <v>1.134596930247695</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.129904600289366</v>
+        <v>1.129590885411706</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.124828946281983</v>
+        <v>1.124654561462221</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.121680849821628</v>
+        <v>1.121706752310659</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.12047161179923</v>
+        <v>1.120350114416097</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.122526370185522</v>
+        <v>1.120459701009325</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.125683757092646</v>
+        <v>1.12462216633822</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131797145085808</v>
+        <v>1.12907378623441</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.130766181833131</v>
+        <v>1.133858069771247</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.12450415488339</v>
+        <v>1.135664875672209</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145481628656922</v>
+        <v>1.146302242599943</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143434497319468</v>
+        <v>1.143971015340555</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.143404072232219</v>
+        <v>1.1440896933288</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.143393241935424</v>
+        <v>1.144041945611848</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14215932597186</v>
+        <v>1.143172254527856</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.139590956373431</v>
+        <v>1.14073694945939</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.134596930247695</v>
+        <v>1.13565603367888</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.129590885411706</v>
+        <v>1.130429506232442</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.124654561462221</v>
+        <v>1.125348269542319</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.121706752310659</v>
+        <v>1.122087568756315</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.120350114416097</v>
+        <v>1.121235997352147</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.120459701009325</v>
+        <v>1.122927875954815</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.12462216633822</v>
+        <v>1.125663273244057</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.12907378623441</v>
+        <v>1.130975795295349</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.133858069771247</v>
+        <v>1.12959418402523</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135664875672209</v>
+        <v>1.123408454886488</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187096527008064</v>
+        <v>1.187104758886121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178742973144855</v>
+        <v>1.178755995047537</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177267052747411</v>
+        <v>1.177278323011547</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172762198802531</v>
+        <v>1.172778114224243</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171526332367561</v>
+        <v>1.171543007058113</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169501189546521</v>
+        <v>1.169518414848496</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167031800015281</v>
+        <v>1.167049175798396</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165291973453214</v>
+        <v>1.165309255284408</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166358802713924</v>
+        <v>1.166370436685454</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161113006977412</v>
+        <v>1.161111240098992</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161587312783384</v>
+        <v>1.161586181072298</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160934635063242</v>
+        <v>1.160933753628943</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162198724470364</v>
+        <v>1.162192347768319</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159780054470508</v>
+        <v>1.159776940312682</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155413962953284</v>
+        <v>1.155414102402524</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148447188126794</v>
+        <v>1.148448896746754</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143148373567251</v>
+        <v>1.143147503172283</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137941821722599</v>
+        <v>1.137936159449733</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.1302993368228</v>
+        <v>1.130285628984038</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125183779658327</v>
+        <v>1.125166737200428</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130231801842144</v>
+        <v>1.130194882115984</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137458038754453</v>
+        <v>1.137405866121587</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143793547456871</v>
+        <v>1.143707922761441</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147289830391643</v>
+        <v>1.147190180081924</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147366596757755</v>
+        <v>1.147247603587106</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141672878171945</v>
+        <v>1.141549057412781</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140147246962729</v>
+        <v>1.140017760742266</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.140093081080262</v>
+        <v>1.139956997122617</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151200846562473</v>
+        <v>1.151111999436155</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166384864475455</v>
+        <v>1.16632542061813</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166794861735283</v>
+        <v>1.166739658701213</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18070126739298</v>
+        <v>1.180692513376328</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191044398924654</v>
+        <v>1.191089331873309</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199148785981068</v>
+        <v>1.199203208682231</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210597668667454</v>
+        <v>1.21067873496108</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205372164533618</v>
+        <v>1.205402659580554</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205963500963195</v>
+        <v>1.206012800492925</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20903288955389</v>
+        <v>1.209136703879516</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214269712351409</v>
+        <v>1.214417680640075</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220207280925225</v>
+        <v>1.220377464780932</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219291060886877</v>
+        <v>1.21942390994131</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.206984150458677</v>
+        <v>1.207102548011009</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198767267587755</v>
+        <v>1.198878433825507</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188448721300502</v>
+        <v>1.188531409840764</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180254077450735</v>
+        <v>1.180323262163366</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175228994013461</v>
+        <v>1.175280733827721</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171947665517054</v>
+        <v>1.171982473687081</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172966697398063</v>
+        <v>1.173025673887642</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16924541459769</v>
+        <v>1.169284090068675</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167946695234952</v>
+        <v>1.167991931464651</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167725003015125</v>
+        <v>1.16779651915434</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165722404378555</v>
+        <v>1.165784358119399</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15764887566587</v>
+        <v>1.157697263973319</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151033970099951</v>
+        <v>1.151099419927377</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146302242599943</v>
+        <v>1.145545277128865</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143971015340555</v>
+        <v>1.143465766221487</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.1440896933288</v>
+        <v>1.144194779387009</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.144041945611848</v>
+        <v>1.144386537171826</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.143172254527856</v>
+        <v>1.143220083358436</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.14073694945939</v>
+        <v>1.14084800818471</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.13565603367888</v>
+        <v>1.136049010185691</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.130429506232442</v>
+        <v>1.131143700325982</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.125348269542319</v>
+        <v>1.126398703677115</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.122087568756315</v>
+        <v>1.123585203529707</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.121235997352147</v>
+        <v>1.122154293960799</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.122927875954815</v>
+        <v>1.121353692496284</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.125663273244057</v>
+        <v>1.125578304562733</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.130975795295349</v>
+        <v>1.130243353905306</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.12959418402523</v>
+        <v>1.133843208433967</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.123408454886488</v>
+        <v>1.13389633817913</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187104758886121</v>
+        <v>1.187100704365332</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178755995047537</v>
+        <v>1.1787495808741</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177278323011547</v>
+        <v>1.177272770658564</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172778114224243</v>
+        <v>1.172770273858957</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171543007058113</v>
+        <v>1.171534792765117</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169518414848496</v>
+        <v>1.169509929413783</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167049175798396</v>
+        <v>1.167040616283298</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165309255284408</v>
+        <v>1.165300742055983</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166370436685454</v>
+        <v>1.166364703473405</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161111240098992</v>
+        <v>1.161112109708351</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161586181072298</v>
+        <v>1.161586737866322</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160933753628943</v>
+        <v>1.160934187167229</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162192347768319</v>
+        <v>1.162195487388877</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159776940312682</v>
+        <v>1.159778473743329</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414102402524</v>
+        <v>1.155414032798907</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148448896746754</v>
+        <v>1.148448051592141</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143147503172283</v>
+        <v>1.143147925948759</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137936159449733</v>
+        <v>1.137938939450327</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130285628984038</v>
+        <v>1.130292373507992</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125166737200428</v>
+        <v>1.1251751253505</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130194882115984</v>
+        <v>1.130213060021946</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137405866121587</v>
+        <v>1.137431557329015</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143707922761441</v>
+        <v>1.143750103600925</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147190180081924</v>
+        <v>1.147239274411506</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147247603587106</v>
+        <v>1.14730623105329</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141549057412781</v>
+        <v>1.141610072191522</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140017760742266</v>
+        <v>1.140081575700537</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139956997122617</v>
+        <v>1.14002407445129</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151111999436155</v>
+        <v>1.151155800394007</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16632542061813</v>
+        <v>1.166354723928085</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166739658701213</v>
+        <v>1.166766877374498</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180692513376328</v>
+        <v>1.180696833741754</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191089331873309</v>
+        <v>1.191067179094099</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199203208682231</v>
+        <v>1.199176379768108</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21067873496108</v>
+        <v>1.210638789011576</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205402659580554</v>
+        <v>1.205387672279986</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206012800492925</v>
+        <v>1.205988554731448</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209136703879516</v>
+        <v>1.209085588471231</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214417680640075</v>
+        <v>1.214344788766951</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220377464780932</v>
+        <v>1.220293622661707</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.21942390994131</v>
+        <v>1.219358478420522</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207102548011009</v>
+        <v>1.207044223470631</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198878433825507</v>
+        <v>1.198823663288972</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188531409840764</v>
+        <v>1.188490655171904</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180323262163366</v>
+        <v>1.180289159116559</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175280733827721</v>
+        <v>1.175255227880386</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171982473687081</v>
+        <v>1.171965315397699</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173025673887642</v>
+        <v>1.172996606915593</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169284090068675</v>
+        <v>1.169265039643853</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167991931464651</v>
+        <v>1.167969650252473</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16779651915434</v>
+        <v>1.167761281391086</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165784358119399</v>
+        <v>1.165753835385041</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157697263973319</v>
+        <v>1.157673437866516</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151099419927377</v>
+        <v>1.151067154278175</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145545277128865</v>
+        <v>1.146333855798766</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143465766221487</v>
+        <v>1.143985558174589</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144194779387009</v>
+        <v>1.144662293132884</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.144386537171826</v>
+        <v>1.144710595379704</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.143220083358436</v>
+        <v>1.14384447740393</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.14084800818471</v>
+        <v>1.141424952905054</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.136049010185691</v>
+        <v>1.136386524619289</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.131143700325982</v>
+        <v>1.131172591104917</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.126398703677115</v>
+        <v>1.126122261056298</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.123585203529707</v>
+        <v>1.122844291882873</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.122154293960799</v>
+        <v>1.122384724307913</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.121353692496284</v>
+        <v>1.123817703612942</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.125578304562733</v>
+        <v>1.12624659420339</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.130243353905306</v>
+        <v>1.131143032519387</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.133843208433967</v>
+        <v>1.129871855116034</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.13389633817913</v>
+        <v>1.125195602449151</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187100704365332</v>
+        <v>1.187108695909618</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.1787495808741</v>
+        <v>1.178762224045658</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177272770658564</v>
+        <v>1.177283716890922</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172770273858957</v>
+        <v>1.172785729979471</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171534792765117</v>
+        <v>1.171550985827064</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169509929413783</v>
+        <v>1.169526656797742</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167040616283298</v>
+        <v>1.167057489611634</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165300742055983</v>
+        <v>1.16531752413064</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166364703473405</v>
+        <v>1.166376009374658</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161112109708351</v>
+        <v>1.161110396892404</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161586737866322</v>
+        <v>1.161585641561253</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160934187167229</v>
+        <v>1.160933333773216</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162195487388877</v>
+        <v>1.16218930127676</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159778473743329</v>
+        <v>1.159775452090028</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414032798907</v>
+        <v>1.155414171695254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148448051592141</v>
+        <v>1.1484497240811</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143147925948759</v>
+        <v>1.14314710365998</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137938939450327</v>
+        <v>1.137933476535249</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130292373507992</v>
+        <v>1.130279093153544</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.1251751253505</v>
+        <v>1.125158603154997</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130213060021946</v>
+        <v>1.130177243110722</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137431557329015</v>
+        <v>1.137380930366521</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143750103600925</v>
+        <v>1.143666950746921</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147239274411506</v>
+        <v>1.147142485068643</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14730623105329</v>
+        <v>1.147190640556921</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141610072191522</v>
+        <v>1.141489758562718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.140081575700537</v>
+        <v>1.139955724827594</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.14002407445129</v>
+        <v>1.139891769752843</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151155800394007</v>
+        <v>1.151069393017763</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166354723928085</v>
+        <v>1.166296920261434</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166766877374498</v>
+        <v>1.166713174882213</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180696833741754</v>
+        <v>1.180688302023069</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191067179094099</v>
+        <v>1.191110882706605</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199176379768108</v>
+        <v>1.199229303961914</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210638789011576</v>
+        <v>1.210717556025211</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205387672279986</v>
+        <v>1.205417151717082</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.205988554731448</v>
+        <v>1.206036276250616</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209085588471231</v>
+        <v>1.209186305819968</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214344788766951</v>
+        <v>1.214488481736843</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220293622661707</v>
+        <v>1.220458913962468</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219358478420522</v>
+        <v>1.219487441668672</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207044223470631</v>
+        <v>1.207159199049151</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198823663288972</v>
+        <v>1.198931648144621</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188490655171904</v>
+        <v>1.18857103408415</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180289159116559</v>
+        <v>1.180356426752324</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175255227880386</v>
+        <v>1.175305541623618</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171965315397699</v>
+        <v>1.171999160563651</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.172996606915593</v>
+        <v>1.173053933288406</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169265039643853</v>
+        <v>1.169302590634894</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.167969650252473</v>
+        <v>1.168013567980204</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167761281391086</v>
+        <v>1.167830760302181</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165753835385041</v>
+        <v>1.165814011300284</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157673437866516</v>
+        <v>1.157720386414319</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151067154278175</v>
+        <v>1.151130804227523</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146333855798766</v>
+        <v>1.14557586936666</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143985558174589</v>
+        <v>1.143480922857191</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144662293132884</v>
+        <v>1.144735371325956</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.144710595379704</v>
+        <v>1.145044303581278</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14384447740393</v>
+        <v>1.143915659732859</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.141424952905054</v>
+        <v>1.141636862451466</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.136386524619289</v>
+        <v>1.136943427690712</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.131172591104917</v>
+        <v>1.132086810503447</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.126122261056298</v>
+        <v>1.127422689873786</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.122844291882873</v>
+        <v>1.124683767235815</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.122384724307913</v>
+        <v>1.123214736350099</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.123817703612942</v>
+        <v>1.122001441316543</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.12624659420339</v>
+        <v>1.126715787960239</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131143032519387</v>
+        <v>1.131119145259222</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.129871855116034</v>
+        <v>1.134390692772382</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.125195602449151</v>
+        <v>1.134267042502861</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187108695909618</v>
+        <v>1.187112520470019</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178762224045658</v>
+        <v>1.178768275772103</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177283716890922</v>
+        <v>1.177288958982903</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172785729979471</v>
+        <v>1.172793130636717</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171550985827064</v>
+        <v>1.171558739054772</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169526656797742</v>
+        <v>1.169534665589694</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167057489611634</v>
+        <v>1.167065568149056</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.16531752413064</v>
+        <v>1.165325558965116</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166376009374658</v>
+        <v>1.166381428178998</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161110396892404</v>
+        <v>1.161109578906534</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161585641561253</v>
+        <v>1.161585118544071</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160933333773216</v>
+        <v>1.160932926966341</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16218930127676</v>
+        <v>1.162186343835015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159775452090028</v>
+        <v>1.159774007107856</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414171695254</v>
+        <v>1.15541424061672</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.1484497240811</v>
+        <v>1.148450534074931</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314710365998</v>
+        <v>1.143146725952025</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137933476535249</v>
+        <v>1.137930885858574</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130279093153544</v>
+        <v>1.13027275652819</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125158603154997</v>
+        <v>1.125150711875978</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130177243110722</v>
+        <v>1.130160119447187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137380930366521</v>
+        <v>1.137356717303421</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143666950746921</v>
+        <v>1.143627136416915</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147142485068643</v>
+        <v>1.147096130523746</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147190640556921</v>
+        <v>1.147135272268291</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141489758562718</v>
+        <v>1.141432104512133</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139955724827594</v>
+        <v>1.13989539490517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139891769752843</v>
+        <v>1.139828317266384</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151069393017763</v>
+        <v>1.15102793316545</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166296920261434</v>
+        <v>1.166269190413675</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166713174882213</v>
+        <v>1.166687396708289</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180688302023069</v>
+        <v>1.180684195620264</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191110882706605</v>
+        <v>1.191131855687689</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199229303961914</v>
+        <v>1.199254695174609</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210717556025211</v>
+        <v>1.210755298973944</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205417151717082</v>
+        <v>1.205431172383376</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206036276250616</v>
+        <v>1.206059017684455</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209186305819968</v>
+        <v>1.209234460277999</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214488481736843</v>
+        <v>1.214557280544732</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220458913962468</v>
+        <v>1.220538070918338</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219487441668672</v>
+        <v>1.219549154917073</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207159199049151</v>
+        <v>1.207214247343966</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198931648144621</v>
+        <v>1.198983371364891</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18857103408415</v>
+        <v>1.188609574041112</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180356426752324</v>
+        <v>1.180388690889365</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175305541623618</v>
+        <v>1.175329679441252</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171999160563651</v>
+        <v>1.172015395120782</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173053933288406</v>
+        <v>1.173081418190238</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169302590634894</v>
+        <v>1.169320564708654</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168013567980204</v>
+        <v>1.168034587262061</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167830760302181</v>
+        <v>1.167864046394024</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165814011300284</v>
+        <v>1.165842831481493</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157720386414319</v>
+        <v>1.157742835749729</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151130804227523</v>
+        <v>1.151161342403834</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14557586936666</v>
+        <v>1.145605681274011</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143480922857191</v>
+        <v>1.143495771747526</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144735371325956</v>
+        <v>1.144726246081262</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145044303581278</v>
+        <v>1.145430033880649</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.143915659732859</v>
+        <v>1.144366367661978</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.141636862451466</v>
+        <v>1.14208934243515</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.136943427690712</v>
+        <v>1.137336427179652</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.132086810503447</v>
+        <v>1.132578155355384</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.127422689873786</v>
+        <v>1.128007941872201</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.124683767235815</v>
+        <v>1.125340365835495</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.123214736350099</v>
+        <v>1.12387335045545</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.122001441316543</v>
+        <v>1.122642634768737</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.126715787960239</v>
+        <v>1.12662193234203</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131119145259222</v>
+        <v>1.131763737067221</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.134390692772382</v>
+        <v>1.134834806117508</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.134267042502861</v>
+        <v>1.134767022812528</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B116">
+        <v>1.136250697167382</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187112520470019</v>
+        <v>1.187108695909618</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178768275772103</v>
+        <v>1.178762224045658</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177288958982903</v>
+        <v>1.177283716890922</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172793130636717</v>
+        <v>1.172785729979471</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171558739054772</v>
+        <v>1.171550985827064</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169534665589694</v>
+        <v>1.169526656797742</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167065568149056</v>
+        <v>1.167057489611634</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165325558965116</v>
+        <v>1.16531752413064</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166381428178998</v>
+        <v>1.166376009374658</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161109578906534</v>
+        <v>1.161110396892404</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161585118544071</v>
+        <v>1.161585641561253</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160932926966341</v>
+        <v>1.160933333773216</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162186343835015</v>
+        <v>1.16218930127676</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159774007107856</v>
+        <v>1.159775452090028</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541424061672</v>
+        <v>1.155414171695254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148450534074931</v>
+        <v>1.1484497240811</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143146725952025</v>
+        <v>1.14314710365998</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137930885858574</v>
+        <v>1.137933476535249</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13027275652819</v>
+        <v>1.130279093153544</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125150711875978</v>
+        <v>1.125158603154997</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130160119447187</v>
+        <v>1.130177243110722</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137356717303421</v>
+        <v>1.137380930366521</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143627136416915</v>
+        <v>1.143666950746921</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147096130523746</v>
+        <v>1.147142485068643</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147135272268291</v>
+        <v>1.147190640556921</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141432104512133</v>
+        <v>1.141489758562718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13989539490517</v>
+        <v>1.139955724827594</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139828317266384</v>
+        <v>1.139891769752843</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15102793316545</v>
+        <v>1.151069393017763</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166269190413675</v>
+        <v>1.166296920261434</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166687396708289</v>
+        <v>1.166713174882213</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180684195620264</v>
+        <v>1.180688302023069</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191131855687689</v>
+        <v>1.191110882706605</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199254695174609</v>
+        <v>1.199229303961914</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210755298973944</v>
+        <v>1.210717556025211</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205431172383376</v>
+        <v>1.205417151717082</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206059017684455</v>
+        <v>1.206036276250616</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209234460277999</v>
+        <v>1.209186305819968</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214557280544732</v>
+        <v>1.214488481736843</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220538070918338</v>
+        <v>1.220458913962468</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219549154917073</v>
+        <v>1.219487441668672</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207214247343966</v>
+        <v>1.207159199049151</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198983371364891</v>
+        <v>1.198931648144621</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188609574041112</v>
+        <v>1.18857103408415</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180388690889365</v>
+        <v>1.180356426752324</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175329679441252</v>
+        <v>1.175305541623618</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172015395120782</v>
+        <v>1.171999160563651</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173081418190238</v>
+        <v>1.173053933288406</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169320564708654</v>
+        <v>1.169302590634894</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168034587262061</v>
+        <v>1.168013567980204</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167864046394024</v>
+        <v>1.167830760302181</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165842831481493</v>
+        <v>1.165814011300284</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157742835749729</v>
+        <v>1.157720386414319</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151161342403834</v>
+        <v>1.151130804227523</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145605681274011</v>
+        <v>1.146394606099224</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143495771747526</v>
+        <v>1.144013782410803</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144726246081262</v>
+        <v>1.144646530773603</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145430033880649</v>
+        <v>1.145513870239609</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.144366367661978</v>
+        <v>1.144789494675316</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.14208934243515</v>
+        <v>1.142366962637744</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.137336427179652</v>
+        <v>1.137190259776818</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.132578155355384</v>
+        <v>1.132217605417767</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.128007941872201</v>
+        <v>1.127291930205169</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.125340365835495</v>
+        <v>1.124156498518821</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.12387335045545</v>
+        <v>1.123465136947506</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.122642634768737</v>
+        <v>1.124954859691776</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.12662193234203</v>
+        <v>1.127437884978083</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131763737067221</v>
+        <v>1.131608309315189</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.134834806117508</v>
+        <v>1.130401591078802</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.134767022812528</v>
+        <v>1.127225931291624</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136250697167382</v>
+        <v>1.130897283710932</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187108695909618</v>
+        <v>1.187116237318003</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178762224045658</v>
+        <v>1.178774157687098</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177283716890922</v>
+        <v>1.177294055602954</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172785729979471</v>
+        <v>1.172800325178621</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171550985827064</v>
+        <v>1.17156627616793</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169526656797742</v>
+        <v>1.169542450976739</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167057489611634</v>
+        <v>1.167073421255245</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.16531752413064</v>
+        <v>1.165333369579893</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166376009374658</v>
+        <v>1.166386699376032</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161110396892404</v>
+        <v>1.161108785028728</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161585641561253</v>
+        <v>1.161584611278786</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160933333773216</v>
+        <v>1.160932532612944</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16218930127676</v>
+        <v>1.162183471598492</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159775452090028</v>
+        <v>1.15977260351105</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414171695254</v>
+        <v>1.155414309114124</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.1484497240811</v>
+        <v>1.148451327196832</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314710365998</v>
+        <v>1.143146368696382</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137933476535249</v>
+        <v>1.137928382882133</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130279093153544</v>
+        <v>1.130266610183676</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125158603154997</v>
+        <v>1.125143052687941</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130177243110722</v>
+        <v>1.130143488916969</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137380930366521</v>
+        <v>1.137333196034932</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143666950746921</v>
+        <v>1.143588431470652</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147142485068643</v>
+        <v>1.14705106084586</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147190640556921</v>
+        <v>1.147081432853549</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141489758562718</v>
+        <v>1.141376027995455</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139955724827594</v>
+        <v>1.139836701851237</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139891769752843</v>
+        <v>1.139766568572404</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.151069393017763</v>
+        <v>1.150987574427465</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166296920261434</v>
+        <v>1.166242200349047</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166713174882213</v>
+        <v>1.166662296489373</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180688302023069</v>
+        <v>1.18068019030514</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191110882706605</v>
+        <v>1.191152273647599</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199229303961914</v>
+        <v>1.199279410326504</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210717556025211</v>
+        <v>1.210792008024514</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205417151717082</v>
+        <v>1.205444743806612</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206036276250616</v>
+        <v>1.206081058324688</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209186305819968</v>
+        <v>1.209281229471596</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214488481736843</v>
+        <v>1.21462416063811</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220458913962468</v>
+        <v>1.220615030803298</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219487441668672</v>
+        <v>1.219609126438919</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207159199049151</v>
+        <v>1.207267759734385</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198931648144621</v>
+        <v>1.199033665037164</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18857103408415</v>
+        <v>1.188647073387535</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180356426752324</v>
+        <v>1.180420090566959</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175305541623618</v>
+        <v>1.175353173963792</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.171999160563651</v>
+        <v>1.17203119543843</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173053933288406</v>
+        <v>1.173108159890668</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169302590634894</v>
+        <v>1.169338034356185</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168013567980204</v>
+        <v>1.168055015241578</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167830760302181</v>
+        <v>1.167896416717414</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165814011300284</v>
+        <v>1.165870853200849</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157720386414319</v>
+        <v>1.15776464080387</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151130804227523</v>
+        <v>1.151191067851777</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146394606099224</v>
+        <v>1.145634741752963</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144013782410803</v>
+        <v>1.143510320791034</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144646530773603</v>
+        <v>1.144717497296446</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145513870239609</v>
+        <v>1.145780392204041</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.144789494675316</v>
+        <v>1.144771951772193</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.142366962637744</v>
+        <v>1.142489609865156</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.137190259776818</v>
+        <v>1.13765373663816</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.132217605417767</v>
+        <v>1.132997153671659</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.127291930205169</v>
+        <v>1.128507509451139</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.124156498518821</v>
+        <v>1.125899993544062</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.123465136947506</v>
+        <v>1.124432722472292</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.124954859691776</v>
+        <v>1.123182583009728</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.127437884978083</v>
+        <v>1.126480577177126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131608309315189</v>
+        <v>1.132299581291992</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.130401591078802</v>
+        <v>1.135158032258076</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.127225931291624</v>
+        <v>1.13507983233312</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.130897283710932</v>
+        <v>1.136048363849532</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187116237318003</v>
+        <v>1.187112520470019</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178774157687098</v>
+        <v>1.178768275772103</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177294055602954</v>
+        <v>1.177288958982903</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172800325178621</v>
+        <v>1.172793130636717</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17156627616793</v>
+        <v>1.171558739054772</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169542450976739</v>
+        <v>1.169534665589694</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167073421255245</v>
+        <v>1.167065568149056</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165333369579893</v>
+        <v>1.165325558965116</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166386699376032</v>
+        <v>1.166381428178998</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161108785028728</v>
+        <v>1.161109578906534</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161584611278786</v>
+        <v>1.161585118544071</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160932532612944</v>
+        <v>1.160932926966341</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162183471598492</v>
+        <v>1.162186343835015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15977260351105</v>
+        <v>1.159774007107856</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414309114124</v>
+        <v>1.15541424061672</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148451327196832</v>
+        <v>1.148450534074931</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143146368696382</v>
+        <v>1.143146725952025</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137928382882133</v>
+        <v>1.137930885858574</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130266610183676</v>
+        <v>1.13027275652819</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125143052687941</v>
+        <v>1.125150711875978</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130143488916969</v>
+        <v>1.130160119447187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137333196034932</v>
+        <v>1.137356717303421</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143588431470652</v>
+        <v>1.143627136416915</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14705106084586</v>
+        <v>1.147096130523746</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147081432853549</v>
+        <v>1.147135272268291</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141376027995455</v>
+        <v>1.141432104512133</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139836701851237</v>
+        <v>1.13989539490517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139766568572404</v>
+        <v>1.139828317266384</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150987574427465</v>
+        <v>1.15102793316545</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166242200349047</v>
+        <v>1.166269190413675</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166662296489373</v>
+        <v>1.166687396708289</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18068019030514</v>
+        <v>1.180684195620264</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191152273647599</v>
+        <v>1.191131855687689</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199279410326504</v>
+        <v>1.199254695174609</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210792008024514</v>
+        <v>1.210755298973944</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205444743806612</v>
+        <v>1.205431172383376</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206081058324688</v>
+        <v>1.206059017684455</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209281229471596</v>
+        <v>1.209234460277999</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21462416063811</v>
+        <v>1.214557280544732</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220615030803298</v>
+        <v>1.220538070918338</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219609126438919</v>
+        <v>1.219549154917073</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207267759734385</v>
+        <v>1.207214247343966</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199033665037164</v>
+        <v>1.198983371364891</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188647073387535</v>
+        <v>1.188609574041112</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180420090566959</v>
+        <v>1.180388690889365</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175353173963792</v>
+        <v>1.175329679441252</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17203119543843</v>
+        <v>1.172015395120782</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173108159890668</v>
+        <v>1.173081418190238</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169338034356185</v>
+        <v>1.169320564708654</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168055015241578</v>
+        <v>1.168034587262061</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167896416717414</v>
+        <v>1.167864046394024</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165870853200849</v>
+        <v>1.165842831481493</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15776464080387</v>
+        <v>1.157742835749729</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151191067851777</v>
+        <v>1.151161342403834</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145634741752963</v>
+        <v>1.14642380587522</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143510320791034</v>
+        <v>1.144027477325388</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144717497296446</v>
+        <v>1.144639178057493</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145780392204041</v>
+        <v>1.145822564531316</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.144771951772193</v>
+        <v>1.145156121976274</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.142489609865156</v>
+        <v>1.142727176175318</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.13765373663816</v>
+        <v>1.137451920923847</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.132997153671659</v>
+        <v>1.132591198467063</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.128507509451139</v>
+        <v>1.127730904335673</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.125899993544062</v>
+        <v>1.124649618573269</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.124432722472292</v>
+        <v>1.123853317322698</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.123182583009728</v>
+        <v>1.125081290008211</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.126480577177126</v>
+        <v>1.127873470403685</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.132299581291992</v>
+        <v>1.131706555192651</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135158032258076</v>
+        <v>1.13049587776081</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.13507983233312</v>
+        <v>1.127703705270512</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136048363849532</v>
+        <v>1.130538222062507</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187112520470019</v>
+        <v>1.187119850940408</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178768275772103</v>
+        <v>1.178779876838112</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177288958982903</v>
+        <v>1.177299012721118</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172793130636717</v>
+        <v>1.172807322094703</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171558739054772</v>
+        <v>1.171573606075297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169534665589694</v>
+        <v>1.169550022175029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167065568149056</v>
+        <v>1.167081058233284</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165325558965116</v>
+        <v>1.165340965228395</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166381428178998</v>
+        <v>1.166391828906991</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161109578906534</v>
+        <v>1.161108014210713</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161585118544071</v>
+        <v>1.161584119067124</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160932926966341</v>
+        <v>1.16093215015315</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162186343835015</v>
+        <v>1.162180680940582</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159774007107856</v>
+        <v>1.15977123954899</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541424061672</v>
+        <v>1.155414377141429</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148450534074931</v>
+        <v>1.148452103903907</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143146725952025</v>
+        <v>1.143146030639573</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137930885858574</v>
+        <v>1.137925963354966</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13027275652819</v>
+        <v>1.130260645718582</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125150711875978</v>
+        <v>1.125135615530633</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130160119447187</v>
+        <v>1.130127330567003</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137356717303421</v>
+        <v>1.137310337396438</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143627136416915</v>
+        <v>1.14355079025298</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.147096130523746</v>
+        <v>1.14700722345984</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147135272268291</v>
+        <v>1.147029060013446</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141432104512133</v>
+        <v>1.141321465352881</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13989539490517</v>
+        <v>1.139779580210416</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139828317266384</v>
+        <v>1.139706456305539</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15102793316545</v>
+        <v>1.150948273711084</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166269190413675</v>
+        <v>1.166215920948388</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166687396708289</v>
+        <v>1.166637847957647</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180684195620264</v>
+        <v>1.180676282401834</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191131855687689</v>
+        <v>1.191172158235924</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199254695174609</v>
+        <v>1.199303475963786</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210755298973944</v>
+        <v>1.210827725012926</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205431172383376</v>
+        <v>1.205457886857805</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206059017684455</v>
+        <v>1.206102429710057</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209234460277999</v>
+        <v>1.209326672115519</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214557280544732</v>
+        <v>1.214689201013814</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220538070918338</v>
+        <v>1.220689883591836</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219549154917073</v>
+        <v>1.219667428739186</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207214247343966</v>
+        <v>1.207319799406175</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.198983371364891</v>
+        <v>1.199082587384526</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188609574041112</v>
+        <v>1.188683573497377</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180388690889365</v>
+        <v>1.180450659894922</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175329679441252</v>
+        <v>1.175376050481233</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172015395120782</v>
+        <v>1.17204657864922</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173081418190238</v>
+        <v>1.173134188029428</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169320564708654</v>
+        <v>1.169355020432584</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168034587262061</v>
+        <v>1.168074876423407</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167864046394024</v>
+        <v>1.167927908440684</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165842831481493</v>
+        <v>1.165898109116976</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157742835749729</v>
+        <v>1.15778582878614</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151161342403834</v>
+        <v>1.151220012252742</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14642380587522</v>
+        <v>1.145663078328482</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144027477325388</v>
+        <v>1.143524577716547</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144639178057493</v>
+        <v>1.144709105131907</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145822564531316</v>
+        <v>1.146062993205902</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.145156121976274</v>
+        <v>1.145092562843825</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.142727176175318</v>
+        <v>1.142780062779512</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.137451920923847</v>
+        <v>1.137843416689857</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.132591198467063</v>
+        <v>1.133265211644913</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.127730904335673</v>
+        <v>1.128828072246204</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.124649618573269</v>
+        <v>1.12624666258031</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.123853317322698</v>
+        <v>1.124758824453556</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.125081290008211</v>
+        <v>1.123468535606101</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.127873470403685</v>
+        <v>1.126082408813424</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.131706555192651</v>
+        <v>1.132535680485494</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.13049587776081</v>
+        <v>1.135076127336322</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.127703705270512</v>
+        <v>1.134798144116495</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.130538222062507</v>
+        <v>1.134439111011933</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187119850940408</v>
+        <v>1.187123365578297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178779876838112</v>
+        <v>1.178785439888016</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177299012721118</v>
+        <v>1.177303835985313</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172807322094703</v>
+        <v>1.172814129414735</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171573606075297</v>
+        <v>1.171580737202781</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169550022175029</v>
+        <v>1.169557387900834</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167081058233284</v>
+        <v>1.167088487881474</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165340965228395</v>
+        <v>1.165348354661941</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166391828906991</v>
+        <v>1.166396822398969</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161108014210713</v>
+        <v>1.161107265464022</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161584119067124</v>
+        <v>1.161583641251342</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16093215015315</v>
+        <v>1.160931779059979</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162180680940582</v>
+        <v>1.162177968437437</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15977123954899</v>
+        <v>1.159769913568297</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414377141429</v>
+        <v>1.155414444658635</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148452103903907</v>
+        <v>1.148452864641575</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143146030639573</v>
+        <v>1.14314571061837</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137925963354966</v>
+        <v>1.13792362329081</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130260645718582</v>
+        <v>1.130254855216786</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125135615530633</v>
+        <v>1.125128390915411</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130127330567003</v>
+        <v>1.130111624612278</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137310337396438</v>
+        <v>1.137288113836523</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14355079025298</v>
+        <v>1.143514169575968</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14700722345984</v>
+        <v>1.146964568614112</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147029060013446</v>
+        <v>1.146978094779381</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141321465352881</v>
+        <v>1.141268356292836</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139779580210416</v>
+        <v>1.139723967956649</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139706456305539</v>
+        <v>1.139647916586468</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150948273711084</v>
+        <v>1.150909990132349</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166215920948388</v>
+        <v>1.166190324595894</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166637847957647</v>
+        <v>1.16661402617792</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180676282401834</v>
+        <v>1.180672468410225</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191172158235924</v>
+        <v>1.191191529995866</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199303475963786</v>
+        <v>1.199326917266156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210827725012926</v>
+        <v>1.210862489551857</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205457886857805</v>
+        <v>1.205470621152535</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206102429710057</v>
+        <v>1.206123161532306</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209326672115519</v>
+        <v>1.209370843663648</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214689201013814</v>
+        <v>1.214752476399669</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220689883591836</v>
+        <v>1.220762714424972</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219667428739186</v>
+        <v>1.219724130364418</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207319799406175</v>
+        <v>1.20737042613733</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199082587384526</v>
+        <v>1.199130193523268</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188683573497377</v>
+        <v>1.188719113591466</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180450659894922</v>
+        <v>1.180480431221215</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175376050481233</v>
+        <v>1.175398332979798</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17204657864922</v>
+        <v>1.172061560999443</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173134188029428</v>
+        <v>1.17315953069637</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169355020432584</v>
+        <v>1.169371542663453</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168074876423407</v>
+        <v>1.168094193981903</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167927908440684</v>
+        <v>1.167958556753518</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165898109116976</v>
+        <v>1.16592463013512</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15778582878614</v>
+        <v>1.15780642540204</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151220012252742</v>
+        <v>1.15124820568119</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145663078328482</v>
+        <v>1.145690717227175</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143524577716547</v>
+        <v>1.1435385500776</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144709105131907</v>
+        <v>1.144701051016204</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146062993205902</v>
+        <v>1.146491273691959</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.145092562843825</v>
+        <v>1.14557477614161</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.142780062779512</v>
+        <v>1.143270064270187</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.137843416689857</v>
+        <v>1.138346873348635</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.133265211644913</v>
+        <v>1.133823121220499</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.128828072246204</v>
+        <v>1.12946798616435</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.12624666258031</v>
+        <v>1.126947667494521</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.124758824453556</v>
+        <v>1.12547282826825</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.123468535606101</v>
+        <v>1.124175959977941</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.126082408813424</v>
+        <v>1.126243674048668</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.132535680485494</v>
+        <v>1.133356367785233</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135076127336322</v>
+        <v>1.135864284472208</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.134798144116495</v>
+        <v>1.13577761497878</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.134439111011933</v>
+        <v>1.136589246978825</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187123365578297</v>
+        <v>1.187126785243558</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178785439888016</v>
+        <v>1.178790853140958</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177303835985313</v>
+        <v>1.17730853074275</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172814129414735</v>
+        <v>1.17282075473943</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171580737202781</v>
+        <v>1.1715876775257</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169557387900834</v>
+        <v>1.16956455640396</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167088487881474</v>
+        <v>1.1670957185271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165348354661941</v>
+        <v>1.165355546163331</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166396822398969</v>
+        <v>1.16640168518538</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161107265464022</v>
+        <v>1.161106537855789</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161583641251342</v>
+        <v>1.161583177211339</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160931779059979</v>
+        <v>1.160931418836983</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162177968437437</v>
+        <v>1.162175330854005</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159769913568297</v>
+        <v>1.159768624006189</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414444658635</v>
+        <v>1.155414511631129</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148452864641575</v>
+        <v>1.148453609843469</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314571061837</v>
+        <v>1.143145407552255</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.13792362329081</v>
+        <v>1.137921358948126</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130254855216786</v>
+        <v>1.130249231213041</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125128390915411</v>
+        <v>1.125121369885304</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130111624612278</v>
+        <v>1.13009635235572</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137288113836523</v>
+        <v>1.137266499307177</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143514169575968</v>
+        <v>1.143478528554736</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146964568614112</v>
+        <v>1.146923049194048</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146978094779381</v>
+        <v>1.146928481294348</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141268356292836</v>
+        <v>1.141216643672885</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139723967956649</v>
+        <v>1.139669806272507</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139647916586468</v>
+        <v>1.139590888800585</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150909990132349</v>
+        <v>1.150872684877085</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166190324595894</v>
+        <v>1.166165385083671</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16661402617792</v>
+        <v>1.166590807464655</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180672468410225</v>
+        <v>1.180668744995556</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191191529995866</v>
+        <v>1.191210408433676</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199326917266156</v>
+        <v>1.199349758133281</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210862489551857</v>
+        <v>1.210896339176165</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205470621152535</v>
+        <v>1.20548296514291</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206123161532306</v>
+        <v>1.206143281768387</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209370843663648</v>
+        <v>1.209413796531542</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214752476399669</v>
+        <v>1.214814057538423</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220762714424972</v>
+        <v>1.220833603929653</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219724130364418</v>
+        <v>1.219779296168525</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20737042613733</v>
+        <v>1.20741969652401</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199130193523268</v>
+        <v>1.199176535666536</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188719113591466</v>
+        <v>1.188753730874993</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180480431221215</v>
+        <v>1.180509435243622</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175398332979798</v>
+        <v>1.175420044224581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172061560999443</v>
+        <v>1.172076157905428</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17315953069637</v>
+        <v>1.173184214531095</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169371542663453</v>
+        <v>1.169387619720046</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168094193981903</v>
+        <v>1.168112989849842</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167958556753518</v>
+        <v>1.167988394996493</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16592463013512</v>
+        <v>1.165950445523013</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15780642540204</v>
+        <v>1.157826454955213</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15124820568119</v>
+        <v>1.15127567670398</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145690717227175</v>
+        <v>1.14571768345087</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.1435385500776</v>
+        <v>1.143552245248583</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144701051016204</v>
+        <v>1.144693317551299</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146491273691959</v>
+        <v>1.146891944048619</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14557477614161</v>
+        <v>1.146053052983719</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.143270064270187</v>
+        <v>1.143771391682218</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.138346873348635</v>
+        <v>1.13898325092093</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.133823121220499</v>
+        <v>1.134571927264502</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.12946798616435</v>
+        <v>1.13037835499378</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.126947667494521</v>
+        <v>1.128006832398616</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.12547282826825</v>
+        <v>1.126600148810373</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.124175959977941</v>
+        <v>1.125339318444975</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.126243674048668</v>
+        <v>1.127070501551817</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.133356367785233</v>
+        <v>1.13377362394448</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135864284472208</v>
+        <v>1.136078363845713</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.13577761497878</v>
+        <v>1.135919907158524</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136589246978825</v>
+        <v>1.136310096137989</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187126785243558</v>
+        <v>1.187130113734177</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178790853140958</v>
+        <v>1.178796122566179</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17730853074275</v>
+        <v>1.177313102059683</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.17282075473943</v>
+        <v>1.172827205268721</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.1715876775257</v>
+        <v>1.171594434598494</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16956455640396</v>
+        <v>1.169571535498539</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.1670957185271</v>
+        <v>1.167102758057524</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165355546163331</v>
+        <v>1.165362547577777</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16640168518538</v>
+        <v>1.166406422324841</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161106537855789</v>
+        <v>1.161105830504903</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161583177211339</v>
+        <v>1.161582726362007</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160931418836983</v>
+        <v>1.160931069016068</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162175330854005</v>
+        <v>1.162172765131208</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159768624006189</v>
+        <v>1.159767369384364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414511631129</v>
+        <v>1.155414578029113</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148453609843469</v>
+        <v>1.148454339931405</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143145407552255</v>
+        <v>1.143145120436623</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137921358948126</v>
+        <v>1.137919166811897</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130249231213041</v>
+        <v>1.130243766661453</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125121369885304</v>
+        <v>1.12511454397838</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.13009635235572</v>
+        <v>1.130081496114562</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137266499307177</v>
+        <v>1.137245469162826</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143478528554736</v>
+        <v>1.143443828456197</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146923049194048</v>
+        <v>1.146882620549915</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146928481294348</v>
+        <v>1.14688016661089</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141216643672885</v>
+        <v>1.141166273297472</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139669806272507</v>
+        <v>1.139617039345246</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139590888800585</v>
+        <v>1.139535315393235</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150872684877085</v>
+        <v>1.150836321072216</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166165385083671</v>
+        <v>1.166141077523448</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166590807464655</v>
+        <v>1.166568169305086</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180668744995556</v>
+        <v>1.180665108978792</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191210408433676</v>
+        <v>1.191228812082959</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199349758133281</v>
+        <v>1.199372021264797</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210896339176165</v>
+        <v>1.21092930947715</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20548296514291</v>
+        <v>1.205494936201632</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206143281768387</v>
+        <v>1.206162816801529</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209413796531542</v>
+        <v>1.20945558030108</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214814057538423</v>
+        <v>1.214874011449378</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220833603929653</v>
+        <v>1.220902628513213</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219779296168525</v>
+        <v>1.219832987557492</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20741969652401</v>
+        <v>1.207467664188801</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199176535666536</v>
+        <v>1.199221663312247</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188753730874993</v>
+        <v>1.188787460664649</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180509435243622</v>
+        <v>1.180537701113086</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175420044224581</v>
+        <v>1.17544120583599</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172076157905428</v>
+        <v>1.172090384005678</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173184214531095</v>
+        <v>1.173208264815027</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169387619720046</v>
+        <v>1.169403269288522</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168112989849842</v>
+        <v>1.168131284800169</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167988394996493</v>
+        <v>1.168017454780617</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165950445523013</v>
+        <v>1.165975583017693</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157826454955213</v>
+        <v>1.157845940441315</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15127567670398</v>
+        <v>1.151302452472529</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14571768345087</v>
+        <v>1.145744000845421</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143552245248583</v>
+        <v>1.14356567042235</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144693317551299</v>
+        <v>1.144685888425859</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146891944048619</v>
+        <v>1.147275611151766</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.146053052983719</v>
+        <v>1.146503385945671</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.143771391682218</v>
+        <v>1.144242387420994</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.13898325092093</v>
+        <v>1.13958167092957</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.134571927264502</v>
+        <v>1.135267307285459</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.13037835499378</v>
+        <v>1.131222388847271</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.128006832398616</v>
+        <v>1.128981315628685</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.126600148810373</v>
+        <v>1.127633551321904</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.125339318444975</v>
+        <v>1.126400991048223</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.127070501551817</v>
+        <v>1.127811162768235</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.13377362394448</v>
+        <v>1.134126906040642</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.136078363845713</v>
+        <v>1.136235618407162</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135919907158524</v>
+        <v>1.135999143190556</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136310096137989</v>
+        <v>1.136048532834905</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187130113734177</v>
+        <v>1.187119850940408</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178796122566179</v>
+        <v>1.178779876838112</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177313102059683</v>
+        <v>1.177299012721118</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172827205268721</v>
+        <v>1.172807322094703</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171594434598494</v>
+        <v>1.171573606075297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169571535498539</v>
+        <v>1.169550022175029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167102758057524</v>
+        <v>1.167081058233284</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165362547577777</v>
+        <v>1.165340965228395</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166406422324841</v>
+        <v>1.166391828906991</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161105830504903</v>
+        <v>1.161108014210713</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161582726362007</v>
+        <v>1.161584119067124</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160931069016068</v>
+        <v>1.16093215015315</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162172765131208</v>
+        <v>1.162180680940582</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159767369384364</v>
+        <v>1.15977123954899</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414578029113</v>
+        <v>1.155414377141429</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148454339931405</v>
+        <v>1.148452103903907</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143145120436623</v>
+        <v>1.143146030639573</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137919166811897</v>
+        <v>1.137925963354966</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130243766661453</v>
+        <v>1.130260645718582</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12511454397838</v>
+        <v>1.125135615530633</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130081496114562</v>
+        <v>1.130127330567003</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137245469162826</v>
+        <v>1.137310337396438</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143443828456197</v>
+        <v>1.14355079025298</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146882620549915</v>
+        <v>1.14700722345984</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14688016661089</v>
+        <v>1.147029060013446</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141166273297472</v>
+        <v>1.141321465352881</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139617039345246</v>
+        <v>1.139779580210416</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139535315393235</v>
+        <v>1.139706456305539</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150836321072216</v>
+        <v>1.150948273711084</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166141077523448</v>
+        <v>1.166215920948388</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166568169305086</v>
+        <v>1.166637847957647</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180665108978792</v>
+        <v>1.180676282401834</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191228812082959</v>
+        <v>1.191172158235924</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199372021264797</v>
+        <v>1.199303475963786</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21092930947715</v>
+        <v>1.210827725012926</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205494936201632</v>
+        <v>1.205457886857805</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206162816801529</v>
+        <v>1.206102429710057</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20945558030108</v>
+        <v>1.209326672115519</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214874011449378</v>
+        <v>1.214689201013814</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220902628513213</v>
+        <v>1.220689883591836</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219832987557492</v>
+        <v>1.219667428739186</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207467664188801</v>
+        <v>1.207319799406175</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199221663312247</v>
+        <v>1.199082587384526</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188787460664649</v>
+        <v>1.188683573497377</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180537701113086</v>
+        <v>1.180450659894922</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17544120583599</v>
+        <v>1.175376050481233</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172090384005678</v>
+        <v>1.17204657864922</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173208264815027</v>
+        <v>1.173134188029428</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169403269288522</v>
+        <v>1.169355020432584</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168131284800169</v>
+        <v>1.168074876423407</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168017454780617</v>
+        <v>1.167927908440684</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165975583017693</v>
+        <v>1.165898109116976</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157845940441315</v>
+        <v>1.15778582878614</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151302452472529</v>
+        <v>1.151220012252742</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145744000845421</v>
+        <v>1.146479999997208</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14356567042235</v>
+        <v>1.144054065878187</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144685888425859</v>
+        <v>1.144625433755782</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147275611151766</v>
+        <v>1.14625918448275</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.146503385945671</v>
+        <v>1.146181805171833</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.144242387420994</v>
+        <v>1.143878600467297</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.13958167092957</v>
+        <v>1.138798145385759</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.135267307285459</v>
+        <v>1.13388852685947</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.131222388847271</v>
+        <v>1.129393078558358</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.128981315628685</v>
+        <v>1.126452101437594</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.127633551321904</v>
+        <v>1.125606678472913</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.126400991048223</v>
+        <v>1.126523726896747</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.127811162768235</v>
+        <v>1.129386641328125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.134126906040642</v>
+        <v>1.133710738973986</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.136235618407162</v>
+        <v>1.133072104231555</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135999143190556</v>
+        <v>1.132083114227445</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136048532834905</v>
+        <v>1.137898190741099</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B117">
+        <v>1.156657372388302</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187119850940408</v>
+        <v>1.187133354648306</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178779876838112</v>
+        <v>1.178801253819965</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177299012721118</v>
+        <v>1.177317554739612</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172807322094703</v>
+        <v>1.172833487827817</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171573606075297</v>
+        <v>1.171601015582122</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169550022175029</v>
+        <v>1.169578332591403</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167081058233284</v>
+        <v>1.16710961394885</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165340965228395</v>
+        <v>1.165369366341417</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166391828906991</v>
+        <v>1.166411038618618</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161108014210713</v>
+        <v>1.161105142578473</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161584119067124</v>
+        <v>1.161582288150808</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16093215015315</v>
+        <v>1.160930729155514</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162180680940582</v>
+        <v>1.16217026837414</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15977123954899</v>
+        <v>1.159766148303372</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414377141429</v>
+        <v>1.155414643827089</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148452103903907</v>
+        <v>1.148455055315425</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143146030639573</v>
+        <v>1.1431448483366</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137925963354966</v>
+        <v>1.137917043576998</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130260645718582</v>
+        <v>1.130238454906545</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125135615530633</v>
+        <v>1.125107905194088</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130127330567003</v>
+        <v>1.130067039152612</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137310337396438</v>
+        <v>1.137225000067383</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14355079025298</v>
+        <v>1.143410032559551</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14700722345984</v>
+        <v>1.146843240338097</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.147029060013446</v>
+        <v>1.146833100504562</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141321465352881</v>
+        <v>1.141117193730994</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139779580210416</v>
+        <v>1.139565614178148</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139706456305539</v>
+        <v>1.139481141680064</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150948273711084</v>
+        <v>1.150800863666513</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166215920948388</v>
+        <v>1.166117378264817</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166637847957647</v>
+        <v>1.166546090287897</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180676282401834</v>
+        <v>1.180661557327638</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191172158235924</v>
+        <v>1.191246758564275</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199303475963786</v>
+        <v>1.199393728234401</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210827725012926</v>
+        <v>1.21096143422654</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205457886857805</v>
+        <v>1.205506550698946</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206102429710057</v>
+        <v>1.206181791532273</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209326672115519</v>
+        <v>1.20949624190882</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214689201013814</v>
+        <v>1.214932401669707</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220689883591836</v>
+        <v>1.220969860635146</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219667428739186</v>
+        <v>1.219885262714938</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207319799406175</v>
+        <v>1.207514379972871</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199082587384526</v>
+        <v>1.199265623416641</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188683573497377</v>
+        <v>1.188820336506326</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180450659894922</v>
+        <v>1.180565256529422</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175376050481233</v>
+        <v>1.175461838360558</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17204657864922</v>
+        <v>1.172104253209137</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173134188029428</v>
+        <v>1.173231705556581</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169355020432584</v>
+        <v>1.169418508133823</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168074876423407</v>
+        <v>1.168149098521382</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167927908440684</v>
+        <v>1.16804576609773</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165898109116976</v>
+        <v>1.166000068924081</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15778582878614</v>
+        <v>1.157864903634477</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151220012252742</v>
+        <v>1.151328558808375</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146479999997208</v>
+        <v>1.145769692165084</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144054065878187</v>
+        <v>1.143578832609069</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144625433755782</v>
+        <v>1.144678748335854</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.14625918448275</v>
+        <v>1.147251460035885</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.146181805171833</v>
+        <v>1.146922612015937</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.143878600467297</v>
+        <v>1.144788181489744</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.138798145385759</v>
+        <v>1.140245531093502</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.13388852685947</v>
+        <v>1.135932911523472</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.129393078558358</v>
+        <v>1.132106538082138</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.126452101437594</v>
+        <v>1.129934989079829</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.125606678472913</v>
+        <v>1.128681998746047</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.126523726896747</v>
+        <v>1.127489535587457</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.129386641328125</v>
+        <v>1.128804105956691</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.133710738973986</v>
+        <v>1.134620485868881</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.133072104231555</v>
+        <v>1.136684063205881</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.132083114227445</v>
+        <v>1.136625751878853</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.137898190741099</v>
+        <v>1.137165516299494</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.156657372388302</v>
+        <v>1.156665516299494</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187133354648306</v>
+        <v>1.187123365578297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178801253819965</v>
+        <v>1.178785439888016</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177317554739612</v>
+        <v>1.177303835985313</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172833487827817</v>
+        <v>1.172814129414735</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171601015582122</v>
+        <v>1.171580737202781</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169578332591403</v>
+        <v>1.169557387900834</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.16710961394885</v>
+        <v>1.167088487881474</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165369366341417</v>
+        <v>1.165348354661941</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166411038618618</v>
+        <v>1.166396822398969</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161105142578473</v>
+        <v>1.161107265464022</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161582288150808</v>
+        <v>1.161583641251342</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160930729155514</v>
+        <v>1.160931779059979</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16217026837414</v>
+        <v>1.162177968437437</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159766148303372</v>
+        <v>1.159769913568297</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414643827089</v>
+        <v>1.155414444658635</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148455055315425</v>
+        <v>1.148452864641575</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.1431448483366</v>
+        <v>1.14314571061837</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137917043576998</v>
+        <v>1.13792362329081</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130238454906545</v>
+        <v>1.130254855216786</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125107905194088</v>
+        <v>1.125128390915411</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130067039152612</v>
+        <v>1.130111624612278</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137225000067383</v>
+        <v>1.137288113836523</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143410032559551</v>
+        <v>1.143514169575968</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146843240338097</v>
+        <v>1.146964568614112</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146833100504562</v>
+        <v>1.146978094779381</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141117193730994</v>
+        <v>1.141268356292836</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139565614178148</v>
+        <v>1.139723967956649</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139481141680064</v>
+        <v>1.139647916586468</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150800863666513</v>
+        <v>1.150909990132349</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166117378264817</v>
+        <v>1.166190324595894</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166546090287897</v>
+        <v>1.16661402617792</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180661557327638</v>
+        <v>1.180672468410225</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191246758564275</v>
+        <v>1.191191529995866</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199393728234401</v>
+        <v>1.199326917266156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21096143422654</v>
+        <v>1.210862489551857</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205506550698946</v>
+        <v>1.205470621152535</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206181791532273</v>
+        <v>1.206123161532306</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20949624190882</v>
+        <v>1.209370843663648</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214932401669707</v>
+        <v>1.214752476399669</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220969860635146</v>
+        <v>1.220762714424972</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219885262714938</v>
+        <v>1.219724130364418</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207514379972871</v>
+        <v>1.20737042613733</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199265623416641</v>
+        <v>1.199130193523268</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188820336506326</v>
+        <v>1.188719113591466</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180565256529422</v>
+        <v>1.180480431221215</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175461838360558</v>
+        <v>1.175398332979798</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172104253209137</v>
+        <v>1.172061560999443</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173231705556581</v>
+        <v>1.17315953069637</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169418508133823</v>
+        <v>1.169371542663453</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168149098521382</v>
+        <v>1.168094193981903</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16804576609773</v>
+        <v>1.167958556753518</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166000068924081</v>
+        <v>1.16592463013512</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157864903634477</v>
+        <v>1.15780642540204</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151328558808375</v>
+        <v>1.15124820568119</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145769692165084</v>
+        <v>1.146507048294433</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143578832609069</v>
+        <v>1.144066972455855</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144678748335854</v>
+        <v>1.144619007609541</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147251460035885</v>
+        <v>1.146237661771356</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.146922612015937</v>
+        <v>1.146756393883985</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.144788181489744</v>
+        <v>1.144556186216757</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.140245531093502</v>
+        <v>1.139650719440082</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.135932911523472</v>
+        <v>1.134650579378105</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.132106538082138</v>
+        <v>1.130470567102908</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.129934989079829</v>
+        <v>1.127598649573503</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.128681998746047</v>
+        <v>1.126806338443895</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.127489535587457</v>
+        <v>1.127676769351993</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.128804105956691</v>
+        <v>1.130390065881281</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.134620485868881</v>
+        <v>1.135262623134559</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.136684063205881</v>
+        <v>1.135043455989399</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.136625751878853</v>
+        <v>1.135069586404431</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.137165516299494</v>
+        <v>1.142395243030832</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.156665516299494</v>
+        <v>1.161082064320185</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187123365578297</v>
+        <v>1.187136511397233</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178785439888016</v>
+        <v>1.178806252265881</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177303835985313</v>
+        <v>1.177321893340092</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172814129414735</v>
+        <v>1.172839608891267</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171580737202781</v>
+        <v>1.171607427269343</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169557387900834</v>
+        <v>1.169584954708273</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167088487881474</v>
+        <v>1.167116293292378</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165348354661941</v>
+        <v>1.165376009507624</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166396822398969</v>
+        <v>1.166415538626763</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161107265464022</v>
+        <v>1.161104473288578</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161583641251342</v>
+        <v>1.161581862055541</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160931779059979</v>
+        <v>1.160930398838146</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162177968437437</v>
+        <v>1.162167837841215</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159769913568297</v>
+        <v>1.159764959437433</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414444658635</v>
+        <v>1.1554147090034</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148452864641575</v>
+        <v>1.148455756393888</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314571061837</v>
+        <v>1.143144590381448</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.13792362329081</v>
+        <v>1.137914986132998</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130254855216786</v>
+        <v>1.130233289656684</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125128390915411</v>
+        <v>1.125101445962307</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130111624612278</v>
+        <v>1.130052965617859</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137288113836523</v>
+        <v>1.137205069908578</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143514169575968</v>
+        <v>1.143377106027468</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146964568614112</v>
+        <v>1.146804868374407</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146978094779381</v>
+        <v>1.146787235301523</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141268356292836</v>
+        <v>1.141069356124868</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139723967956649</v>
+        <v>1.139515480415849</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139647916586468</v>
+        <v>1.139428315671227</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150909990132349</v>
+        <v>1.15076627931998</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166190324595894</v>
+        <v>1.166094264819466</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16661402617792</v>
+        <v>1.166524550037028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180672468410225</v>
+        <v>1.180658087148176</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191191529995866</v>
+        <v>1.191264264640432</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199326917266156</v>
+        <v>1.199414899558553</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210862489551857</v>
+        <v>1.210992745491132</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205470621152535</v>
+        <v>1.205517824073158</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206123161532306</v>
+        <v>1.206200229480408</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209370843663648</v>
+        <v>1.209535825819581</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214752476399669</v>
+        <v>1.214989288477283</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220762714424972</v>
+        <v>1.221035369058193</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219724130364418</v>
+        <v>1.219936176810237</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20737042613733</v>
+        <v>1.207559892113473</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199130193523268</v>
+        <v>1.199308460554755</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188719113591466</v>
+        <v>1.188852390284162</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180480431221215</v>
+        <v>1.180592127830048</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175398332979798</v>
+        <v>1.175481961336566</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172061560999443</v>
+        <v>1.17211777873993</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17315953069637</v>
+        <v>1.173254559570029</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169371542663453</v>
+        <v>1.169433352158671</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168094193981903</v>
+        <v>1.168166449687141</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167958556753518</v>
+        <v>1.16807335742259</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16592463013512</v>
+        <v>1.166023928206055</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15780642540204</v>
+        <v>1.157883365167023</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15124820568119</v>
+        <v>1.151354020282704</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146507048294433</v>
+        <v>1.145794779132774</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144066972455855</v>
+        <v>1.143591738636102</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144619007609541</v>
+        <v>1.144671882911759</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146237661771356</v>
+        <v>1.147227973535501</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.146756393883985</v>
+        <v>1.147421030629979</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.144556186216757</v>
+        <v>1.145412710193638</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.139650719440082</v>
+        <v>1.141018602300492</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.134650579378105</v>
+        <v>1.136755727928065</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.130470567102908</v>
+        <v>1.133102715355117</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.127598649573503</v>
+        <v>1.131122483095004</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.126806338443895</v>
+        <v>1.130000435297289</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.127676769351993</v>
+        <v>1.128905872746053</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.130390065881281</v>
+        <v>1.130198924078022</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.135262623134559</v>
+        <v>1.135756014277295</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135043455989399</v>
+        <v>1.138007768060124</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135069586404431</v>
+        <v>1.138393820026082</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.142395243030832</v>
+        <v>1.140146260790785</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.161082064320185</v>
+        <v>1.159646260790785</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187136511397233</v>
+        <v>1.187126785243558</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178806252265881</v>
+        <v>1.178790853140958</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177321893340092</v>
+        <v>1.17730853074275</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172839608891267</v>
+        <v>1.17282075473943</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171607427269343</v>
+        <v>1.1715876775257</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169584954708273</v>
+        <v>1.16956455640396</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167116293292378</v>
+        <v>1.1670957185271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165376009507624</v>
+        <v>1.165355546163331</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166415538626763</v>
+        <v>1.16640168518538</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161104473288578</v>
+        <v>1.161106537855789</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161581862055541</v>
+        <v>1.161583177211339</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160930398838146</v>
+        <v>1.160931418836983</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162167837841215</v>
+        <v>1.162175330854005</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159764959437433</v>
+        <v>1.159768624006189</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.1554147090034</v>
+        <v>1.155414511631129</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148455756393888</v>
+        <v>1.148453609843469</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143144590381448</v>
+        <v>1.143145407552255</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137914986132998</v>
+        <v>1.137921358948126</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130233289656684</v>
+        <v>1.130249231213041</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125101445962307</v>
+        <v>1.125121369885304</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130052965617859</v>
+        <v>1.13009635235572</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137205069908578</v>
+        <v>1.137266499307177</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143377106027468</v>
+        <v>1.143478528554736</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146804868374407</v>
+        <v>1.146923049194048</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146787235301523</v>
+        <v>1.146928481294348</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141069356124868</v>
+        <v>1.141216643672885</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139515480415849</v>
+        <v>1.139669806272507</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139428315671227</v>
+        <v>1.139590888800585</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15076627931998</v>
+        <v>1.150872684877085</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166094264819466</v>
+        <v>1.166165385083671</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166524550037028</v>
+        <v>1.166590807464655</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180658087148176</v>
+        <v>1.180668744995556</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191264264640432</v>
+        <v>1.191210408433676</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199414899558553</v>
+        <v>1.199349758133281</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210992745491132</v>
+        <v>1.210896339176165</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205517824073158</v>
+        <v>1.20548296514291</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206200229480408</v>
+        <v>1.206143281768387</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209535825819581</v>
+        <v>1.209413796531542</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214989288477283</v>
+        <v>1.214814057538423</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221035369058193</v>
+        <v>1.220833603929653</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219936176810237</v>
+        <v>1.219779296168525</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207559892113473</v>
+        <v>1.20741969652401</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199308460554755</v>
+        <v>1.199176535666536</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188852390284162</v>
+        <v>1.188753730874993</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180592127830048</v>
+        <v>1.180509435243622</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175481961336566</v>
+        <v>1.175420044224581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17211777873993</v>
+        <v>1.172076157905428</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173254559570029</v>
+        <v>1.173184214531095</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169433352158671</v>
+        <v>1.169387619720046</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168166449687141</v>
+        <v>1.168112989849842</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16807335742259</v>
+        <v>1.167988394996493</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166023928206055</v>
+        <v>1.165950445523013</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157883365167023</v>
+        <v>1.157826454955213</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151354020282704</v>
+        <v>1.15127567670398</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145794779132774</v>
+        <v>1.146533431250854</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143591738636102</v>
+        <v>1.144079628998399</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144671882911759</v>
+        <v>1.144612857624439</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147227973535501</v>
+        <v>1.146216778891952</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.147421030629979</v>
+        <v>1.147615788434551</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.145412710193638</v>
+        <v>1.145606080037312</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.141018602300492</v>
+        <v>1.140948335053686</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.136755727928065</v>
+        <v>1.136125227514353</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.133102715355117</v>
+        <v>1.132331982347524</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.131122483095004</v>
+        <v>1.129527746002617</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.130000435297289</v>
+        <v>1.128881170646053</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.128905872746053</v>
+        <v>1.129814628482625</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.130198924078022</v>
+        <v>1.13253802101108</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.135756014277295</v>
+        <v>1.137435680768751</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.138007768060124</v>
+        <v>1.138225722788621</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.138393820026082</v>
+        <v>1.139592676964912</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.140146260790785</v>
+        <v>1.149066823909133</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.159646260790785</v>
+        <v>1.170635868206222</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187126785243558</v>
+        <v>1.187139587217357</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178790853140958</v>
+        <v>1.178811122993468</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17730853074275</v>
+        <v>1.17732612218827</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.17282075473943</v>
+        <v>1.172845574605183</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.1715876775257</v>
+        <v>1.171613676108069</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16956455640396</v>
+        <v>1.169591408517951</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.1670957185271</v>
+        <v>1.167122802819036</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165355546163331</v>
+        <v>1.165382483771317</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16640168518538</v>
+        <v>1.166419926683053</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161106537855789</v>
+        <v>1.161103821889279</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161583177211339</v>
+        <v>1.161581447582297</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160931418836983</v>
+        <v>1.160930077669658</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162175330854005</v>
+        <v>1.162165470934151</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159768624006189</v>
+        <v>1.159763801529659</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414511631129</v>
+        <v>1.155414773539827</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148453609843469</v>
+        <v>1.148456443553608</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143145407552255</v>
+        <v>1.143144345759468</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137921358948126</v>
+        <v>1.137912991550246</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130249231213041</v>
+        <v>1.130228264959637</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125121369885304</v>
+        <v>1.125095159114846</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.13009635235572</v>
+        <v>1.130039260484947</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137266499307177</v>
+        <v>1.137185657718913</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143478528554736</v>
+        <v>1.14334501578704</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146923049194048</v>
+        <v>1.146767466498431</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146928481294348</v>
+        <v>1.146742525719034</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141216643672885</v>
+        <v>1.141022714057417</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139669806272507</v>
+        <v>1.139466590182441</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139590888800585</v>
+        <v>1.139376787908284</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150872684877085</v>
+        <v>1.150732536301163</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166165385083671</v>
+        <v>1.166071715790888</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166590807464655</v>
+        <v>1.166503529150154</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180668744995556</v>
+        <v>1.180654695677069</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191210408433676</v>
+        <v>1.191281346267824</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199349758133281</v>
+        <v>1.19943555476022</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210896339176165</v>
+        <v>1.211023273738877</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20548296514291</v>
+        <v>1.205528770895326</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206143281768387</v>
+        <v>1.206218152878667</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209413796531542</v>
+        <v>1.209574374186567</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214814057538423</v>
+        <v>1.215044729096647</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.220833603929653</v>
+        <v>1.221099219080557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219779296168525</v>
+        <v>1.219985782190754</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20741969652401</v>
+        <v>1.207604246408056</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199176535666536</v>
+        <v>1.199350217068929</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188753730874993</v>
+        <v>1.188883652321681</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180509435243622</v>
+        <v>1.180618340072322</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175420044224581</v>
+        <v>1.175501593354942</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172076157905428</v>
+        <v>1.17213097317885</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173184214531095</v>
+        <v>1.173276848548591</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169387619720046</v>
+        <v>1.169447816458101</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168112989849842</v>
+        <v>1.168183356020601</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.167988394996493</v>
+        <v>1.16810025580734</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.165950445523013</v>
+        <v>1.166047184570675</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157826454955213</v>
+        <v>1.15790134460305</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15127567670398</v>
+        <v>1.151378860290297</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146533431250854</v>
+        <v>1.145819282496497</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144079628998399</v>
+        <v>1.143604395148748</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144612857624439</v>
+        <v>1.144665278651755</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146216778891952</v>
+        <v>1.147205125544418</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.147615788434551</v>
+        <v>1.148187449169539</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.145606080037312</v>
+        <v>1.146382220370781</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.140948335053686</v>
+        <v>1.142223336578222</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.136125227514353</v>
+        <v>1.138221703296132</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.132331982347524</v>
+        <v>1.134652926119684</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.129527746002617</v>
+        <v>1.132910941051456</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.128881170646053</v>
+        <v>1.13196152645035</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.129814628482625</v>
+        <v>1.131013629840656</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.13253802101108</v>
+        <v>1.132375640775551</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.137435680768751</v>
+        <v>1.137945975066929</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.138225722788621</v>
+        <v>1.140684906535125</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.139592676964912</v>
+        <v>1.14181788251141</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.149066823909133</v>
+        <v>1.145558549834836</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.170635868206222</v>
+        <v>1.171051806064857</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187139587217357</v>
+        <v>1.187142585181255</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178811122993468</v>
+        <v>1.17881587083552</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17732612218827</v>
+        <v>1.177330245395259</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172845574605183</v>
+        <v>1.172851390807801</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171613676108069</v>
+        <v>1.171619768222976</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169591408517951</v>
+        <v>1.169597700354697</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167122802819036</v>
+        <v>1.167129148921979</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165382483771317</v>
+        <v>1.165388795491441</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166419926683053</v>
+        <v>1.166424206908834</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161103821889279</v>
+        <v>1.161103187673858</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161581447582297</v>
+        <v>1.161581044263571</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160930077669658</v>
+        <v>1.160929765277079</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162165470934151</v>
+        <v>1.162163165188735</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159763801529659</v>
+        <v>1.159762673387638</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414773539827</v>
+        <v>1.155414837421216</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148456443553608</v>
+        <v>1.148457117170031</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143144345759468</v>
+        <v>1.143144113713377</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137912991550246</v>
+        <v>1.137911057067122</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130228264959637</v>
+        <v>1.130223375180069</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125095159114846</v>
+        <v>1.125089037859176</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130039260484947</v>
+        <v>1.130025909502074</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137185657718913</v>
+        <v>1.137166743602659</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14334501578704</v>
+        <v>1.143313730419622</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146767466498431</v>
+        <v>1.146730998447949</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146742525719034</v>
+        <v>1.146698928717746</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141022714057417</v>
+        <v>1.14097722338544</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139466590182441</v>
+        <v>1.139418897931303</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139376787908284</v>
+        <v>1.139326511312742</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150732536301163</v>
+        <v>1.150699604391729</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166071715790888</v>
+        <v>1.166049710809113</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166503529150154</v>
+        <v>1.166483009141496</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180654695677069</v>
+        <v>1.180651380274283</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191281346267824</v>
+        <v>1.191298018644152</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19943555476022</v>
+        <v>1.199455712428084</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211023273738877</v>
+        <v>1.21105304793716</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205528770895326</v>
+        <v>1.205539404928695</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206218152878667</v>
+        <v>1.206235582758937</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209574374186567</v>
+        <v>1.20961192699924</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215044729096647</v>
+        <v>1.215098777889573</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221099219080557</v>
+        <v>1.221161472750869</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219985782190754</v>
+        <v>1.220034128559586</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207604246408056</v>
+        <v>1.207647486366162</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199350217068929</v>
+        <v>1.199390933206375</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188883652321681</v>
+        <v>1.188914151475664</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180618340072322</v>
+        <v>1.180643917110006</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175501593354942</v>
+        <v>1.175520752115803</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17213097317885</v>
+        <v>1.172143848501888</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173276848548591</v>
+        <v>1.173298593132244</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169447816458101</v>
+        <v>1.169461915369918</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168183356020601</v>
+        <v>1.168199834353923</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16810025580734</v>
+        <v>1.168126486969026</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166047184570675</v>
+        <v>1.166069860546146</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15790134460305</v>
+        <v>1.157918860506415</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151378860290297</v>
+        <v>1.15140310111836</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145819282496497</v>
+        <v>1.145843222082224</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143604395148748</v>
+        <v>1.143616808611712</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144665278651755</v>
+        <v>1.144658922860366</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147205125544418</v>
+        <v>1.147182891263768</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.148187449169539</v>
+        <v>1.148981380504774</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.146382220370781</v>
+        <v>1.147394462564574</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.142223336578222</v>
+        <v>1.143463490891244</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.138221703296132</v>
+        <v>1.139733652110034</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.134652926119684</v>
+        <v>1.136245214961637</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.132910941051456</v>
+        <v>1.134740916820012</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.13196152645035</v>
+        <v>1.133972887306634</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.131013629840656</v>
+        <v>1.133180718598204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.132375640775551</v>
+        <v>1.134630324727783</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.137945975066929</v>
+        <v>1.140273693872842</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.140684906535125</v>
+        <v>1.14350870012969</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.14181788251141</v>
+        <v>1.145354670327868</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.145558549834836</v>
+        <v>1.150772442565225</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.171051806064857</v>
+        <v>1.177181460263822</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187142585181255</v>
+        <v>1.187145508207915</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17881587083552</v>
+        <v>1.178820500384066</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177330245395259</v>
+        <v>1.177334266869447</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172851390807801</v>
+        <v>1.172857063048515</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171619768222976</v>
+        <v>1.171625709435494</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169597700354697</v>
+        <v>1.169603836238939</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167129148921979</v>
+        <v>1.167135337677514</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165388795491441</v>
+        <v>1.165394950711771</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166424206908834</v>
+        <v>1.166428383225861</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161103187673858</v>
+        <v>1.161102569972285</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161581044263571</v>
+        <v>1.161580651656528</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160929765277079</v>
+        <v>1.160929461307349</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162163165188735</v>
+        <v>1.162160918266295</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159762673387638</v>
+        <v>1.159761573879361</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414837421216</v>
+        <v>1.155414900635159</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148457117170031</v>
+        <v>1.148457777607427</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143144113713377</v>
+        <v>1.143143893536085</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137911057067122</v>
+        <v>1.137909180078332</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130223375180069</v>
+        <v>1.130218614978802</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125089037859176</v>
+        <v>1.125083075754195</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130025909502074</v>
+        <v>1.130012899141927</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137166743602659</v>
+        <v>1.137148308668358</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143313730419622</v>
+        <v>1.143283220058827</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146730998447949</v>
+        <v>1.146695429742582</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146698928717746</v>
+        <v>1.14665640336478</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.14097722338544</v>
+        <v>1.140932842106535</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139418897931303</v>
+        <v>1.13937236030566</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139326511312742</v>
+        <v>1.139277441045277</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150699604391729</v>
+        <v>1.150667454797721</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166049710809113</v>
+        <v>1.166028230470056</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166483009141496</v>
+        <v>1.166462972388574</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180651380274283</v>
+        <v>1.180648138416293</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191298018644152</v>
+        <v>1.191314296252799</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199455712428084</v>
+        <v>1.199475390271582</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21105304793716</v>
+        <v>1.211082095643923</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205539404928695</v>
+        <v>1.205549739183341</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206235582758937</v>
+        <v>1.20625253903169</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20961192699924</v>
+        <v>1.209648522220016</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215098777889573</v>
+        <v>1.215151486531571</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221161472750869</v>
+        <v>1.22122218906739</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220034128559586</v>
+        <v>1.220081263140073</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207647486366162</v>
+        <v>1.207689653350144</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199390933206375</v>
+        <v>1.199430647246738</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188914151475664</v>
+        <v>1.188943915223366</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180643917110006</v>
+        <v>1.18066888166434</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175520752115803</v>
+        <v>1.175539454481014</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172143848501888</v>
+        <v>1.172156416116026</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173298593132244</v>
+        <v>1.173319812970678</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169461915369918</v>
+        <v>1.169475662521438</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168199834353923</v>
+        <v>1.168215900683394</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168126486969026</v>
+        <v>1.168152075370758</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166069860546146</v>
+        <v>1.166091977554069</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157918860506415</v>
+        <v>1.157935930503609</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15140310111836</v>
+        <v>1.151426764010635</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145843222082224</v>
+        <v>1.145866616843451</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143616808611712</v>
+        <v>1.143628985311159</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144658922860366</v>
+        <v>1.144652803592051</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147182891263768</v>
+        <v>1.147161247123598</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.148981380504774</v>
+        <v>1.149728767784776</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.147394462564574</v>
+        <v>1.148335484419966</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.143463490891244</v>
+        <v>1.144597787045313</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.139733652110034</v>
+        <v>1.141089336493496</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.136245214961637</v>
+        <v>1.137654107504206</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.134740916820012</v>
+        <v>1.136389756201488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.133972887306634</v>
+        <v>1.135858841770102</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.133180718598204</v>
+        <v>1.135336500961079</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.134630324727783</v>
+        <v>1.137007190814429</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.140273693872842</v>
+        <v>1.142970622522306</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.14350870012969</v>
+        <v>1.146878501779402</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.145354670327868</v>
+        <v>1.149547999590894</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.150772442565225</v>
+        <v>1.156631809232281</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.177181460263822</v>
+        <v>1.184108288435099</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187145508207915</v>
+        <v>1.187148359072216</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178820500384066</v>
+        <v>1.178825016005181</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177334266869447</v>
+        <v>1.17733819032884</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172857063048515</v>
+        <v>1.172862596605518</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171625709435494</v>
+        <v>1.171631505282346</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169603836238939</v>
+        <v>1.169609821896468</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167135337677514</v>
+        <v>1.167141374864478</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165394950711771</v>
+        <v>1.165400955180198</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166428383225861</v>
+        <v>1.166432459368221</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161102569972285</v>
+        <v>1.161101968148863</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161580651656528</v>
+        <v>1.161580269341399</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160929461307349</v>
+        <v>1.160929165426016</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162160918266295</v>
+        <v>1.162158727945809</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159761573879361</v>
+        <v>1.159760501929441</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414900635159</v>
+        <v>1.155414963171696</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148457777607427</v>
+        <v>1.148458425219125</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143143893536085</v>
+        <v>1.143143684566853</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137909180078332</v>
+        <v>1.137907358124171</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130218614978802</v>
+        <v>1.130213979293678</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125083075754195</v>
+        <v>1.12507726668783</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130012899141927</v>
+        <v>1.130000216556297</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137148308668358</v>
+        <v>1.137130334966352</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143283220058827</v>
+        <v>1.143253456295954</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146695429742582</v>
+        <v>1.14666072757587</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14665640336478</v>
+        <v>1.146614910706696</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140932842106535</v>
+        <v>1.140889530231233</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13937236030566</v>
+        <v>1.139326936009012</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139277441045277</v>
+        <v>1.139229534374793</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150667454797721</v>
+        <v>1.150636060066967</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166028230470056</v>
+        <v>1.166007256279096</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166462972388574</v>
+        <v>1.166443402082629</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180648138416293</v>
+        <v>1.180644967689735</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191314296252799</v>
+        <v>1.19133019290415</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199475390271582</v>
+        <v>1.19949460517211</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211082095643923</v>
+        <v>1.21111044309224</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205549739183341</v>
+        <v>1.205559785966484</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20625253903169</v>
+        <v>1.206269040559206</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209648522220016</v>
+        <v>1.209684195910744</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215151486531571</v>
+        <v>1.215202904175509</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.22122218906739</v>
+        <v>1.221281424162761</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220081263140073</v>
+        <v>1.2201272308282</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207689653350144</v>
+        <v>1.207730786705651</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199430647246738</v>
+        <v>1.199469395620478</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188943915223366</v>
+        <v>1.188972969743606</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18066888166434</v>
+        <v>1.180693255390172</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175539454481014</v>
+        <v>1.175557716523083</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172156416116026</v>
+        <v>1.172168686892532</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173319812970678</v>
+        <v>1.173340526781812</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169475662521438</v>
+        <v>1.169489070872815</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168215900683394</v>
+        <v>1.168231570220506</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168152075370758</v>
+        <v>1.168177044297023</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166091977554069</v>
+        <v>1.166113555976438</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157935930503609</v>
+        <v>1.157952571341966</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151426764010635</v>
+        <v>1.151449869227156</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145866616843451</v>
+        <v>1.145889484907688</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143628985311159</v>
+        <v>1.143640931357259</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144652803592051</v>
+        <v>1.144646909599298</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147161247123598</v>
+        <v>1.147140170709866</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149728767784776</v>
+        <v>1.150336369209498</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.148335484419966</v>
+        <v>1.149103279484553</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.144597787045313</v>
+        <v>1.145549791960059</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.141089336493496</v>
+        <v>1.142064699112304</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.137654107504206</v>
+        <v>1.138786517037999</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.136389756201488</v>
+        <v>1.137721070295278</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.135858841770102</v>
+        <v>1.137394557240778</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.135336500961079</v>
+        <v>1.137106525205555</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.137007190814429</v>
+        <v>1.138955369896277</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.142970622522306</v>
+        <v>1.145117900214633</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.146878501779402</v>
+        <v>1.149504354789802</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.149547999590894</v>
+        <v>1.152747077442874</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.156631809232281</v>
+        <v>1.160754502382762</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.184108288435099</v>
+        <v>1.187265142828077</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187148359072216</v>
+        <v>1.187136511397233</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178825016005181</v>
+        <v>1.178806252265881</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17733819032884</v>
+        <v>1.177321893340092</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172862596605518</v>
+        <v>1.172839608891267</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171631505282346</v>
+        <v>1.171607427269343</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169609821896468</v>
+        <v>1.169584954708273</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167141374864478</v>
+        <v>1.167116293292378</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165400955180198</v>
+        <v>1.165376009507624</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166432459368221</v>
+        <v>1.166415538626763</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161101968148863</v>
+        <v>1.161104473288578</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161580269341399</v>
+        <v>1.161581862055541</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160929165426016</v>
+        <v>1.160930398838146</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162158727945809</v>
+        <v>1.162167837841215</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159760501929441</v>
+        <v>1.159764959437433</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414963171696</v>
+        <v>1.1554147090034</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148458425219125</v>
+        <v>1.148455756393888</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143143684566853</v>
+        <v>1.143144590381448</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137907358124171</v>
+        <v>1.137914986132998</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130213979293678</v>
+        <v>1.130233289656684</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12507726668783</v>
+        <v>1.125101445962307</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130000216556297</v>
+        <v>1.130052965617859</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137130334966352</v>
+        <v>1.137205069908578</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143253456295954</v>
+        <v>1.143377106027468</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14666072757587</v>
+        <v>1.146804868374407</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146614910706696</v>
+        <v>1.146787235301523</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140889530231233</v>
+        <v>1.141069356124868</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139326936009012</v>
+        <v>1.139515480415849</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139229534374793</v>
+        <v>1.139428315671227</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150636060066967</v>
+        <v>1.15076627931998</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166007256279096</v>
+        <v>1.166094264819466</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166443402082629</v>
+        <v>1.166524550037028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180644967689735</v>
+        <v>1.180658087148176</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19133019290415</v>
+        <v>1.191264264640432</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19949460517211</v>
+        <v>1.199414899558553</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21111044309224</v>
+        <v>1.210992745491132</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205559785966484</v>
+        <v>1.205517824073158</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206269040559206</v>
+        <v>1.206200229480408</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209684195910744</v>
+        <v>1.209535825819581</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215202904175509</v>
+        <v>1.214989288477283</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221281424162761</v>
+        <v>1.221035369058193</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.2201272308282</v>
+        <v>1.219936176810237</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207730786705651</v>
+        <v>1.207559892113473</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199469395620478</v>
+        <v>1.199308460554755</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188972969743606</v>
+        <v>1.188852390284162</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180693255390172</v>
+        <v>1.180592127830048</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175557716523083</v>
+        <v>1.175481961336566</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172168686892532</v>
+        <v>1.17211777873993</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173340526781812</v>
+        <v>1.173254559570029</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169489070872815</v>
+        <v>1.169433352158671</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168231570220506</v>
+        <v>1.168166449687141</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168177044297023</v>
+        <v>1.16807335742259</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166113555976438</v>
+        <v>1.166023928206055</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157952571341966</v>
+        <v>1.157883365167023</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151449869227156</v>
+        <v>1.151354020282704</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145889484907688</v>
+        <v>1.146608821454663</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143640931357259</v>
+        <v>1.144116159417613</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144646909599298</v>
+        <v>1.144595923109151</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147140170709866</v>
+        <v>1.146157706097943</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150336369209498</v>
+        <v>1.149179128699105</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.149103279484553</v>
+        <v>1.148265943540261</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.145549791960059</v>
+        <v>1.14434936610788</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.142064699112304</v>
+        <v>1.140086459932395</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.138786517037999</v>
+        <v>1.136880435279348</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.137721070295278</v>
+        <v>1.134652106853813</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.137394557240778</v>
+        <v>1.134237187894742</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.137106525205555</v>
+        <v>1.135225076376702</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.138955369896277</v>
+        <v>1.137877516435231</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.145117900214633</v>
+        <v>1.142775083830522</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.149504354789802</v>
+        <v>1.145288278560262</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.152747077442874</v>
+        <v>1.14877374719662</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.160754502382762</v>
+        <v>1.159810162913643</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.187265142828077</v>
+        <v>1.177710081843028</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B118">
+        <v>1.172233530117813</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187136511397233</v>
+        <v>1.187151140413711</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178806252265881</v>
+        <v>1.178829421852712</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177321893340092</v>
+        <v>1.177342019312506</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172839608891267</v>
+        <v>1.172867996502159</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171607427269343</v>
+        <v>1.171637161032738</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169584954708273</v>
+        <v>1.16961566277624</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167116293292378</v>
+        <v>1.167147265982217</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165376009507624</v>
+        <v>1.165406814366613</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166415538626763</v>
+        <v>1.166436438893413</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161104473288578</v>
+        <v>1.161101381600068</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161581862055541</v>
+        <v>1.161579896920005</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160930398838146</v>
+        <v>1.16092887731603</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162167837841215</v>
+        <v>1.162156592116601</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159764959437433</v>
+        <v>1.159759456515629</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.1554147090034</v>
+        <v>1.155415025023055</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148455756393888</v>
+        <v>1.148459060347746</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143144590381448</v>
+        <v>1.143143486187779</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137914986132998</v>
+        <v>1.137905588880629</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130233289656684</v>
+        <v>1.130209463321876</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125101445962307</v>
+        <v>1.125071604856341</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130052965617859</v>
+        <v>1.129987849534058</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137205069908578</v>
+        <v>1.137112805430914</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143377106027468</v>
+        <v>1.143224412092252</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146804868374407</v>
+        <v>1.146626860715088</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146787235301523</v>
+        <v>1.146574413651515</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141069356124868</v>
+        <v>1.140847249664179</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139515480415849</v>
+        <v>1.139282585684615</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139428315671227</v>
+        <v>1.139182750556509</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15076627931998</v>
+        <v>1.150605394012133</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166094264819466</v>
+        <v>1.165986770598564</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166524550037028</v>
+        <v>1.166424282182391</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180658087148176</v>
+        <v>1.180641865785464</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191264264640432</v>
+        <v>1.191345721774084</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199414899558553</v>
+        <v>1.199513373230707</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.210992745491132</v>
+        <v>1.211138115268885</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205517824073158</v>
+        <v>1.205569556928845</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206200229480408</v>
+        <v>1.206285105223193</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209535825819581</v>
+        <v>1.209718982349874</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.214989288477283</v>
+        <v>1.215253077603434</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221035369058193</v>
+        <v>1.221339231475526</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219936176810237</v>
+        <v>1.220172074333921</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207559892113473</v>
+        <v>1.207770923882736</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199308460554755</v>
+        <v>1.199507213018844</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188852390284162</v>
+        <v>1.189001339992238</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180592127830048</v>
+        <v>1.180717058937517</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175481961336566</v>
+        <v>1.175575553570678</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17211777873993</v>
+        <v>1.172180671197952</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173254559570029</v>
+        <v>1.173360752406216</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169433352158671</v>
+        <v>1.169502152757248</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168166449687141</v>
+        <v>1.168246857439358</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16807335742259</v>
+        <v>1.168201415923655</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166023928206055</v>
+        <v>1.166134615217852</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157883365167023</v>
+        <v>1.157968798943608</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151354020282704</v>
+        <v>1.151472436099995</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146608821454663</v>
+        <v>1.145911843620081</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144116159417613</v>
+        <v>1.14365265268713</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144595923109151</v>
+        <v>1.144641230284811</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146157706097943</v>
+        <v>1.14711964069642</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149179128699105</v>
+        <v>1.150295460817156</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.148265943540261</v>
+        <v>1.149682697095435</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.14434936610788</v>
+        <v>1.14631273681741</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.140086459932395</v>
+        <v>1.142955701670284</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.136880435279348</v>
+        <v>1.139924781886412</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.134652106853813</v>
+        <v>1.13874686804251</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.134237187894742</v>
+        <v>1.138333210486301</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.135225076376702</v>
+        <v>1.137974066906033</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.137877516435231</v>
+        <v>1.139711581388512</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.142775083830522</v>
+        <v>1.145703051052514</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.145288278560262</v>
+        <v>1.149907617794584</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.14877374719662</v>
+        <v>1.153251572334011</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.159810162913643</v>
+        <v>1.161087588443795</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.177710081843028</v>
+        <v>1.184249482604959</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.172233530117813</v>
+        <v>1.169463694417664</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187151140413711</v>
+        <v>1.187139587217357</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178829421852712</v>
+        <v>1.178811122993468</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177342019312506</v>
+        <v>1.17732612218827</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172867996502159</v>
+        <v>1.172845574605183</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171637161032738</v>
+        <v>1.171613676108069</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16961566277624</v>
+        <v>1.169591408517951</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167147265982217</v>
+        <v>1.167122802819036</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165406814366613</v>
+        <v>1.165382483771317</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166436438893413</v>
+        <v>1.166419926683053</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161101381600068</v>
+        <v>1.161103821889279</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161579896920005</v>
+        <v>1.161581447582297</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16092887731603</v>
+        <v>1.160930077669658</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162156592116601</v>
+        <v>1.162165470934151</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159759456515629</v>
+        <v>1.159763801529659</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415025023055</v>
+        <v>1.155414773539827</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148459060347746</v>
+        <v>1.148456443553608</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143143486187779</v>
+        <v>1.143144345759468</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137905588880629</v>
+        <v>1.137912991550246</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130209463321876</v>
+        <v>1.130228264959637</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125071604856341</v>
+        <v>1.125095159114846</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129987849534058</v>
+        <v>1.130039260484947</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137112805430914</v>
+        <v>1.137185657718913</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143224412092252</v>
+        <v>1.14334501578704</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146626860715088</v>
+        <v>1.146767466498431</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146574413651515</v>
+        <v>1.146742525719034</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140847249664179</v>
+        <v>1.141022714057417</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139282585684615</v>
+        <v>1.139466590182441</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139182750556509</v>
+        <v>1.139376787908284</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150605394012133</v>
+        <v>1.150732536301163</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165986770598564</v>
+        <v>1.166071715790888</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166424282182391</v>
+        <v>1.166503529150154</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180641865785464</v>
+        <v>1.180654695677069</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191345721774084</v>
+        <v>1.191281346267824</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199513373230707</v>
+        <v>1.19943555476022</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211138115268885</v>
+        <v>1.211023273738877</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205569556928845</v>
+        <v>1.205528770895326</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206285105223193</v>
+        <v>1.206218152878667</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209718982349874</v>
+        <v>1.209574374186567</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215253077603434</v>
+        <v>1.215044729096647</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221339231475526</v>
+        <v>1.221099219080557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220172074333921</v>
+        <v>1.219985782190754</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207770923882736</v>
+        <v>1.207604246408056</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199507213018844</v>
+        <v>1.199350217068929</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189001339992238</v>
+        <v>1.188883652321681</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180717058937517</v>
+        <v>1.180618340072322</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175575553570678</v>
+        <v>1.175501593354942</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172180671197952</v>
+        <v>1.17213097317885</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173360752406216</v>
+        <v>1.173276848548591</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169502152757248</v>
+        <v>1.169447816458101</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168246857439358</v>
+        <v>1.168183356020601</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168201415923655</v>
+        <v>1.16810025580734</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166134615217852</v>
+        <v>1.166047184570675</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157968798943608</v>
+        <v>1.15790134460305</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151472436099995</v>
+        <v>1.151378860290297</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145911843620081</v>
+        <v>1.146632771121228</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14365265268713</v>
+        <v>1.144127876153305</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144641230284811</v>
+        <v>1.144590740607179</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.14711964069642</v>
+        <v>1.146139126299856</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150295460817156</v>
+        <v>1.149139797468095</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.149682697095435</v>
+        <v>1.148953650472921</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.14631273681741</v>
+        <v>1.1452783897863</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.142955701670284</v>
+        <v>1.141209522169707</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.139924781886412</v>
+        <v>1.138325474643979</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.13874686804251</v>
+        <v>1.136151294351234</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.138333210486301</v>
+        <v>1.135692336493351</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.137974066906033</v>
+        <v>1.136612875581374</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.139711581388512</v>
+        <v>1.139177897744364</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.145703051052514</v>
+        <v>1.144066070788845</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.149907617794584</v>
+        <v>1.146592117152458</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.153251572334011</v>
+        <v>1.150242249289303</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.161087588443795</v>
+        <v>1.160760431240369</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.184249482604959</v>
+        <v>1.176315599549078</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.169463694417664</v>
+        <v>1.169693473010468</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187139587217357</v>
+        <v>1.187153854744776</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178811122993468</v>
+        <v>1.17883372188102</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17732612218827</v>
+        <v>1.177345757191214</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172845574605183</v>
+        <v>1.172873267522143</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171613676108069</v>
+        <v>1.171642681704316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169591408517951</v>
+        <v>1.1696213640669</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167122802819036</v>
+        <v>1.167153016267281</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165382483771317</v>
+        <v>1.165412533479503</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166419926683053</v>
+        <v>1.166440325192649</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161103821889279</v>
+        <v>1.161100809752532</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161581447582297</v>
+        <v>1.161579534014386</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160930077669658</v>
+        <v>1.160928596676628</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162165470934151</v>
+        <v>1.162154508771583</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159763801529659</v>
+        <v>1.159758436665566</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155414773539827</v>
+        <v>1.155415086183419</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148456443553608</v>
+        <v>1.148459683325461</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143144345759468</v>
+        <v>1.143143297820591</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137912991550246</v>
+        <v>1.137903870150304</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130228264959637</v>
+        <v>1.130205062503571</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125095159114846</v>
+        <v>1.125066084745158</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.130039260484947</v>
+        <v>1.129975786462224</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137185657718913</v>
+        <v>1.137095703826587</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14334501578704</v>
+        <v>1.143196061697419</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146767466498431</v>
+        <v>1.146593799408165</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146742525719034</v>
+        <v>1.146534876859075</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.141022714057417</v>
+        <v>1.140805964093598</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139466590182441</v>
+        <v>1.139239271803292</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139376787908284</v>
+        <v>1.139137050718372</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150732536301163</v>
+        <v>1.150575431638996</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.166071715790888</v>
+        <v>1.165966756598802</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166503529150154</v>
+        <v>1.166405597370962</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180654695677069</v>
+        <v>1.180638830493001</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191281346267824</v>
+        <v>1.19136089543986</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19943555476022</v>
+        <v>1.199531709812489</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211023273738877</v>
+        <v>1.211165135987373</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205528770895326</v>
+        <v>1.205579063107423</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206218152878667</v>
+        <v>1.206300749987255</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209574374186567</v>
+        <v>1.209752914141067</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215044729096647</v>
+        <v>1.215302051367591</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221099219080557</v>
+        <v>1.2213956619095</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.219985782190754</v>
+        <v>1.220215834312329</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207604246408056</v>
+        <v>1.207810100548373</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199350217068929</v>
+        <v>1.199544132496101</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.188883652321681</v>
+        <v>1.189029049772437</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180618340072322</v>
+        <v>1.180740312008929</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175501593354942</v>
+        <v>1.175592980251044</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17213097317885</v>
+        <v>1.172192378922978</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173276848548591</v>
+        <v>1.173380506857771</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169447816458101</v>
+        <v>1.16951491991832</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168183356020601</v>
+        <v>1.16826177612066</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16810025580734</v>
+        <v>1.168225211382893</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166047184570675</v>
+        <v>1.166155173763307</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15790134460305</v>
+        <v>1.157984628455471</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151378860290297</v>
+        <v>1.151494483085294</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146632771121228</v>
+        <v>1.145933709584358</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144127876153305</v>
+        <v>1.143664155068089</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144590740607179</v>
+        <v>1.144635755657442</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146139126299856</v>
+        <v>1.147099636781606</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149139797468095</v>
+        <v>1.150255524828805</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.148953650472921</v>
+        <v>1.150253628142999</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.1452783897863</v>
+        <v>1.147060071144208</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.141209522169707</v>
+        <v>1.143824605122201</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.138325474643979</v>
+        <v>1.140983936034006</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.136151294351234</v>
+        <v>1.139709659009739</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.135692336493351</v>
+        <v>1.139265587709716</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.136612875581374</v>
+        <v>1.138880187268378</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.139177897744364</v>
+        <v>1.140546267547546</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.144066070788845</v>
+        <v>1.146406563697071</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.146592117152458</v>
+        <v>1.150502076349831</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.150242249289303</v>
+        <v>1.153967742031995</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.160760431240369</v>
+        <v>1.161742841597062</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.176315599549078</v>
+        <v>1.182655706057729</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.169693473010468</v>
+        <v>1.172273359651134</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187153854744776</v>
+        <v>1.187156504458181</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17883372188102</v>
+        <v>1.178837919856806</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177345757191214</v>
+        <v>1.177349407177311</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172873267522143</v>
+        <v>1.172878414223645</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171642681704316</v>
+        <v>1.171648072078</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.1696213640669</v>
+        <v>1.169626930712143</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167153016267281</v>
+        <v>1.167158630708929</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165412533479503</v>
+        <v>1.165418117481386</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166440325192649</v>
+        <v>1.16644412150045</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161100809752532</v>
+        <v>1.161100252061195</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161579534014386</v>
+        <v>1.161579180265541</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160928596676628</v>
+        <v>1.160928323222308</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162154508771583</v>
+        <v>1.162152476000975</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159758436665566</v>
+        <v>1.159757441453786</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415086183419</v>
+        <v>1.155415146648711</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148459683325461</v>
+        <v>1.148460294474254</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143143297820591</v>
+        <v>1.143143118923713</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137903870150304</v>
+        <v>1.137902199854014</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130205062503571</v>
+        <v>1.130200772506809</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125066084745158</v>
+        <v>1.125060701111127</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129975786462224</v>
+        <v>1.129964016289828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137095703826587</v>
+        <v>1.137079014698375</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143196061697419</v>
+        <v>1.143168380573863</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146593799408165</v>
+        <v>1.14656151529711</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146534876859075</v>
+        <v>1.146496266639017</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140805964093598</v>
+        <v>1.140765638888394</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139239271803292</v>
+        <v>1.139196958558923</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139137050718372</v>
+        <v>1.139092397755138</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150575431638996</v>
+        <v>1.150546149079519</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165966756598802</v>
+        <v>1.165947198212542</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166405597370962</v>
+        <v>1.166387333015548</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180638830493001</v>
+        <v>1.180635859695318</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19136089543986</v>
+        <v>1.191375725913619</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199531709812489</v>
+        <v>1.199549629588095</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211165135987373</v>
+        <v>1.211191527955941</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205579063107423</v>
+        <v>1.205588314964987</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206300749987255</v>
+        <v>1.206315990954671</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209752914141067</v>
+        <v>1.20978602231399</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215302051367591</v>
+        <v>1.215349867921491</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.2213956619095</v>
+        <v>1.221450763981984</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220215834312329</v>
+        <v>1.220258549485521</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207810100548373</v>
+        <v>1.207848350691059</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199544132496101</v>
+        <v>1.199580185564673</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189029049772437</v>
+        <v>1.189056121800221</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180740312008929</v>
+        <v>1.180763033412999</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175592980251044</v>
+        <v>1.175610010529558</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172192378922978</v>
+        <v>1.172203819509365</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173380506857771</v>
+        <v>1.173399806370883</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16951491991832</v>
+        <v>1.169527383544717</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.16826177612066</v>
+        <v>1.168276339392651</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168225211382893</v>
+        <v>1.168248450823914</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166155173763307</v>
+        <v>1.166175249231946</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.157984628455471</v>
+        <v>1.158000074295756</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151494483085294</v>
+        <v>1.151516027811878</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145933709584358</v>
+        <v>1.145955098701299</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143664155068089</v>
+        <v>1.143675444101159</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144635755657442</v>
+        <v>1.144630476291532</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147099636781606</v>
+        <v>1.147080139629114</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150255524828805</v>
+        <v>1.150216527828794</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150253628142999</v>
+        <v>1.150704117911818</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.147060071144208</v>
+        <v>1.147670395492698</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.143824605122201</v>
+        <v>1.14455099065779</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.140983936034006</v>
+        <v>1.141805676068561</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.139709659009739</v>
+        <v>1.140447376012195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.139265587709716</v>
+        <v>1.139928737673504</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.138880187268378</v>
+        <v>1.139480299713411</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.140546267547546</v>
+        <v>1.141029163465853</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.146406563697071</v>
+        <v>1.14669227209434</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.150502076349831</v>
+        <v>1.150538329386501</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.153967742031995</v>
+        <v>1.153999279735668</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.161742841597062</v>
+        <v>1.161447261381707</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.182655706057729</v>
+        <v>1.179986053130183</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.172273359651134</v>
+        <v>1.168851275661333</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187156504458181</v>
+        <v>1.187159091834121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178837919856806</v>
+        <v>1.178842019370115</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177349407177311</v>
+        <v>1.177352972333925</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172878414223645</v>
+        <v>1.172883440952446</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171648072078</v>
+        <v>1.171653336711776</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169626930712143</v>
+        <v>1.169632367424995</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167158630708929</v>
+        <v>1.167164114063554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165418117481386</v>
+        <v>1.165423571103155</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16644412150045</v>
+        <v>1.166447830903578</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161100252061195</v>
+        <v>1.161099708007574</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161579180265541</v>
+        <v>1.161578835332255</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160928323222308</v>
+        <v>1.160928056681874</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162152476000975</v>
+        <v>1.162150491986485</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159757441453786</v>
+        <v>1.159756469998922</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415146648711</v>
+        <v>1.155415206416408</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148460294474254</v>
+        <v>1.148460894106194</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143143118923713</v>
+        <v>1.143142948989575</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137902199854014</v>
+        <v>1.137900576023062</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130200772506809</v>
+        <v>1.130196589213485</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125060701111127</v>
+        <v>1.125055448966047</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129964016289828</v>
+        <v>1.129952528494375</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137079014698375</v>
+        <v>1.137062723325478</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143168380573863</v>
+        <v>1.14314134532622</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14656151529711</v>
+        <v>1.146529981337443</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146496266639017</v>
+        <v>1.146458550855814</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140765638888394</v>
+        <v>1.140726241002273</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139196958558923</v>
+        <v>1.139155611770991</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139092397755138</v>
+        <v>1.139048756229537</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150546149079519</v>
+        <v>1.150517523529365</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165947198212542</v>
+        <v>1.165928080092325</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166387333015548</v>
+        <v>1.166369475129846</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180635859695318</v>
+        <v>1.180632951363965</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191375725913619</v>
+        <v>1.191390224673652</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199549629588095</v>
+        <v>1.199567146572365</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211191527955941</v>
+        <v>1.211217312840855</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205588314964987</v>
+        <v>1.205597322426591</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206315990954671</v>
+        <v>1.206330843421904</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20978602231399</v>
+        <v>1.20981833641794</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215349867921491</v>
+        <v>1.215396567741875</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221450763981984</v>
+        <v>1.221504583961724</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220258549485521</v>
+        <v>1.220300256755894</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207848350691059</v>
+        <v>1.207885706718168</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199580185564673</v>
+        <v>1.199615402283735</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189056121800221</v>
+        <v>1.189082577765564</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180763033412999</v>
+        <v>1.18078524111429</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175610010529558</v>
+        <v>1.175626657746646</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172203819509365</v>
+        <v>1.172215001975047</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173399806370883</v>
+        <v>1.173418666444488</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169527383544717</v>
+        <v>1.169539554302517</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168276339392651</v>
+        <v>1.168290559769142</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168248450823914</v>
+        <v>1.168271153469217</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166175249231946</v>
+        <v>1.166194858427093</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158000074295756</v>
+        <v>1.158015150197083</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151516027811878</v>
+        <v>1.151537087126686</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145955098701299</v>
+        <v>1.145976026204887</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143675444101159</v>
+        <v>1.143686525224763</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144630476291532</v>
+        <v>1.144625383289365</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147080139629114</v>
+        <v>1.147061130812786</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150216527828794</v>
+        <v>1.150178437877882</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150704117911818</v>
+        <v>1.151137380697989</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.147670395492698</v>
+        <v>1.148253820649532</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.14455099065779</v>
+        <v>1.145240999922521</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.141805676068561</v>
+        <v>1.142587577036303</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.140447376012195</v>
+        <v>1.141131626364579</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.139928737673504</v>
+        <v>1.140531768066428</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139480299713411</v>
+        <v>1.140012560853748</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.141029163465853</v>
+        <v>1.141440087733252</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.14669227209434</v>
+        <v>1.146904207440782</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.150538329386501</v>
+        <v>1.150488586327652</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.153999279735668</v>
+        <v>1.153928485193819</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.161447261381707</v>
+        <v>1.161053091249302</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.179986053130183</v>
+        <v>1.177633424518479</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.168851275661333</v>
+        <v>1.16657043341128</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187159091834121</v>
+        <v>1.187161619046759</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178842019370115</v>
+        <v>1.178846023844573</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177352972333925</v>
+        <v>1.17735645558352</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172883440952446</v>
+        <v>1.172888351854154</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171653336711776</v>
+        <v>1.171658479953541</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169632367424995</v>
+        <v>1.169637678701106</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167164114063554</v>
+        <v>1.167169470868109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165423571103155</v>
+        <v>1.165428898857432</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166447830903578</v>
+        <v>1.166451456349372</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161099708007574</v>
+        <v>1.161099177098169</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161578835332255</v>
+        <v>1.161578498890014</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160928056681874</v>
+        <v>1.160927796797558</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162150491986485</v>
+        <v>1.162148554995898</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159756469998922</v>
+        <v>1.159755521461111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415206416408</v>
+        <v>1.155415265485372</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148460894106194</v>
+        <v>1.148461482523705</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143142948989575</v>
+        <v>1.14314278754215</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137900576023062</v>
+        <v>1.137898996792102</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130196589213485</v>
+        <v>1.130192508706353</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125055448966047</v>
+        <v>1.125050323561388</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129952528494375</v>
+        <v>1.129941313050674</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137062723325478</v>
+        <v>1.137046815678266</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14314134532622</v>
+        <v>1.14311493363574</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146529981337443</v>
+        <v>1.146499171723133</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146458550855814</v>
+        <v>1.146421698840266</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140726241002273</v>
+        <v>1.140687738884336</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139155611770991</v>
+        <v>1.139115198793653</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.139048756229537</v>
+        <v>1.13900609227996</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150517523529365</v>
+        <v>1.150489533189509</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165928080092325</v>
+        <v>1.165909387570743</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166369475129846</v>
+        <v>1.166352010338866</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180632951363965</v>
+        <v>1.180630103554486</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191390224673652</v>
+        <v>1.191404402693632</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199567146572365</v>
+        <v>1.199584274160474</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211217312840855</v>
+        <v>1.211242511325424</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205597322426591</v>
+        <v>1.205606094913351</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206330843421904</v>
+        <v>1.20634532192817</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20981833641794</v>
+        <v>1.209849884608869</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215396567741875</v>
+        <v>1.21544218944227</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221504583961724</v>
+        <v>1.221557165997423</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220300256755894</v>
+        <v>1.220340991311594</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207885706718168</v>
+        <v>1.207922199546618</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199615402283735</v>
+        <v>1.199649811341784</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189082577765564</v>
+        <v>1.189108438389458</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18078524111429</v>
+        <v>1.180806952279969</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175626657746646</v>
+        <v>1.175642934652259</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172215001975047</v>
+        <v>1.172225934937593</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173418666444488</v>
+        <v>1.173437101883134</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169539554302517</v>
+        <v>1.16955144236527</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168290559769142</v>
+        <v>1.168304449184951</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168271153469217</v>
+        <v>1.168293337667176</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166194858427093</v>
+        <v>1.166214017382859</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158015150197083</v>
+        <v>1.158029869246632</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151537087126686</v>
+        <v>1.151557677137285</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145976026204887</v>
+        <v>1.145996506696294</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143686525224763</v>
+        <v>1.143697403718568</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144625383289365</v>
+        <v>1.144620468246471</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147061130812786</v>
+        <v>1.147042592765056</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150178437877882</v>
+        <v>1.150141224434655</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151137380697989</v>
+        <v>1.151548150963909</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.148253820649532</v>
+        <v>1.148800678280282</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.145240999922521</v>
+        <v>1.145888600545445</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.142587577036303</v>
+        <v>1.1433424671465</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.141131626364579</v>
+        <v>1.141854316288396</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.140531768066428</v>
+        <v>1.141250367522192</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.140012560853748</v>
+        <v>1.140721382863134</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.141440087733252</v>
+        <v>1.142060488753855</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.146904207440782</v>
+        <v>1.147323855139311</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.150488586327652</v>
+        <v>1.150626186441436</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.153928485193819</v>
+        <v>1.15387953221404</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.161053091249302</v>
+        <v>1.160489812257422</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.177633424518479</v>
+        <v>1.175147305780067</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.16657043341128</v>
+        <v>1.163666319849915</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187161619046759</v>
+        <v>1.18716408817032</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178846023844573</v>
+        <v>1.178849936546913</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17735645558352</v>
+        <v>1.177359859715884</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172888351854154</v>
+        <v>1.172893150885599</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171658479953541</v>
+        <v>1.171663505953062</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169637678701106</v>
+        <v>1.169642868831142</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167169470868109</v>
+        <v>1.167174705452615</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165428898857432</v>
+        <v>1.165434105051007</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166451456349372</v>
+        <v>1.166455000653521</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161099177098169</v>
+        <v>1.161098658862975</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161578498890014</v>
+        <v>1.161578170629995</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160927796797558</v>
+        <v>1.160927543324195</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162148554995898</v>
+        <v>1.162146663378046</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159755521461111</v>
+        <v>1.159754595039585</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415265485372</v>
+        <v>1.155415323855693</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148461482523705</v>
+        <v>1.148462060019848</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314278754215</v>
+        <v>1.143142634134693</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137898996792102</v>
+        <v>1.137897460392532</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130192508706353</v>
+        <v>1.130188527256965</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125050323561388</v>
+        <v>1.125045320374094</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129941313050674</v>
+        <v>1.129930360401842</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137046815678266</v>
+        <v>1.137031278378255</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14311493363574</v>
+        <v>1.143089124199127</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146499171723133</v>
+        <v>1.14646906181662</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146421698840266</v>
+        <v>1.146385681306965</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140687738884336</v>
+        <v>1.140650102395643</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139115198793653</v>
+        <v>1.139075688430821</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13900609227996</v>
+        <v>1.138964373534189</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150489533189509</v>
+        <v>1.150462157211632</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165909387570743</v>
+        <v>1.16589110662327</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166352010338866</v>
+        <v>1.166334925846026</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180630103554486</v>
+        <v>1.180627314402128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191404402693632</v>
+        <v>1.191418270469955</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199584274160474</v>
+        <v>1.199601025161717</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211242511325424</v>
+        <v>1.211267143165049</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205606094913351</v>
+        <v>1.205614641373732</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20634532192817</v>
+        <v>1.206359440301431</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209849884608869</v>
+        <v>1.20988069373036</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21544218944227</v>
+        <v>1.215486769878827</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221557165997423</v>
+        <v>1.221608552237561</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220340991311594</v>
+        <v>1.220380786724726</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207922199546618</v>
+        <v>1.207957858687382</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199649811341784</v>
+        <v>1.199683440133667</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189108438389458</v>
+        <v>1.18913372347722</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180806952279969</v>
+        <v>1.180828183323396</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175642934652259</v>
+        <v>1.175658853438104</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172225934937593</v>
+        <v>1.172236626636118</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173437101883134</v>
+        <v>1.173455126835334</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16955144236527</v>
+        <v>1.169563057442017</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168304449184951</v>
+        <v>1.168318019028907</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168293337667176</v>
+        <v>1.168315020941064</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166214017382859</v>
+        <v>1.16623274140759</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158029869246632</v>
+        <v>1.158044243923497</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151557677137285</v>
+        <v>1.151577813251655</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.145996506696294</v>
+        <v>1.146016554175856</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143697403718568</v>
+        <v>1.14370808470742</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144620468246471</v>
+        <v>1.14461572321954</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147042592765056</v>
+        <v>1.147024508728776</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150141224434655</v>
+        <v>1.150104858281783</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151548150963909</v>
+        <v>1.151724303343275</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.148800678280282</v>
+        <v>1.149050800392286</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.145888600545445</v>
+        <v>1.146238127671681</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.1433424671465</v>
+        <v>1.14366546485856</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.141854316288396</v>
+        <v>1.142161075265678</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.141250367522192</v>
+        <v>1.141517263311014</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.140721382863134</v>
+        <v>1.140941259671323</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.142060488753855</v>
+        <v>1.142146570784383</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.147323855139311</v>
+        <v>1.147121450262576</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.150626186441436</v>
+        <v>1.149986355348275</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.15387953221404</v>
+        <v>1.152915361278718</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.160489812257422</v>
+        <v>1.158766862036632</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.175147305780067</v>
+        <v>1.171261165833859</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.163666319849915</v>
+        <v>1.158123147760989</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18716408817032</v>
+        <v>1.187166501184767</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178849936546913</v>
+        <v>1.178853760595868</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177359859715884</v>
+        <v>1.177363187395565</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172893150885599</v>
+        <v>1.172897841825455</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171663505953062</v>
+        <v>1.171668418673137</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169642868831142</v>
+        <v>1.169647941912328</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167174705452615</v>
+        <v>1.167179821951822</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165434105051007</v>
+        <v>1.165439193796447</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166455000653521</v>
+        <v>1.166458466507328</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161098658862975</v>
+        <v>1.161098152854104</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161578170629995</v>
+        <v>1.161577850258138</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160927543324195</v>
+        <v>1.160927296028471</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162146663378046</v>
+        <v>1.162144815558124</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159754595039585</v>
+        <v>1.159753689970421</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415323855693</v>
+        <v>1.155415381528558</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148462060019848</v>
+        <v>1.148462626878593</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143142634134693</v>
+        <v>1.143142488347661</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137897460392532</v>
+        <v>1.137895965146389</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130188527256965</v>
+        <v>1.130184641314461</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125045320374094</v>
+        <v>1.125040435093385</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129930360401842</v>
+        <v>1.129919661432317</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137031278378255</v>
+        <v>1.137016098660806</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143089124199127</v>
+        <v>1.143063896671504</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14646906181662</v>
+        <v>1.146439628083521</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146385681306965</v>
+        <v>1.146350470277261</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140650102395643</v>
+        <v>1.140613302731291</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139075688430821</v>
+        <v>1.139037050856812</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138964373534189</v>
+        <v>1.13892356902871</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150462157211632</v>
+        <v>1.150435375647037</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16589110662327</v>
+        <v>1.165873223833506</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166334925846026</v>
+        <v>1.166318209402327</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180627314402128</v>
+        <v>1.1806245821178</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191418270469955</v>
+        <v>1.191431838047323</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199601025161717</v>
+        <v>1.199617411831095</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211267143165049</v>
+        <v>1.211291227238624</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205614641373732</v>
+        <v>1.205622970312552</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206359440301431</v>
+        <v>1.206373211701093</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.20988069373036</v>
+        <v>1.209910789389041</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215486769878827</v>
+        <v>1.215530344249027</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221608552237561</v>
+        <v>1.221658782942195</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220380786724726</v>
+        <v>1.220419675042898</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207957858687382</v>
+        <v>1.207992712324332</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199683440133667</v>
+        <v>1.199716314832486</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18913372347722</v>
+        <v>1.189158451968335</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180828183323396</v>
+        <v>1.180848949944902</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175658853438104</v>
+        <v>1.175674425767788</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172236626636118</v>
+        <v>1.172247084951787</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173455126835334</v>
+        <v>1.173472754829421</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169563057442017</v>
+        <v>1.169574408803437</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168318019028907</v>
+        <v>1.168331280174642</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168315020941064</v>
+        <v>1.168336220034824</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16623274140759</v>
+        <v>1.166251045124415</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158044243923497</v>
+        <v>1.158058286133487</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151577813251655</v>
+        <v>1.151597510215454</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146016554175856</v>
+        <v>1.14603618207317</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14370808470742</v>
+        <v>1.143718573165353</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.14461572321954</v>
+        <v>1.144611140696714</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147024508728776</v>
+        <v>1.147006862712158</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150104858281783</v>
+        <v>1.150069311456754</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151724303343275</v>
+        <v>1.15167662643832</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.149050800392286</v>
+        <v>1.149334597226539</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.146238127671681</v>
+        <v>1.146592336471221</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.14366546485856</v>
+        <v>1.144138648871833</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.142161075265678</v>
+        <v>1.142809118690888</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.141517263311014</v>
+        <v>1.142183608534694</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.140941259671323</v>
+        <v>1.141650227980248</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.142146570784383</v>
+        <v>1.142848035819623</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.147121450262576</v>
+        <v>1.147779912369814</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.149986355348275</v>
+        <v>1.15075018523219</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.152915361278718</v>
+        <v>1.153925330263411</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.158766862036632</v>
+        <v>1.159922863505097</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.171261165833859</v>
+        <v>1.172067811797092</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.158123147760989</v>
+        <v>1.161889411269641</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B119">
+        <v>1.177429411269641</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187166501184767</v>
+        <v>1.187168859981093</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178853760595868</v>
+        <v>1.17885749897045</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177363187395565</v>
+        <v>1.177366441168822</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172897841825455</v>
+        <v>1.172902428284149</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171668418673137</v>
+        <v>1.171673221900001</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169647941912328</v>
+        <v>1.16965290185923</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167179821951822</v>
+        <v>1.167184824316093</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165439193796447</v>
+        <v>1.165444169022912</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166458466507328</v>
+        <v>1.166461856484494</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161098152854104</v>
+        <v>1.161097658644501</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161577850258138</v>
+        <v>1.16157753749427</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160927296028471</v>
+        <v>1.160927054688217</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162144815558124</v>
+        <v>1.16214301003333</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159753689970421</v>
+        <v>1.159752805524453</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415381528558</v>
+        <v>1.15541543850612</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148462626878593</v>
+        <v>1.148463183375094</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143142488347661</v>
+        <v>1.143142349786808</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137895965146389</v>
+        <v>1.137894509460699</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130184641314461</v>
+        <v>1.130180847495151</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125040435093385</v>
+        <v>1.125035663608463</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129919661432317</v>
+        <v>1.129909207442702</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137016098660806</v>
+        <v>1.137001264340379</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143063896671504</v>
+        <v>1.143039231613175</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146439628083521</v>
+        <v>1.146410848031662</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146350470277261</v>
+        <v>1.146316039007303</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140613302731291</v>
+        <v>1.140577312347578</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.139037050856812</v>
+        <v>1.138999257542125</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13892356902871</v>
+        <v>1.138883649133195</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150435375647037</v>
+        <v>1.150409169398798</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165873223833506</v>
+        <v>1.165855726360647</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166318209402327</v>
+        <v>1.166301849277487</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.1806245821178</v>
+        <v>1.180621904984281</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191431838047323</v>
+        <v>1.191445115042702</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199617411831095</v>
+        <v>1.19963344589891</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211291227238624</v>
+        <v>1.211314781596557</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205622970312552</v>
+        <v>1.205631089817889</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206373211701093</v>
+        <v>1.206386648657672</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209910789389041</v>
+        <v>1.209940196024855</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215530344249027</v>
+        <v>1.215572946183825</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221658782942195</v>
+        <v>1.221707896587351</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220419675042898</v>
+        <v>1.220457686874629</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.207992712324332</v>
+        <v>1.208026787387847</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199716314832486</v>
+        <v>1.199748460456764</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189158451968335</v>
+        <v>1.189182641983088</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180848949944902</v>
+        <v>1.180869267169946</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175674425767788</v>
+        <v>1.175689662805035</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172247084951787</v>
+        <v>1.172257317426993</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173472754829421</v>
+        <v>1.173489998807078</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169574408803437</v>
+        <v>1.169585505306239</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168331280174642</v>
+        <v>1.168344243009316</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168336220034824</v>
+        <v>1.168356950955829</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166251045124415</v>
+        <v>1.166268942509105</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158058286133487</v>
+        <v>1.158072007241579</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151597510215454</v>
+        <v>1.15161678214696</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14603618207317</v>
+        <v>1.146055403275427</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143718573165353</v>
+        <v>1.14372887391963</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144611140696714</v>
+        <v>1.144606713570074</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.147006862712158</v>
+        <v>1.146989639446632</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150069311456754</v>
+        <v>1.150034557186813</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.15167662643832</v>
+        <v>1.151629944944829</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.149334597226539</v>
+        <v>1.149560830864865</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.146592336471221</v>
+        <v>1.146881106161176</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.144138648871833</v>
+        <v>1.144534965017848</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.142809118690888</v>
+        <v>1.143259289090274</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142183608534694</v>
+        <v>1.142663834146591</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.141650227980248</v>
+        <v>1.142159307917975</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.142848035819623</v>
+        <v>1.143334678929552</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.147779912369814</v>
+        <v>1.14817860420022</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.15075018523219</v>
+        <v>1.151189492883681</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.153925330263411</v>
+        <v>1.154476419970921</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.159922863505097</v>
+        <v>1.160463367325573</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.172067811797092</v>
+        <v>1.172031309517297</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.161889411269641</v>
+        <v>1.163443793991125</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.177429411269641</v>
+        <v>1.178983793991125</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187168859981093</v>
+        <v>1.187171166366268</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17885749897045</v>
+        <v>1.178861154517689</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177366441168822</v>
+        <v>1.177369623470116</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172902428284149</v>
+        <v>1.172906913713126</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171673221900001</v>
+        <v>1.171677919253052</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16965290185923</v>
+        <v>1.169657752413817</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167184824316093</v>
+        <v>1.167189716321568</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165444169022912</v>
+        <v>1.165449034486269</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166461856484494</v>
+        <v>1.166465173047466</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161097658644501</v>
+        <v>1.161097175826745</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.16157753749427</v>
+        <v>1.161577232071296</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160927054688217</v>
+        <v>1.16092681909175</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16214301003333</v>
+        <v>1.162141245368797</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159752805524453</v>
+        <v>1.159751941005308</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541543850612</v>
+        <v>1.155415494791395</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148463183375094</v>
+        <v>1.148463729775961</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143142349786808</v>
+        <v>1.143142218081425</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137894509460699</v>
+        <v>1.137893091822231</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130180847495151</v>
+        <v>1.130177142572824</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125035663608463</v>
+        <v>1.125031001997077</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129909207442702</v>
+        <v>1.129898990126323</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.137001264340379</v>
+        <v>1.136986763778097</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143039231613175</v>
+        <v>1.143015110439886</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146410848031662</v>
+        <v>1.146382700154097</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146316039007303</v>
+        <v>1.146282361920789</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140577312347578</v>
+        <v>1.140542104893877</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138999257542125</v>
+        <v>1.138962281183986</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138883649133195</v>
+        <v>1.13884458547977</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150409169398798</v>
+        <v>1.150383520176928</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165855726360647</v>
+        <v>1.16583860190901</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166301849277487</v>
+        <v>1.166285834232859</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180621904984281</v>
+        <v>1.180619281352655</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191445115042702</v>
+        <v>1.19145811066779</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19963344589891</v>
+        <v>1.199649138598463</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211314781596557</v>
+        <v>1.211337823505672</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205631089817889</v>
+        <v>1.205639007586068</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206386648657672</v>
+        <v>1.206399763109694</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209940196024855</v>
+        <v>1.209968936976614</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215572946183825</v>
+        <v>1.215614607833724</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221707896587351</v>
+        <v>1.221755929962588</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220457686874629</v>
+        <v>1.220494851469081</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208026787387847</v>
+        <v>1.208060109623581</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199748460456764</v>
+        <v>1.199779900933253</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189182641983088</v>
+        <v>1.189206310866226</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180869267169946</v>
+        <v>1.180889149384871</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175689662805035</v>
+        <v>1.175704575240119</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172257317426993</v>
+        <v>1.172267331283323</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173489998807078</v>
+        <v>1.173506871154721</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169585505306239</v>
+        <v>1.169596355415953</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168344243009316</v>
+        <v>1.168356917460456</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168356950955829</v>
+        <v>1.168377229014866</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166268942509105</v>
+        <v>1.166286446925454</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158072007241579</v>
+        <v>1.158085418102179</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15161678214696</v>
+        <v>1.151635642569826</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146055403275427</v>
+        <v>1.146074230154111</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14372887391963</v>
+        <v>1.143738991654799</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144606713570074</v>
+        <v>1.144602435110131</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146989639446632</v>
+        <v>1.146972824347376</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150034557186813</v>
+        <v>1.150000569827796</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151629944944829</v>
+        <v>1.151584228860591</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.149560830864865</v>
+        <v>1.149888484180757</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.146881106161176</v>
+        <v>1.147273726614604</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.144534965017848</v>
+        <v>1.145023587181444</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.143259289090274</v>
+        <v>1.143802994590154</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142663834146591</v>
+        <v>1.143237505647215</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.142159307917975</v>
+        <v>1.142776228050677</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.143334678929552</v>
+        <v>1.143931849944964</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.14817860420022</v>
+        <v>1.14871757608155</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.151189492883681</v>
+        <v>1.151780390173678</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.154476419970921</v>
+        <v>1.155183747129236</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.160463367325573</v>
+        <v>1.161178329018068</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.172031309517297</v>
+        <v>1.17230404146458</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.163443793991125</v>
+        <v>1.165084634471231</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.178983793991125</v>
+        <v>1.179282563252919</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187171166366268</v>
+        <v>1.187173422067848</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178861154517689</v>
+        <v>1.178864729959867</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177369623470116</v>
+        <v>1.177372736628175</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172906913713126</v>
+        <v>1.172911301413495</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171677919253052</v>
+        <v>1.171682514193936</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169657752413817</v>
+        <v>1.169662497154869</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167189716321568</v>
+        <v>1.167194501579658</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165449034486269</v>
+        <v>1.165453793778536</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166465173047466</v>
+        <v>1.16646841855338</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161097175826745</v>
+        <v>1.161096704011938</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161577232071296</v>
+        <v>1.161576933734455</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16092681909175</v>
+        <v>1.160926589037266</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162141245368797</v>
+        <v>1.162139520193801</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159751941005308</v>
+        <v>1.1597510957476</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415494791395</v>
+        <v>1.155415550388155</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148463729775961</v>
+        <v>1.148464266339529</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143142218081425</v>
+        <v>1.143142092882719</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137893091822231</v>
+        <v>1.137891710792639</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130177142572824</v>
+        <v>1.130173523469714</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125031001997077</v>
+        <v>1.125026446514847</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129898990126323</v>
+        <v>1.129889001547338</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136986763778097</v>
+        <v>1.13697258585148</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.143015110439886</v>
+        <v>1.142991515376339</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146382700154097</v>
+        <v>1.146355163875826</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146282361920789</v>
+        <v>1.146249414546034</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140542104893877</v>
+        <v>1.140507655148876</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138962281183986</v>
+        <v>1.138926095641293</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13884458547977</v>
+        <v>1.13880635089672</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150383520176928</v>
+        <v>1.150358410456338</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16583860190901</v>
+        <v>1.165821838699472</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166285834232859</v>
+        <v>1.166270153496038</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180619281352655</v>
+        <v>1.180616709638949</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19145811066779</v>
+        <v>1.191470833750069</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199649138598463</v>
+        <v>1.199664500692044</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211337823505672</v>
+        <v>1.211360369491225</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205639007586068</v>
+        <v>1.205646730944889</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206399763109694</v>
+        <v>1.206412566438039</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209968936976614</v>
+        <v>1.209997034543187</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215614607833724</v>
+        <v>1.21565535994924</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221755929962588</v>
+        <v>1.221802918262237</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220494851469081</v>
+        <v>1.220531196790568</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208060109623581</v>
+        <v>1.208092703656766</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199779900933253</v>
+        <v>1.199810659155691</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189206310866226</v>
+        <v>1.189229475227869</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180889149384871</v>
+        <v>1.180908610370408</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175704575240119</v>
+        <v>1.175719173314641</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172267331283323</v>
+        <v>1.172277133438394</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173506871154721</v>
+        <v>1.173523383732895</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169596355415953</v>
+        <v>1.169606967228241</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168356917460456</v>
+        <v>1.16836931302103</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168377229014866</v>
+        <v>1.168397068863547</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166286446925454</v>
+        <v>1.166303571158367</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158085418102179</v>
+        <v>1.158098529087403</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151635642569826</v>
+        <v>1.151654104443834</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146074230154111</v>
+        <v>1.146092674590164</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143738991654799</v>
+        <v>1.143748930916735</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144602435110131</v>
+        <v>1.144598298942162</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146972824347376</v>
+        <v>1.146956403476355</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.150000569827796</v>
+        <v>1.149967324806605</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151584228860591</v>
+        <v>1.151539449340048</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.149888484180757</v>
+        <v>1.150250515098313</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.147273726614604</v>
+        <v>1.147710136675703</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.145023587181444</v>
+        <v>1.145569069348134</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.143802994590154</v>
+        <v>1.144463388339413</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.143237505647215</v>
+        <v>1.143970939949559</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.142776228050677</v>
+        <v>1.143601025627671</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.143931849944964</v>
+        <v>1.144794043136653</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.14871757608155</v>
+        <v>1.149611071581588</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.151780390173678</v>
+        <v>1.152837965801335</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.155183747129236</v>
+        <v>1.156579050453105</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.161178329018068</v>
+        <v>1.162839304064384</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.17230404146458</v>
+        <v>1.174026609552606</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.165084634471231</v>
+        <v>1.168894165674924</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.179282563252919</v>
+        <v>1.185569908412051</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187173422067848</v>
+        <v>1.187175628738295</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178864729959867</v>
+        <v>1.178868227901267</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177372736628175</v>
+        <v>1.177375782871674</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172911301413495</v>
+        <v>1.172915594544133</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171682514193936</v>
+        <v>1.171687010035049</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169662497154869</v>
+        <v>1.169667139506773</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167194501579658</v>
+        <v>1.167199183545933</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165453793778536</v>
+        <v>1.165458450336723</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16646841855338</v>
+        <v>1.166471595259623</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161096704011938</v>
+        <v>1.161096242828663</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161576933734455</v>
+        <v>1.161576642240605</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160926589037266</v>
+        <v>1.160926364332273</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162139520193801</v>
+        <v>1.162137833198216</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.1597510957476</v>
+        <v>1.159750269115211</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415550388155</v>
+        <v>1.155415605300843</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148464266339529</v>
+        <v>1.148464793316123</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143142092882719</v>
+        <v>1.143141973862328</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137891710792639</v>
+        <v>1.137890365003943</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130173523469714</v>
+        <v>1.130169987248081</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125026446514847</v>
+        <v>1.125021993585315</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129889001547338</v>
+        <v>1.129879234120304</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.13697258585148</v>
+        <v>1.136958719926152</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142991515376339</v>
+        <v>1.142968429412685</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146355163875826</v>
+        <v>1.146328219503926</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146249414546034</v>
+        <v>1.146217173457084</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140507655148876</v>
+        <v>1.140473938960845</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138926095641293</v>
+        <v>1.138890675873649</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13880635089672</v>
+        <v>1.13876891934632</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150358410456338</v>
+        <v>1.150333823437388</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165821838699472</v>
+        <v>1.165805425442688</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166270153496038</v>
+        <v>1.166254796737003</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180616709638949</v>
+        <v>1.180614188320976</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191470833750069</v>
+        <v>1.19148329275258</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199664500692044</v>
+        <v>1.199679542495296</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211360369491225</v>
+        <v>1.211382435376254</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205646730944889</v>
+        <v>1.205654266875231</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206412566438039</v>
+        <v>1.206425069497929</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.209997034543187</v>
+        <v>1.210024510040665</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21565535994924</v>
+        <v>1.215695231956193</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221802918262237</v>
+        <v>1.221848895170786</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220531196790568</v>
+        <v>1.220566749588217</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208092703656766</v>
+        <v>1.208124593052384</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199810659155691</v>
+        <v>1.199840757039813</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189229475227869</v>
+        <v>1.18925215098187</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180908610370408</v>
+        <v>1.180927663333106</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175719173314641</v>
+        <v>1.175733466844769</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172277133438394</v>
+        <v>1.172286730521648</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173523383732895</v>
+        <v>1.17353954790383</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169606967228241</v>
+        <v>1.169617348488823</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.16836931302103</v>
+        <v>1.168381438772912</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168397068863547</v>
+        <v>1.168416484529338</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166303571158367</v>
+        <v>1.166320327444827</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158098529087403</v>
+        <v>1.158111350113482</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151654104443834</v>
+        <v>1.151672180193766</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146092674590164</v>
+        <v>1.146110747997715</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143748930916735</v>
+        <v>1.143758696116655</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144598298942162</v>
+        <v>1.144594299024233</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146956403476355</v>
+        <v>1.146940363507675</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149967324806605</v>
+        <v>1.149934798567092</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151539449340048</v>
+        <v>1.151495578641134</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150250515098313</v>
+        <v>1.150595571026893</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.147710136675703</v>
+        <v>1.148127180666187</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.145569069348134</v>
+        <v>1.146087482819454</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.144463388339413</v>
+        <v>1.145076965125288</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.143970939949559</v>
+        <v>1.144623445958973</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.143601025627671</v>
+        <v>1.144282115638219</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.144794043136653</v>
+        <v>1.145438859225208</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.149611071581588</v>
+        <v>1.150154958180962</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.152837965801335</v>
+        <v>1.153343468841557</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.156579050453105</v>
+        <v>1.157022916292866</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.162839304064384</v>
+        <v>1.16310090962352</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.174026609552606</v>
+        <v>1.17363882562071</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.168894165674924</v>
+        <v>1.168764577902035</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.185569908412051</v>
+        <v>1.181666008857891</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187175628738295</v>
+        <v>1.18717778795901</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178868227901267</v>
+        <v>1.178871650834505</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177375782871674</v>
+        <v>1.177378764334548</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172915594544133</v>
+        <v>1.172919796129255</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171687010035049</v>
+        <v>1.171691409947492</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169667139506773</v>
+        <v>1.169671682747763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167199183545933</v>
+        <v>1.167203765528434</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165458450336723</v>
+        <v>1.165463007451099</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166471595259623</v>
+        <v>1.166474705329052</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161096242828663</v>
+        <v>1.161095791922017</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161576642240605</v>
+        <v>1.161576357357582</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160926364332273</v>
+        <v>1.16092614479306</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162137833198216</v>
+        <v>1.162136183129206</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159750269115211</v>
+        <v>1.159749460499713</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415605300843</v>
+        <v>1.15541565953449</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148464793316123</v>
+        <v>1.148465310948314</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141973862328</v>
+        <v>1.143141860710935</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137890365003943</v>
+        <v>1.137889053154339</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130169987248081</v>
+        <v>1.130166531102364</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125021993585315</v>
+        <v>1.125017639790652</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129879234120304</v>
+        <v>1.129869680591068</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136958719926152</v>
+        <v>1.136945155829395</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142968429412685</v>
+        <v>1.14294583626381</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146328219503926</v>
+        <v>1.146301848180843</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146217173457084</v>
+        <v>1.146185616218527</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140473938960845</v>
+        <v>1.140440933191652</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138890675873649</v>
+        <v>1.138855997884184</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13876891934632</v>
+        <v>1.138732265866479</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150333823437388</v>
+        <v>1.150309743008843</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165805425442688</v>
+        <v>1.165789351313944</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166254796737003</v>
+        <v>1.166239754045718</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180614188320976</v>
+        <v>1.180611715935355</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19148329275258</v>
+        <v>1.19149549579248</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199679542495296</v>
+        <v>1.199694273900093</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211382435376254</v>
+        <v>1.21140403631844</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205654266875231</v>
+        <v>1.205661622031162</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206425069497929</v>
+        <v>1.206437282648754</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210024510040665</v>
+        <v>1.210051383855798</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215695231956193</v>
+        <v>1.215734252026183</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221848895170786</v>
+        <v>1.221893892942855</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220566749588217</v>
+        <v>1.220601535461156</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208124593052384</v>
+        <v>1.208155800371506</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199840757039813</v>
+        <v>1.199870215574894</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18925215098187</v>
+        <v>1.189274353381796</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180927663333106</v>
+        <v>1.180946320934833</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175733466844769</v>
+        <v>1.175747465243053</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172286730521648</v>
+        <v>1.172296128889161</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17353954790383</v>
+        <v>1.173555374557277</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169617348488823</v>
+        <v>1.169627506612142</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168381438772912</v>
+        <v>1.168393303408847</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168416484529338</v>
+        <v>1.168435489448388</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166320327444827</v>
+        <v>1.166336727502901</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158111350113482</v>
+        <v>1.158123890665471</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151672180193766</v>
+        <v>1.151689881736541</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146110747997715</v>
+        <v>1.146128461346466</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143758696116655</v>
+        <v>1.143768291535095</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144594299024233</v>
+        <v>1.144590429626793</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146940363507675</v>
+        <v>1.146924691695088</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149934798567092</v>
+        <v>1.149902968519102</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151495578641134</v>
+        <v>1.151452590074888</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150595571026893</v>
+        <v>1.150924735187069</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.148127180666187</v>
+        <v>1.148506522348387</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146087482819454</v>
+        <v>1.146560353521602</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145076965125288</v>
+        <v>1.145647187601594</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.144623445958973</v>
+        <v>1.14529471257939</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.144282115638219</v>
+        <v>1.145077065701828</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.145438859225208</v>
+        <v>1.146295804364907</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.150154958180962</v>
+        <v>1.151038675977144</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.153343468841557</v>
+        <v>1.154355013740909</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.157022916292866</v>
+        <v>1.158316903846789</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.16310090962352</v>
+        <v>1.164651446126515</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.17363882562071</v>
+        <v>1.175266202159758</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.168764577902035</v>
+        <v>1.171814559613975</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.181666008857891</v>
+        <v>1.185414939501377</v>
       </c>
     </row>
   </sheetData>
